--- a/DOCS/enemyrandologic.xlsx
+++ b/DOCS/enemyrandologic.xlsx
@@ -145,7 +145,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Give every area a tier (1-7, story order) and every monster a native tier (the tier of the area it comes from). An area of tier T draws its roster only from monsters whose native tier is within a chosen spread of T, and any monster placed outside its native tier has its stats rescaled toward the destination area's vanilla averages, so the shape of the monster (glass cannon, tank, fast) survives but its budget matches where it now lives. Exp and stones always scale with the destination, so levelling pace is unchanged.</t>
+          <t xml:space="preserve">Give every area a tier (1-8, story order) and every monster a native tier (the tier of the area it comes from). An area of tier T draws its roster only from monsters whose native tier is within a chosen spread of T, and every placed monster has its stats rescaled toward the destination area's budget, so the shape of the monster (glass cannon, tank, fast) survives but its numbers match where it now lives. The budget never goes down from one area to the next, so the game always gets progressively harder regardless of what the seed placed where. Exp and stones follow the destination budget, so levelling pace is unchanged.</t>
         </is>
       </c>
     </row>
@@ -160,7 +160,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Tiers. Areas tab, column C. Suggested: T1 Holy Plains/Connor, T2 Dondoran Flats/Glencoe/West Carmaugh, T3 Cull Hazard/East Limelin/Windward, T4 Blue Cave/Isle of Skye/Baragoon Tunnel, T5 Dindom Dries/Boil Hole/Baragoon Moor, T6 Brannoch, T7 Mammon's World. Editable.</t>
+          <t xml:space="preserve">1. Tiers (Areas tab, column C): T1 Holy Plains / Connor Forest, T2 Dondoran Flats / Glencoe Forest / West Carmaugh, T3 Cull Hazard / East Limelin, T4 Windward Forest / Blue Cave / Isle of Skye, T5 Baragoon Tunnel, T6 Dindom Dries / Boil Hole, T7 Baragoon Moor / Brannoch Castle, T8 Mammon's World. Editable.</t>
         </is>
       </c>
     </row>
@@ -174,7 +174,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Tier spread (Settings B4). A tier-T area may take monsters of native tier T-spread .. T+spread. 0 = same tier only (a reshuffle within difficulty bands), 1 = the recommended default, 2 = wild, 6 = anything goes (Merrow's behaviour). Dangerous monsters (Monsters column L: Cockatrice petrifies, Flamed Mane) never go below their native tier whatever the spread.</t>
+          <t xml:space="preserve">3. Spread (Settings B4 down / B5 up). A tier-T area may take monsters of native tier T-down .. T+up. 0/0 = a reshuffle within difficulty bands, 1/1 = the recommended default, 0/2 = only ever harder monsters (scaled down to fit), 7/7 = anything goes (Merrow's behaviour). Dangerous monsters (Monsters column L: Cockatrice petrifies, Flamed Mane) never go below their native tier whatever the spread.</t>
         </is>
       </c>
     </row>
@@ -188,41 +188,48 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. Stat scaling (Settings B5). For a monster placed in area A: factor = AreaAvg(A, stat) / AreaAvg(home, stat); new = round(own * factor ^ k). k = 1.0 fits the monster fully to the new area, 0.5 meets halfway, 0 leaves stats alone (not recommended). EXP always uses k = 1. HP capped at 999, ATK/DEF/AGI at 255. See ScalingExample for a live worked example.</t>
+          <t xml:space="preserve">5. Stat scaling (Settings B6). For a monster placed in area A: factor = AreaAvg(A, stat) / AreaAvg(home, stat); new = round(own * factor ^ k * guard(A)). k = 1.0 fits the monster fully to the new area, 0.5 meets halfway, 0 leaves stats alone (not recommended). EXP always uses k = 1. HP capped at 999, ATK/DEF/AGI at 255. See ScalingExample for a live worked example.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6. Flying (Monsters column K). The vanilla game limits fliers because some spells cannot reach them; keep at most Settings B6 fliers per area and none in tier 1.</t>
+          <t xml:space="preserve">6. Progression guard (Areas columns M-N). Each area gets a budget = MAX(its own vanilla average power, the previous area's budget), so budgets never fall as you move through the game. guard(A) = budget / own average power, which is 1.0 wherever vanilla already climbs and &gt; 1 where it dips (East Limelin -&gt; Windward Forest is the one real dip). Applied to every placed monster, this is what makes the randomized game strictly progressively harder.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7. Bosses are never moved or rescaled here; Merrow's boss options already cover them.</t>
+          <t xml:space="preserve">7. Flying (Monsters column K, the ROM's flag). The vanilla game limits fliers because some spells cannot reach them; keep at most Settings B7 fliers per area and none in tier 1.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8. Same seed, same result: the placement is a pure function of the seed and these settings, so a seed can be shared like any other randomizer seed, and the spoiler log lists each area's new roster with the scaled stats.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+          <t xml:space="preserve">8. Bosses are out of scope. The boss logic that already exists in the randomizer stays as it is; nothing here moves, rescales or reads the boss entries (monster ids 67+).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. Same seed, same result: the placement is a pure function of the seed and these settings, so a seed can be shared like any other randomizer seed, and the spoiler log lists each area's new roster with the scaled stats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Why this is cheap to build</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Everything it changes is ROM data the randomizer already writes at boot: the area's table index (map header), the pack member ids, and each monster's six stat halfwords (Monsters column S has the ROM address). No native hooks and no recompiled code. The one engine question to verify is whether a table can mix monsters from different world chunks (the Implementation tab explains).</t>
         </is>
@@ -274,7 +281,7 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tier spread</t>
+          <t xml:space="preserve">Spread down (tiers below)</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -282,14 +289,14 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">How many tiers away from an area's tier a monster may come from. 0 strict, 1 recommended, 2 wild, 6 = anything (Merrow).</t>
+          <t xml:space="preserve">An area may take monsters from this many tiers BELOW its own (easier monsters, scaled up). 0 = none.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scaling strength k</t>
+          <t xml:space="preserve">Spread up (tiers above)</t>
         </is>
       </c>
       <c r="B5" s="2">
@@ -297,214 +304,242 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 = keep home stats, 0.5 = halfway to the destination area's average, 1 = full fit. EXP always uses 1.</t>
+          <t xml:space="preserve">An area may take monsters from this many tiers ABOVE its own (harder monsters, scaled down). 0 = none. 7 = anything (Merrow's behaviour).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max fliers per area</t>
+          <t xml:space="preserve">Scaling strength k</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upper bound on flying monsters in one roster; tier 1 gets none.</t>
+          <t xml:space="preserve">0 = keep home stats, 0.5 = halfway to the destination area's average, 1 = full fit. EXP and the progression guard always use 1.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dangerous: keep at native tier or above</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
+          <t xml:space="preserve">Max fliers per area</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <v>2</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cockatrice / Flamed Mane never appear earlier than vanilla.</t>
+          <t xml:space="preserve">Upper bound on flying monsters in one roster; tier 1 gets none.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulk: DEF weight</t>
-        </is>
-      </c>
-      <c r="B8" s="2">
-        <v>25</v>
+          <t xml:space="preserve">Dangerous: keep at native tier or above</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulk = HP * (1 + DEF / this). Larger = DEF matters less.</t>
+          <t xml:space="preserve">Cockatrice / Flamed Mane never appear earlier than vanilla.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bulk: DEF weight</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulk = HP * (1 + DEF / this). Larger = DEF matters less.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Threat: AGI weight</t>
         </is>
       </c>
-      <c r="B9" s="2">
+      <c r="B10" s="2">
         <v>50</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Threat = ATK * (1 + AGI / this). Larger = AGI matters less.</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Power tier thresholds</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Power at least</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tier</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T2 from</t>
-        </is>
-      </c>
-      <c r="B12" s="2">
-        <v>30</v>
-      </c>
-      <c r="C12" s="0">
-        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T3 from</t>
+          <t xml:space="preserve">T2 from</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="C13" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T4 from</t>
+          <t xml:space="preserve">T3 from</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="C14" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T5 from</t>
+          <t xml:space="preserve">T4 from</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="C15" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T6 from</t>
+          <t xml:space="preserve">T5 from</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>330</v>
+        <v>160</v>
       </c>
       <c r="C16" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">T6 from</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <v>250</v>
+      </c>
+      <c r="C17" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">T7 from</t>
         </is>
       </c>
-      <c r="B17" s="2">
-        <v>400</v>
-      </c>
-      <c r="C17" s="0">
+      <c r="B18" s="2">
+        <v>360</v>
+      </c>
+      <c r="C18" s="0">
         <v>7</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Power = SQRT(Bulk * Threat). Thresholds were chosen so the vanilla areas land on their story tiers; adjust and watch Monsters column P.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T8 from</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <v>450</v>
+      </c>
+      <c r="C19" s="0">
+        <v>8</v>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power = SQRT(Bulk * Threat). Vanilla tier averages under the eight tiers: T1 15, T2 48, T3 119, T4 111, T5 187, T6 329, T7 397, T8 504 (T3 and T4 overlap: East Limelin is tougher by numbers than Windward/Blue Cave). Adjust and watch Monsters column P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Stat caps</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Cap</t>
         </is>
       </c>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">HP cap</t>
         </is>
       </c>
-      <c r="B21" s="2">
+      <c r="B23" s="2">
         <v>999</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Vanilla monsters stay under 999; Hard Mode raises Brian's caps to 999 too.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="0" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">ATK/DEF/AGI cap</t>
         </is>
       </c>
-      <c r="B22" s="2">
+      <c r="B24" s="2">
         <v>255</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Stored as bytes in the game's battle struct.</t>
         </is>
@@ -539,14 +574,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areas: progression order, tier, vanilla roster and averages</t>
+          <t xml:space="preserve">Areas: progression order, tier, vanilla roster, averages and progression budget</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tier (C) is an input. Averages (G-K) are over the area's vanilla roster (Roster tab). Allowed tiers (M-N) follow Settings!B4. O counts how many monsters could be placed here under the current settings; P is the vanilla roster size the randomizer must fill.</t>
+          <t xml:space="preserve">Tier (C) is an input. Averages (G-L) are over the area's vanilla roster (Roster tab). Budget (M) = MAX(own average power, previous budget), so it never falls; Guard (N) = budget / own average, the multiplier applied to everything placed here. Allowed tiers (O-P) follow the spread settings. Q counts how many monsters could be placed here under the current settings; E is how many the randomizer must place.</t>
         </is>
       </c>
     </row>
@@ -613,25 +648,35 @@
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Progression budget</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guard x</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Allowed tier min</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Allowed tier max</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Candidate monsters</t>
         </is>
       </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Packs (vanilla: monster x always + extra)</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Notes</t>
         </is>
@@ -678,21 +723,27 @@
       <c r="L4" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B4)</f>
       </c>
-      <c r="M4" s="0">
+      <c r="M4" s="7">
+        <f>L4</f>
+      </c>
+      <c r="N4" s="7">
+        <f>M4/L4</f>
+      </c>
+      <c r="O4" s="0">
         <f>MAX(1,C4-Settings!$B$4)</f>
       </c>
-      <c r="N4" s="0">
-        <f>MIN(7,C4+Settings!$B$4)</f>
-      </c>
-      <c r="O4" s="0">
+      <c r="P4" s="0">
+        <f>MIN(8,C4+Settings!$B$5)</f>
+      </c>
+      <c r="Q4" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C4,Monsters!$R:$R,"&gt;="&amp;C4)</f>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[WERE HARE x1+2] [HELL HOUND x1+1] [BIG MOUTH x1+0] [HELL HOUND x3+1] [MAN EATER x2+1] [PARASAULT x1+0, BUMBERSHOOT x1+0] [BIG MOUTH x1+0, WERE HARE x2+1] [WERE HARE x1+1, MAN EATER x1+0] [ORK JR x1+0]</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Melrode / Dondoran start</t>
         </is>
@@ -739,21 +790,27 @@
       <c r="L5" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B5)</f>
       </c>
-      <c r="M5" s="0">
+      <c r="M5" s="7">
+        <f>MAX(L5,M4)</f>
+      </c>
+      <c r="N5" s="7">
+        <f>M5/L5</f>
+      </c>
+      <c r="O5" s="0">
         <f>MAX(1,C5-Settings!$B$4)</f>
       </c>
-      <c r="N5" s="0">
-        <f>MIN(7,C5+Settings!$B$4)</f>
-      </c>
-      <c r="O5" s="0">
+      <c r="P5" s="0">
+        <f>MIN(8,C5+Settings!$B$5)</f>
+      </c>
+      <c r="Q5" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C5,Monsters!$R:$R,"&gt;="&amp;C5)</f>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[KOBOLD x1+2] [MAN TRAP x1+1] [BAT x3+3] [FROG KNIGHT x1+1] [MARIONASTY x1+1] [BAT x1+1, KOBOLD x1+0] [KOBOLD x1+0, MARIONASTY x1+0] [FROG KNIGHT x1+0, KOBOLD x1+0, MARIONASTY x1+0] [MAN TRAP x1+0, BAT x1+1]</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Solvaring</t>
         </is>
@@ -800,21 +857,27 @@
       <c r="L6" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B6)</f>
       </c>
-      <c r="M6" s="0">
+      <c r="M6" s="7">
+        <f>MAX(L6,M5)</f>
+      </c>
+      <c r="N6" s="7">
+        <f>M6/L6</f>
+      </c>
+      <c r="O6" s="0">
         <f>MAX(1,C6-Settings!$B$4)</f>
       </c>
-      <c r="N6" s="0">
-        <f>MIN(7,C6+Settings!$B$4)</f>
-      </c>
-      <c r="O6" s="0">
+      <c r="P6" s="0">
+        <f>MIN(8,C6+Settings!$B$5)</f>
+      </c>
+      <c r="Q6" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C6,Monsters!$R:$R,"&gt;="&amp;C6)</f>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[APOPHIS x1+1] [DEATH HUGGER x3+2] [MAD DOLL x1+1] [MAD DOLL x1+0, DEATH HUGGER x2+1] [GOBLIN x2+2] [GOBLIN x2+0, DEATH HUGGER x3+0] [FROG KING x1+0] [FROG KING x1+0, FROG KNIGHT x2+0] [GOBLIN x2+1, FROG KNIGHT x1+0] [COCKATRICE x1+1]</t>
         </is>
       </c>
-      <c r="Q6" s="3"/>
+      <c r="S6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -857,21 +920,27 @@
       <c r="L7" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B7)</f>
       </c>
-      <c r="M7" s="0">
+      <c r="M7" s="7">
+        <f>MAX(L7,M6)</f>
+      </c>
+      <c r="N7" s="7">
+        <f>M7/L7</f>
+      </c>
+      <c r="O7" s="0">
         <f>MAX(1,C7-Settings!$B$4)</f>
       </c>
-      <c r="N7" s="0">
-        <f>MIN(7,C7+Settings!$B$4)</f>
-      </c>
-      <c r="O7" s="0">
+      <c r="P7" s="0">
+        <f>MIN(8,C7+Settings!$B$5)</f>
+      </c>
+      <c r="Q7" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C7,Monsters!$R:$R,"&gt;="&amp;C7)</f>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[DARK GOBLIN x2+4] [HOT LIPS x1+1] [GHOST STALKER x2+2] [TREANT x1+1] [TREANT x1+0, GHOST STALKER x1+2] [DARK GOBLIN x2+1, GHOST STALKER x1+1]</t>
         </is>
       </c>
-      <c r="Q7" s="3"/>
+      <c r="S7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="0">
@@ -914,21 +983,27 @@
       <c r="L8" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B8)</f>
       </c>
-      <c r="M8" s="0">
+      <c r="M8" s="7">
+        <f>MAX(L8,M7)</f>
+      </c>
+      <c r="N8" s="7">
+        <f>M8/L8</f>
+      </c>
+      <c r="O8" s="0">
         <f>MAX(1,C8-Settings!$B$4)</f>
       </c>
-      <c r="N8" s="0">
-        <f>MIN(7,C8+Settings!$B$4)</f>
-      </c>
-      <c r="O8" s="0">
+      <c r="P8" s="0">
+        <f>MIN(8,C8+Settings!$B$5)</f>
+      </c>
+      <c r="Q8" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C8,Monsters!$R:$R,"&gt;="&amp;C8)</f>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[WERE HARE x3+2] [ORK JR x1+2] [GREMLIN x2+2] [SKELETON x1+2] [GHOSTHOUND x1+2] [MERROW x2+2] [WOLF GOAT x1+2] [WERE HARE x2+1, ORK JR x1+1] [GREMLIN x1+1, ORK JR x1+2] [WOLF GOAT x1+0, ORK JR x1+1] [WOLF GOAT x1+0, GHOSTHOUND x1+1] [WERE HARE x1+0, MERROW x1+0, ORK JR x1+0] [GHOSTHOUND x1+1, SKELETON x1+1]</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">after Larapool</t>
         </is>
@@ -975,21 +1050,27 @@
       <c r="L9" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B9)</f>
       </c>
-      <c r="M9" s="0">
+      <c r="M9" s="7">
+        <f>MAX(L9,M8)</f>
+      </c>
+      <c r="N9" s="7">
+        <f>M9/L9</f>
+      </c>
+      <c r="O9" s="0">
         <f>MAX(1,C9-Settings!$B$4)</f>
       </c>
-      <c r="N9" s="0">
-        <f>MIN(7,C9+Settings!$B$4)</f>
-      </c>
-      <c r="O9" s="0">
+      <c r="P9" s="0">
+        <f>MIN(8,C9+Settings!$B$5)</f>
+      </c>
+      <c r="Q9" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C9,Monsters!$R:$R,"&gt;="&amp;C9)</f>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[BLOOD JELL x2+2] [MIMIC x1+0] [SCARE CROW x1+1] [WYVERN x1+0] [SKELEBAT x1+1] [BLOOD JELL x1+1, SCARE CROW x1+1] [WYVERN x1+0, SKELEBAT x2+0] [BLOOD JELL x1+1, SKELEBAT x1+1, SCARE CROW x1+0]</t>
         </is>
       </c>
-      <c r="Q9" s="3"/>
+      <c r="S9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="0">
@@ -1032,23 +1113,29 @@
       <c r="L10" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B10)</f>
       </c>
-      <c r="M10" s="0">
+      <c r="M10" s="7">
+        <f>MAX(L10,M9)</f>
+      </c>
+      <c r="N10" s="7">
+        <f>M10/L10</f>
+      </c>
+      <c r="O10" s="0">
         <f>MAX(1,C10-Settings!$B$4)</f>
       </c>
-      <c r="N10" s="0">
-        <f>MIN(7,C10+Settings!$B$4)</f>
-      </c>
-      <c r="O10" s="0">
+      <c r="P10" s="0">
+        <f>MIN(8,C10+Settings!$B$5)</f>
+      </c>
+      <c r="Q10" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C10,Monsters!$R:$R,"&gt;="&amp;C10)</f>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[CRYSHELL x1+2] [BLOOD JELL x2+4] [CATERPILLAR x2+3] [FISH MAN x1+3] [SCARE CROW x1+2] [WYVERN x1+1] [SCARE CROW x1+0, BLOOD JELL x1+1] [WYVERN x1+0, BLOOD JELL x1+1] [CRYSHELL x1+0, WYVERN x1+0] [FISH MAN x2+0, CRYSHELL x1+0] [FISH MAN x1+1, CRYSHELL x1+0, SCARE CROW x1+0]</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Normoon side</t>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normoon side; by vanilla numbers it is tougher than the T4 areas, the progression guard covers this</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1149,7 @@
         </is>
       </c>
       <c r="C11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="0">
         <v>4</v>
@@ -1093,21 +1180,27 @@
       <c r="L11" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B11)</f>
       </c>
-      <c r="M11" s="0">
+      <c r="M11" s="7">
+        <f>MAX(L11,M10)</f>
+      </c>
+      <c r="N11" s="7">
+        <f>M11/L11</f>
+      </c>
+      <c r="O11" s="0">
         <f>MAX(1,C11-Settings!$B$4)</f>
       </c>
-      <c r="N11" s="0">
-        <f>MIN(7,C11+Settings!$B$4)</f>
-      </c>
-      <c r="O11" s="0">
+      <c r="P11" s="0">
+        <f>MIN(8,C11+Settings!$B$5)</f>
+      </c>
+      <c r="Q11" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C11,Monsters!$R:$R,"&gt;="&amp;C11)</f>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[JACK-O'-LANTERN x1+3] [ARACHNOID x2+3] [LAMIA x1+1] [TEMPTRESS x2+2] [THUNDER JELL x3+3] [TERMANT x3+3] [TERMANT x2+1, ARACHNOID x1+2] [JACK-O'-LANTERN x1+1, TEMPTRESS x2+1] [THUNDER JELL x1+0, TERMANT x1+1, ARACHNOID x1+0, TEMPTRESS x1+0] [ORK x1+1] [ORK x1+0, JACK-O'-LANTERN x1+0]</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Zelse</t>
         </is>
@@ -1154,21 +1247,27 @@
       <c r="L12" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B12)</f>
       </c>
-      <c r="M12" s="0">
+      <c r="M12" s="7">
+        <f>MAX(L12,M11)</f>
+      </c>
+      <c r="N12" s="7">
+        <f>M12/L12</f>
+      </c>
+      <c r="O12" s="0">
         <f>MAX(1,C12-Settings!$B$4)</f>
       </c>
-      <c r="N12" s="0">
-        <f>MIN(7,C12+Settings!$B$4)</f>
-      </c>
-      <c r="O12" s="0">
+      <c r="P12" s="0">
+        <f>MIN(8,C12+Settings!$B$5)</f>
+      </c>
+      <c r="Q12" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C12,Monsters!$R:$R,"&gt;="&amp;C12)</f>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[MULTI OPTICS x2+2] [MIMIC x1+0] [CRAWLER x2+2] [SCORPION x2+2] [SKELEBAT x2+2] [BLOOD JELL x1+2] [CRAWLER x1+1, SCORPION x2+1] [MULTI OPTICS x1+1, CRAWLER x1+1] [MULTI OPTICS x2+1, BLOOD JELL x1+0] [SCARE CROW x1+0]</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Nepty</t>
         </is>
@@ -1215,21 +1314,27 @@
       <c r="L13" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B13)</f>
       </c>
-      <c r="M13" s="0">
+      <c r="M13" s="7">
+        <f>MAX(L13,M12)</f>
+      </c>
+      <c r="N13" s="7">
+        <f>M13/L13</f>
+      </c>
+      <c r="O13" s="0">
         <f>MAX(1,C13-Settings!$B$4)</f>
       </c>
-      <c r="N13" s="0">
-        <f>MIN(7,C13+Settings!$B$4)</f>
-      </c>
-      <c r="O13" s="0">
+      <c r="P13" s="0">
+        <f>MIN(8,C13+Settings!$B$5)</f>
+      </c>
+      <c r="Q13" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C13,Monsters!$R:$R,"&gt;="&amp;C13)</f>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[GRANGACH x1+2] [PIXIE x1+2] [THUNDER JELL x2+1] [TERMANT x2+1] [THUNDER JELL x1+0, GRANGACH x1+0, TERMANT x1+0] [PIXIE x1+0, THUNDER JELL x1+0, TERMANT x1+1]</t>
         </is>
       </c>
-      <c r="Q13" s="3"/>
+      <c r="S13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="0">
@@ -1241,7 +1346,7 @@
         </is>
       </c>
       <c r="C14" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="0">
         <v>4</v>
@@ -1272,21 +1377,27 @@
       <c r="L14" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B14)</f>
       </c>
-      <c r="M14" s="0">
+      <c r="M14" s="7">
+        <f>MAX(L14,M13)</f>
+      </c>
+      <c r="N14" s="7">
+        <f>M14/L14</f>
+      </c>
+      <c r="O14" s="0">
         <f>MAX(1,C14-Settings!$B$4)</f>
       </c>
-      <c r="N14" s="0">
-        <f>MIN(7,C14+Settings!$B$4)</f>
-      </c>
-      <c r="O14" s="0">
+      <c r="P14" s="0">
+        <f>MIN(8,C14+Settings!$B$5)</f>
+      </c>
+      <c r="Q14" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C14,Monsters!$R:$R,"&gt;="&amp;C14)</f>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[TERMANT x1+2] [GHOST x1+2] [SPRITE x2+1] [WILL-O'-WISP x1+2] [GHOST x1+0, WILL-O'-WISP x1+2] [SPRITE x1+1, WILL-O'-WISP x1+1] [TERMANT x1+1, GHOST x1+0] [WILL-O'-WISP x1+1, SPRITE x1+1]</t>
         </is>
       </c>
-      <c r="Q14" s="3"/>
+      <c r="S14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="0">
@@ -1298,7 +1409,7 @@
         </is>
       </c>
       <c r="C15" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="0">
         <v>3</v>
@@ -1329,21 +1440,27 @@
       <c r="L15" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B15)</f>
       </c>
-      <c r="M15" s="0">
+      <c r="M15" s="7">
+        <f>MAX(L15,M14)</f>
+      </c>
+      <c r="N15" s="7">
+        <f>M15/L15</f>
+      </c>
+      <c r="O15" s="0">
         <f>MAX(1,C15-Settings!$B$4)</f>
       </c>
-      <c r="N15" s="0">
-        <f>MIN(7,C15+Settings!$B$4)</f>
-      </c>
-      <c r="O15" s="0">
+      <c r="P15" s="0">
+        <f>MIN(8,C15+Settings!$B$5)</f>
+      </c>
+      <c r="Q15" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C15,Monsters!$R:$R,"&gt;="&amp;C15)</f>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[SANDMAN x2+1] [BLUE MAN x1+1] [BLUE MAN x3+1] [MAGMA FISH x2+3] [WERE CAT x1+2] [NIGHTMARE x1+4] [WERE CAT x1+1, NIGHTMARE x1+2] [SANDMAN x1+0, BLUE MAN x1+2] [NIGHTMARE x1+2, BLUE MAN x1+2] [BLUE MAN x1+0, MAGMA FISH x1+0] [MAGMA FISH x1+1, NIGHTMARE x1+1]</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Shamwood side</t>
         </is>
@@ -1359,7 +1476,7 @@
         </is>
       </c>
       <c r="C16" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="0">
         <v>3</v>
@@ -1390,21 +1507,27 @@
       <c r="L16" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B16)</f>
       </c>
-      <c r="M16" s="0">
+      <c r="M16" s="7">
+        <f>MAX(L16,M15)</f>
+      </c>
+      <c r="N16" s="7">
+        <f>M16/L16</f>
+      </c>
+      <c r="O16" s="0">
         <f>MAX(1,C16-Settings!$B$4)</f>
       </c>
-      <c r="N16" s="0">
-        <f>MIN(7,C16+Settings!$B$4)</f>
-      </c>
-      <c r="O16" s="0">
+      <c r="P16" s="0">
+        <f>MIN(8,C16+Settings!$B$5)</f>
+      </c>
+      <c r="Q16" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C16,Monsters!$R:$R,"&gt;="&amp;C16)</f>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[NIGHTMARE x2+2] [ROCKY x1+1] [RED WYVERN x1+0] [FLAMED MANE x1+0] [MAGMA FISH x2+2] [NIGHTMARE x1+1, MAGMA FISH x1+1] [RED WYVERN x1+0, MAGMA FISH x1+1] [FLAMED MANE x1+0, MAGMA FISH x1+1] [ROCKY x1+1, FLAMED MANE x1+0]</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
+      <c r="S16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Fargo</t>
         </is>
@@ -1420,7 +1543,7 @@
         </is>
       </c>
       <c r="C17" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="0">
         <v>3</v>
@@ -1451,21 +1574,27 @@
       <c r="L17" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B17)</f>
       </c>
-      <c r="M17" s="0">
+      <c r="M17" s="7">
+        <f>MAX(L17,M16)</f>
+      </c>
+      <c r="N17" s="7">
+        <f>M17/L17</f>
+      </c>
+      <c r="O17" s="0">
         <f>MAX(1,C17-Settings!$B$4)</f>
       </c>
-      <c r="N17" s="0">
-        <f>MIN(7,C17+Settings!$B$4)</f>
-      </c>
-      <c r="O17" s="0">
+      <c r="P17" s="0">
+        <f>MIN(8,C17+Settings!$B$5)</f>
+      </c>
+      <c r="Q17" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C17,Monsters!$R:$R,"&gt;="&amp;C17)</f>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[GLOOM WING x2+2] [OGRE x1+0] [ROCKY x2+2] [RED WYVERN x1+0] [RED ROSE KNIGHT x2+1] [WHITE ROSE KNIGHT x2+1] [OGRE x1+0, GLOOM WING x1+1] [RED ROSE KNIGHT x1+1, WHITE ROSE KNIGHT x1+1] [WINGED SUNFISH x2+1, GLOOM WING x1+1] [OGRE x1+0, ROCKY x1+1]</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr">
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Shilf; submaps 1-2 share one roster</t>
         </is>
@@ -1481,7 +1610,7 @@
         </is>
       </c>
       <c r="C18" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="0">
         <v>3</v>
@@ -1512,21 +1641,27 @@
       <c r="L18" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B18)</f>
       </c>
-      <c r="M18" s="0">
+      <c r="M18" s="7">
+        <f>MAX(L18,M17)</f>
+      </c>
+      <c r="N18" s="7">
+        <f>M18/L18</f>
+      </c>
+      <c r="O18" s="0">
         <f>MAX(1,C18-Settings!$B$4)</f>
       </c>
-      <c r="N18" s="0">
-        <f>MIN(7,C18+Settings!$B$4)</f>
-      </c>
-      <c r="O18" s="0">
+      <c r="P18" s="0">
+        <f>MIN(8,C18+Settings!$B$5)</f>
+      </c>
+      <c r="Q18" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C18,Monsters!$R:$R,"&gt;="&amp;C18)</f>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[RED ROSE KNIGHT x1+2] [WHITE ROSE KNIGHT x1+2] [RED ROSE KNIGHT x1+0, WHITE ROSE KNIGHT x1+1]</t>
         </is>
       </c>
-      <c r="Q18" s="3" t="inlineStr">
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Guilty, Beigis; submaps 1-6 share one roster</t>
         </is>
@@ -1542,7 +1677,7 @@
         </is>
       </c>
       <c r="C19" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" s="0">
         <v>5</v>
@@ -1573,21 +1708,27 @@
       <c r="L19" s="7">
         <f>AVERAGEIFS(Roster!$I:$I,Roster!$A:$A,$B19)</f>
       </c>
-      <c r="M19" s="0">
+      <c r="M19" s="7">
+        <f>MAX(L19,M18)</f>
+      </c>
+      <c r="N19" s="7">
+        <f>M19/L19</f>
+      </c>
+      <c r="O19" s="0">
         <f>MAX(1,C19-Settings!$B$4)</f>
       </c>
-      <c r="N19" s="0">
-        <f>MIN(7,C19+Settings!$B$4)</f>
-      </c>
-      <c r="O19" s="0">
+      <c r="P19" s="0">
+        <f>MIN(8,C19+Settings!$B$5)</f>
+      </c>
+      <c r="Q19" s="0">
         <f>COUNTIFS(Monsters!$Q:$Q,"&lt;="&amp;C19,Monsters!$R:$R,"&gt;="&amp;C19)</f>
       </c>
-      <c r="P19" s="3" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">[JUDGMENT x2+1] [PALE RIDER x2+1] [PIN HEAD x1+3] [SPRIGGAN x1+1] [JUDGMENT x1+0, PIN HEAD x1+1]</t>
         </is>
       </c>
-      <c r="Q19" s="3" t="inlineStr">
+      <c r="S19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">submaps 1-6 share one roster</t>
         </is>
@@ -5340,7 +5481,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stats are the ROM's (HP, ATK, DEF, AGI, EXP; Drop is the item drop slot). Native tier comes from the home area's tier on the Areas tab. Flying is the ROM's own flag (only Wyvern, Will-o'-Wisp and Pixie carry it), not a visual judgement. Power/Power tier use the Settings weights and thresholds. Q-R are the area tiers this monster may be placed in under the current spread; dangerous monsters are pinned at or above their native tier. S is where the six stat halfwords live in the ROM.</t>
+          <t xml:space="preserve">Stats are the ROM's (HP, ATK, DEF, AGI, EXP; Drop is the item drop slot). Native tier comes from the home area's tier on the Areas tab. Flying is the ROM's own flag (only Wyvern, Will-o'-Wisp and Pixie carry it), not a visual judgement. Power/Power tier use the Settings weights and thresholds. Q-R are the area tiers this monster may be placed in under the current spread (Q uses spread-up: a monster may go to areas up to that many tiers below it; R uses spread-down); dangerous monsters are pinned at or above their native tier. S is where the six stat halfwords live in the ROM. Bosses (ids 67+) are not listed: they are not part of this.</t>
         </is>
       </c>
     </row>
@@ -5487,22 +5628,22 @@
         </is>
       </c>
       <c r="M4" s="7">
-        <f>E4*(1+G4/Settings!$B$8)</f>
+        <f>E4*(1+G4/Settings!$B$9)</f>
       </c>
       <c r="N4" s="7">
-        <f>F4*(1+H4/Settings!$B$9)</f>
+        <f>F4*(1+H4/Settings!$B$10)</f>
       </c>
       <c r="O4" s="7">
         <f>ROUND(SQRT(M4*N4),1)</f>
       </c>
       <c r="P4" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O4)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O4)</f>
       </c>
       <c r="Q4" s="0">
-        <f>IF(AND(L4="Y",Settings!$B$7="Y"),D4,MAX(1,D4-Settings!$B$4))</f>
+        <f>IF(AND(L4="Y",Settings!$B$8="Y"),D4,MAX(1,D4-Settings!$B$5))</f>
       </c>
       <c r="R4" s="0">
-        <f>MIN(7,D4+Settings!$B$4)</f>
+        <f>MIN(8,D4+Settings!$B$4)</f>
       </c>
       <c r="S4" s="0" t="inlineStr">
         <is>
@@ -5556,22 +5697,22 @@
         </is>
       </c>
       <c r="M5" s="7">
-        <f>E5*(1+G5/Settings!$B$8)</f>
+        <f>E5*(1+G5/Settings!$B$9)</f>
       </c>
       <c r="N5" s="7">
-        <f>F5*(1+H5/Settings!$B$9)</f>
+        <f>F5*(1+H5/Settings!$B$10)</f>
       </c>
       <c r="O5" s="7">
         <f>ROUND(SQRT(M5*N5),1)</f>
       </c>
       <c r="P5" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O5)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O5)</f>
       </c>
       <c r="Q5" s="0">
-        <f>IF(AND(L5="Y",Settings!$B$7="Y"),D5,MAX(1,D5-Settings!$B$4))</f>
+        <f>IF(AND(L5="Y",Settings!$B$8="Y"),D5,MAX(1,D5-Settings!$B$5))</f>
       </c>
       <c r="R5" s="0">
-        <f>MIN(7,D5+Settings!$B$4)</f>
+        <f>MIN(8,D5+Settings!$B$4)</f>
       </c>
       <c r="S5" s="0" t="inlineStr">
         <is>
@@ -5625,22 +5766,22 @@
         </is>
       </c>
       <c r="M6" s="7">
-        <f>E6*(1+G6/Settings!$B$8)</f>
+        <f>E6*(1+G6/Settings!$B$9)</f>
       </c>
       <c r="N6" s="7">
-        <f>F6*(1+H6/Settings!$B$9)</f>
+        <f>F6*(1+H6/Settings!$B$10)</f>
       </c>
       <c r="O6" s="7">
         <f>ROUND(SQRT(M6*N6),1)</f>
       </c>
       <c r="P6" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O6)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O6)</f>
       </c>
       <c r="Q6" s="0">
-        <f>IF(AND(L6="Y",Settings!$B$7="Y"),D6,MAX(1,D6-Settings!$B$4))</f>
+        <f>IF(AND(L6="Y",Settings!$B$8="Y"),D6,MAX(1,D6-Settings!$B$5))</f>
       </c>
       <c r="R6" s="0">
-        <f>MIN(7,D6+Settings!$B$4)</f>
+        <f>MIN(8,D6+Settings!$B$4)</f>
       </c>
       <c r="S6" s="0" t="inlineStr">
         <is>
@@ -5694,22 +5835,22 @@
         </is>
       </c>
       <c r="M7" s="7">
-        <f>E7*(1+G7/Settings!$B$8)</f>
+        <f>E7*(1+G7/Settings!$B$9)</f>
       </c>
       <c r="N7" s="7">
-        <f>F7*(1+H7/Settings!$B$9)</f>
+        <f>F7*(1+H7/Settings!$B$10)</f>
       </c>
       <c r="O7" s="7">
         <f>ROUND(SQRT(M7*N7),1)</f>
       </c>
       <c r="P7" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O7)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O7)</f>
       </c>
       <c r="Q7" s="0">
-        <f>IF(AND(L7="Y",Settings!$B$7="Y"),D7,MAX(1,D7-Settings!$B$4))</f>
+        <f>IF(AND(L7="Y",Settings!$B$8="Y"),D7,MAX(1,D7-Settings!$B$5))</f>
       </c>
       <c r="R7" s="0">
-        <f>MIN(7,D7+Settings!$B$4)</f>
+        <f>MIN(8,D7+Settings!$B$4)</f>
       </c>
       <c r="S7" s="0" t="inlineStr">
         <is>
@@ -5763,22 +5904,22 @@
         </is>
       </c>
       <c r="M8" s="7">
-        <f>E8*(1+G8/Settings!$B$8)</f>
+        <f>E8*(1+G8/Settings!$B$9)</f>
       </c>
       <c r="N8" s="7">
-        <f>F8*(1+H8/Settings!$B$9)</f>
+        <f>F8*(1+H8/Settings!$B$10)</f>
       </c>
       <c r="O8" s="7">
         <f>ROUND(SQRT(M8*N8),1)</f>
       </c>
       <c r="P8" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O8)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O8)</f>
       </c>
       <c r="Q8" s="0">
-        <f>IF(AND(L8="Y",Settings!$B$7="Y"),D8,MAX(1,D8-Settings!$B$4))</f>
+        <f>IF(AND(L8="Y",Settings!$B$8="Y"),D8,MAX(1,D8-Settings!$B$5))</f>
       </c>
       <c r="R8" s="0">
-        <f>MIN(7,D8+Settings!$B$4)</f>
+        <f>MIN(8,D8+Settings!$B$4)</f>
       </c>
       <c r="S8" s="0" t="inlineStr">
         <is>
@@ -5832,22 +5973,22 @@
         </is>
       </c>
       <c r="M9" s="7">
-        <f>E9*(1+G9/Settings!$B$8)</f>
+        <f>E9*(1+G9/Settings!$B$9)</f>
       </c>
       <c r="N9" s="7">
-        <f>F9*(1+H9/Settings!$B$9)</f>
+        <f>F9*(1+H9/Settings!$B$10)</f>
       </c>
       <c r="O9" s="7">
         <f>ROUND(SQRT(M9*N9),1)</f>
       </c>
       <c r="P9" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O9)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O9)</f>
       </c>
       <c r="Q9" s="0">
-        <f>IF(AND(L9="Y",Settings!$B$7="Y"),D9,MAX(1,D9-Settings!$B$4))</f>
+        <f>IF(AND(L9="Y",Settings!$B$8="Y"),D9,MAX(1,D9-Settings!$B$5))</f>
       </c>
       <c r="R9" s="0">
-        <f>MIN(7,D9+Settings!$B$4)</f>
+        <f>MIN(8,D9+Settings!$B$4)</f>
       </c>
       <c r="S9" s="0" t="inlineStr">
         <is>
@@ -5901,22 +6042,22 @@
         </is>
       </c>
       <c r="M10" s="7">
-        <f>E10*(1+G10/Settings!$B$8)</f>
+        <f>E10*(1+G10/Settings!$B$9)</f>
       </c>
       <c r="N10" s="7">
-        <f>F10*(1+H10/Settings!$B$9)</f>
+        <f>F10*(1+H10/Settings!$B$10)</f>
       </c>
       <c r="O10" s="7">
         <f>ROUND(SQRT(M10*N10),1)</f>
       </c>
       <c r="P10" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O10)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O10)</f>
       </c>
       <c r="Q10" s="0">
-        <f>IF(AND(L10="Y",Settings!$B$7="Y"),D10,MAX(1,D10-Settings!$B$4))</f>
+        <f>IF(AND(L10="Y",Settings!$B$8="Y"),D10,MAX(1,D10-Settings!$B$5))</f>
       </c>
       <c r="R10" s="0">
-        <f>MIN(7,D10+Settings!$B$4)</f>
+        <f>MIN(8,D10+Settings!$B$4)</f>
       </c>
       <c r="S10" s="0" t="inlineStr">
         <is>
@@ -5970,22 +6111,22 @@
         </is>
       </c>
       <c r="M11" s="7">
-        <f>E11*(1+G11/Settings!$B$8)</f>
+        <f>E11*(1+G11/Settings!$B$9)</f>
       </c>
       <c r="N11" s="7">
-        <f>F11*(1+H11/Settings!$B$9)</f>
+        <f>F11*(1+H11/Settings!$B$10)</f>
       </c>
       <c r="O11" s="7">
         <f>ROUND(SQRT(M11*N11),1)</f>
       </c>
       <c r="P11" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O11)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O11)</f>
       </c>
       <c r="Q11" s="0">
-        <f>IF(AND(L11="Y",Settings!$B$7="Y"),D11,MAX(1,D11-Settings!$B$4))</f>
+        <f>IF(AND(L11="Y",Settings!$B$8="Y"),D11,MAX(1,D11-Settings!$B$5))</f>
       </c>
       <c r="R11" s="0">
-        <f>MIN(7,D11+Settings!$B$4)</f>
+        <f>MIN(8,D11+Settings!$B$4)</f>
       </c>
       <c r="S11" s="0" t="inlineStr">
         <is>
@@ -6039,22 +6180,22 @@
         </is>
       </c>
       <c r="M12" s="7">
-        <f>E12*(1+G12/Settings!$B$8)</f>
+        <f>E12*(1+G12/Settings!$B$9)</f>
       </c>
       <c r="N12" s="7">
-        <f>F12*(1+H12/Settings!$B$9)</f>
+        <f>F12*(1+H12/Settings!$B$10)</f>
       </c>
       <c r="O12" s="7">
         <f>ROUND(SQRT(M12*N12),1)</f>
       </c>
       <c r="P12" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O12)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O12)</f>
       </c>
       <c r="Q12" s="0">
-        <f>IF(AND(L12="Y",Settings!$B$7="Y"),D12,MAX(1,D12-Settings!$B$4))</f>
+        <f>IF(AND(L12="Y",Settings!$B$8="Y"),D12,MAX(1,D12-Settings!$B$5))</f>
       </c>
       <c r="R12" s="0">
-        <f>MIN(7,D12+Settings!$B$4)</f>
+        <f>MIN(8,D12+Settings!$B$4)</f>
       </c>
       <c r="S12" s="0" t="inlineStr">
         <is>
@@ -6108,22 +6249,22 @@
         </is>
       </c>
       <c r="M13" s="7">
-        <f>E13*(1+G13/Settings!$B$8)</f>
+        <f>E13*(1+G13/Settings!$B$9)</f>
       </c>
       <c r="N13" s="7">
-        <f>F13*(1+H13/Settings!$B$9)</f>
+        <f>F13*(1+H13/Settings!$B$10)</f>
       </c>
       <c r="O13" s="7">
         <f>ROUND(SQRT(M13*N13),1)</f>
       </c>
       <c r="P13" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O13)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O13)</f>
       </c>
       <c r="Q13" s="0">
-        <f>IF(AND(L13="Y",Settings!$B$7="Y"),D13,MAX(1,D13-Settings!$B$4))</f>
+        <f>IF(AND(L13="Y",Settings!$B$8="Y"),D13,MAX(1,D13-Settings!$B$5))</f>
       </c>
       <c r="R13" s="0">
-        <f>MIN(7,D13+Settings!$B$4)</f>
+        <f>MIN(8,D13+Settings!$B$4)</f>
       </c>
       <c r="S13" s="0" t="inlineStr">
         <is>
@@ -6177,22 +6318,22 @@
         </is>
       </c>
       <c r="M14" s="7">
-        <f>E14*(1+G14/Settings!$B$8)</f>
+        <f>E14*(1+G14/Settings!$B$9)</f>
       </c>
       <c r="N14" s="7">
-        <f>F14*(1+H14/Settings!$B$9)</f>
+        <f>F14*(1+H14/Settings!$B$10)</f>
       </c>
       <c r="O14" s="7">
         <f>ROUND(SQRT(M14*N14),1)</f>
       </c>
       <c r="P14" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O14)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O14)</f>
       </c>
       <c r="Q14" s="0">
-        <f>IF(AND(L14="Y",Settings!$B$7="Y"),D14,MAX(1,D14-Settings!$B$4))</f>
+        <f>IF(AND(L14="Y",Settings!$B$8="Y"),D14,MAX(1,D14-Settings!$B$5))</f>
       </c>
       <c r="R14" s="0">
-        <f>MIN(7,D14+Settings!$B$4)</f>
+        <f>MIN(8,D14+Settings!$B$4)</f>
       </c>
       <c r="S14" s="0" t="inlineStr">
         <is>
@@ -6246,22 +6387,22 @@
         </is>
       </c>
       <c r="M15" s="7">
-        <f>E15*(1+G15/Settings!$B$8)</f>
+        <f>E15*(1+G15/Settings!$B$9)</f>
       </c>
       <c r="N15" s="7">
-        <f>F15*(1+H15/Settings!$B$9)</f>
+        <f>F15*(1+H15/Settings!$B$10)</f>
       </c>
       <c r="O15" s="7">
         <f>ROUND(SQRT(M15*N15),1)</f>
       </c>
       <c r="P15" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O15)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O15)</f>
       </c>
       <c r="Q15" s="0">
-        <f>IF(AND(L15="Y",Settings!$B$7="Y"),D15,MAX(1,D15-Settings!$B$4))</f>
+        <f>IF(AND(L15="Y",Settings!$B$8="Y"),D15,MAX(1,D15-Settings!$B$5))</f>
       </c>
       <c r="R15" s="0">
-        <f>MIN(7,D15+Settings!$B$4)</f>
+        <f>MIN(8,D15+Settings!$B$4)</f>
       </c>
       <c r="S15" s="0" t="inlineStr">
         <is>
@@ -6315,22 +6456,22 @@
         </is>
       </c>
       <c r="M16" s="7">
-        <f>E16*(1+G16/Settings!$B$8)</f>
+        <f>E16*(1+G16/Settings!$B$9)</f>
       </c>
       <c r="N16" s="7">
-        <f>F16*(1+H16/Settings!$B$9)</f>
+        <f>F16*(1+H16/Settings!$B$10)</f>
       </c>
       <c r="O16" s="7">
         <f>ROUND(SQRT(M16*N16),1)</f>
       </c>
       <c r="P16" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O16)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O16)</f>
       </c>
       <c r="Q16" s="0">
-        <f>IF(AND(L16="Y",Settings!$B$7="Y"),D16,MAX(1,D16-Settings!$B$4))</f>
+        <f>IF(AND(L16="Y",Settings!$B$8="Y"),D16,MAX(1,D16-Settings!$B$5))</f>
       </c>
       <c r="R16" s="0">
-        <f>MIN(7,D16+Settings!$B$4)</f>
+        <f>MIN(8,D16+Settings!$B$4)</f>
       </c>
       <c r="S16" s="0" t="inlineStr">
         <is>
@@ -6384,22 +6525,22 @@
         </is>
       </c>
       <c r="M17" s="7">
-        <f>E17*(1+G17/Settings!$B$8)</f>
+        <f>E17*(1+G17/Settings!$B$9)</f>
       </c>
       <c r="N17" s="7">
-        <f>F17*(1+H17/Settings!$B$9)</f>
+        <f>F17*(1+H17/Settings!$B$10)</f>
       </c>
       <c r="O17" s="7">
         <f>ROUND(SQRT(M17*N17),1)</f>
       </c>
       <c r="P17" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O17)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O17)</f>
       </c>
       <c r="Q17" s="0">
-        <f>IF(AND(L17="Y",Settings!$B$7="Y"),D17,MAX(1,D17-Settings!$B$4))</f>
+        <f>IF(AND(L17="Y",Settings!$B$8="Y"),D17,MAX(1,D17-Settings!$B$5))</f>
       </c>
       <c r="R17" s="0">
-        <f>MIN(7,D17+Settings!$B$4)</f>
+        <f>MIN(8,D17+Settings!$B$4)</f>
       </c>
       <c r="S17" s="0" t="inlineStr">
         <is>
@@ -6453,22 +6594,22 @@
         </is>
       </c>
       <c r="M18" s="7">
-        <f>E18*(1+G18/Settings!$B$8)</f>
+        <f>E18*(1+G18/Settings!$B$9)</f>
       </c>
       <c r="N18" s="7">
-        <f>F18*(1+H18/Settings!$B$9)</f>
+        <f>F18*(1+H18/Settings!$B$10)</f>
       </c>
       <c r="O18" s="7">
         <f>ROUND(SQRT(M18*N18),1)</f>
       </c>
       <c r="P18" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O18)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O18)</f>
       </c>
       <c r="Q18" s="0">
-        <f>IF(AND(L18="Y",Settings!$B$7="Y"),D18,MAX(1,D18-Settings!$B$4))</f>
+        <f>IF(AND(L18="Y",Settings!$B$8="Y"),D18,MAX(1,D18-Settings!$B$5))</f>
       </c>
       <c r="R18" s="0">
-        <f>MIN(7,D18+Settings!$B$4)</f>
+        <f>MIN(8,D18+Settings!$B$4)</f>
       </c>
       <c r="S18" s="0" t="inlineStr">
         <is>
@@ -6522,22 +6663,22 @@
         </is>
       </c>
       <c r="M19" s="7">
-        <f>E19*(1+G19/Settings!$B$8)</f>
+        <f>E19*(1+G19/Settings!$B$9)</f>
       </c>
       <c r="N19" s="7">
-        <f>F19*(1+H19/Settings!$B$9)</f>
+        <f>F19*(1+H19/Settings!$B$10)</f>
       </c>
       <c r="O19" s="7">
         <f>ROUND(SQRT(M19*N19),1)</f>
       </c>
       <c r="P19" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O19)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O19)</f>
       </c>
       <c r="Q19" s="0">
-        <f>IF(AND(L19="Y",Settings!$B$7="Y"),D19,MAX(1,D19-Settings!$B$4))</f>
+        <f>IF(AND(L19="Y",Settings!$B$8="Y"),D19,MAX(1,D19-Settings!$B$5))</f>
       </c>
       <c r="R19" s="0">
-        <f>MIN(7,D19+Settings!$B$4)</f>
+        <f>MIN(8,D19+Settings!$B$4)</f>
       </c>
       <c r="S19" s="0" t="inlineStr">
         <is>
@@ -6591,22 +6732,22 @@
         </is>
       </c>
       <c r="M20" s="7">
-        <f>E20*(1+G20/Settings!$B$8)</f>
+        <f>E20*(1+G20/Settings!$B$9)</f>
       </c>
       <c r="N20" s="7">
-        <f>F20*(1+H20/Settings!$B$9)</f>
+        <f>F20*(1+H20/Settings!$B$10)</f>
       </c>
       <c r="O20" s="7">
         <f>ROUND(SQRT(M20*N20),1)</f>
       </c>
       <c r="P20" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O20)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O20)</f>
       </c>
       <c r="Q20" s="0">
-        <f>IF(AND(L20="Y",Settings!$B$7="Y"),D20,MAX(1,D20-Settings!$B$4))</f>
+        <f>IF(AND(L20="Y",Settings!$B$8="Y"),D20,MAX(1,D20-Settings!$B$5))</f>
       </c>
       <c r="R20" s="0">
-        <f>MIN(7,D20+Settings!$B$4)</f>
+        <f>MIN(8,D20+Settings!$B$4)</f>
       </c>
       <c r="S20" s="0" t="inlineStr">
         <is>
@@ -6660,22 +6801,22 @@
         </is>
       </c>
       <c r="M21" s="7">
-        <f>E21*(1+G21/Settings!$B$8)</f>
+        <f>E21*(1+G21/Settings!$B$9)</f>
       </c>
       <c r="N21" s="7">
-        <f>F21*(1+H21/Settings!$B$9)</f>
+        <f>F21*(1+H21/Settings!$B$10)</f>
       </c>
       <c r="O21" s="7">
         <f>ROUND(SQRT(M21*N21),1)</f>
       </c>
       <c r="P21" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O21)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O21)</f>
       </c>
       <c r="Q21" s="0">
-        <f>IF(AND(L21="Y",Settings!$B$7="Y"),D21,MAX(1,D21-Settings!$B$4))</f>
+        <f>IF(AND(L21="Y",Settings!$B$8="Y"),D21,MAX(1,D21-Settings!$B$5))</f>
       </c>
       <c r="R21" s="0">
-        <f>MIN(7,D21+Settings!$B$4)</f>
+        <f>MIN(8,D21+Settings!$B$4)</f>
       </c>
       <c r="S21" s="0" t="inlineStr">
         <is>
@@ -6729,22 +6870,22 @@
         </is>
       </c>
       <c r="M22" s="7">
-        <f>E22*(1+G22/Settings!$B$8)</f>
+        <f>E22*(1+G22/Settings!$B$9)</f>
       </c>
       <c r="N22" s="7">
-        <f>F22*(1+H22/Settings!$B$9)</f>
+        <f>F22*(1+H22/Settings!$B$10)</f>
       </c>
       <c r="O22" s="7">
         <f>ROUND(SQRT(M22*N22),1)</f>
       </c>
       <c r="P22" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O22)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O22)</f>
       </c>
       <c r="Q22" s="0">
-        <f>IF(AND(L22="Y",Settings!$B$7="Y"),D22,MAX(1,D22-Settings!$B$4))</f>
+        <f>IF(AND(L22="Y",Settings!$B$8="Y"),D22,MAX(1,D22-Settings!$B$5))</f>
       </c>
       <c r="R22" s="0">
-        <f>MIN(7,D22+Settings!$B$4)</f>
+        <f>MIN(8,D22+Settings!$B$4)</f>
       </c>
       <c r="S22" s="0" t="inlineStr">
         <is>
@@ -6798,22 +6939,22 @@
         </is>
       </c>
       <c r="M23" s="7">
-        <f>E23*(1+G23/Settings!$B$8)</f>
+        <f>E23*(1+G23/Settings!$B$9)</f>
       </c>
       <c r="N23" s="7">
-        <f>F23*(1+H23/Settings!$B$9)</f>
+        <f>F23*(1+H23/Settings!$B$10)</f>
       </c>
       <c r="O23" s="7">
         <f>ROUND(SQRT(M23*N23),1)</f>
       </c>
       <c r="P23" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O23)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O23)</f>
       </c>
       <c r="Q23" s="0">
-        <f>IF(AND(L23="Y",Settings!$B$7="Y"),D23,MAX(1,D23-Settings!$B$4))</f>
+        <f>IF(AND(L23="Y",Settings!$B$8="Y"),D23,MAX(1,D23-Settings!$B$5))</f>
       </c>
       <c r="R23" s="0">
-        <f>MIN(7,D23+Settings!$B$4)</f>
+        <f>MIN(8,D23+Settings!$B$4)</f>
       </c>
       <c r="S23" s="0" t="inlineStr">
         <is>
@@ -6867,22 +7008,22 @@
         </is>
       </c>
       <c r="M24" s="7">
-        <f>E24*(1+G24/Settings!$B$8)</f>
+        <f>E24*(1+G24/Settings!$B$9)</f>
       </c>
       <c r="N24" s="7">
-        <f>F24*(1+H24/Settings!$B$9)</f>
+        <f>F24*(1+H24/Settings!$B$10)</f>
       </c>
       <c r="O24" s="7">
         <f>ROUND(SQRT(M24*N24),1)</f>
       </c>
       <c r="P24" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O24)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O24)</f>
       </c>
       <c r="Q24" s="0">
-        <f>IF(AND(L24="Y",Settings!$B$7="Y"),D24,MAX(1,D24-Settings!$B$4))</f>
+        <f>IF(AND(L24="Y",Settings!$B$8="Y"),D24,MAX(1,D24-Settings!$B$5))</f>
       </c>
       <c r="R24" s="0">
-        <f>MIN(7,D24+Settings!$B$4)</f>
+        <f>MIN(8,D24+Settings!$B$4)</f>
       </c>
       <c r="S24" s="0" t="inlineStr">
         <is>
@@ -6936,22 +7077,22 @@
         </is>
       </c>
       <c r="M25" s="7">
-        <f>E25*(1+G25/Settings!$B$8)</f>
+        <f>E25*(1+G25/Settings!$B$9)</f>
       </c>
       <c r="N25" s="7">
-        <f>F25*(1+H25/Settings!$B$9)</f>
+        <f>F25*(1+H25/Settings!$B$10)</f>
       </c>
       <c r="O25" s="7">
         <f>ROUND(SQRT(M25*N25),1)</f>
       </c>
       <c r="P25" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O25)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O25)</f>
       </c>
       <c r="Q25" s="0">
-        <f>IF(AND(L25="Y",Settings!$B$7="Y"),D25,MAX(1,D25-Settings!$B$4))</f>
+        <f>IF(AND(L25="Y",Settings!$B$8="Y"),D25,MAX(1,D25-Settings!$B$5))</f>
       </c>
       <c r="R25" s="0">
-        <f>MIN(7,D25+Settings!$B$4)</f>
+        <f>MIN(8,D25+Settings!$B$4)</f>
       </c>
       <c r="S25" s="0" t="inlineStr">
         <is>
@@ -7005,22 +7146,22 @@
         </is>
       </c>
       <c r="M26" s="7">
-        <f>E26*(1+G26/Settings!$B$8)</f>
+        <f>E26*(1+G26/Settings!$B$9)</f>
       </c>
       <c r="N26" s="7">
-        <f>F26*(1+H26/Settings!$B$9)</f>
+        <f>F26*(1+H26/Settings!$B$10)</f>
       </c>
       <c r="O26" s="7">
         <f>ROUND(SQRT(M26*N26),1)</f>
       </c>
       <c r="P26" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O26)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O26)</f>
       </c>
       <c r="Q26" s="0">
-        <f>IF(AND(L26="Y",Settings!$B$7="Y"),D26,MAX(1,D26-Settings!$B$4))</f>
+        <f>IF(AND(L26="Y",Settings!$B$8="Y"),D26,MAX(1,D26-Settings!$B$5))</f>
       </c>
       <c r="R26" s="0">
-        <f>MIN(7,D26+Settings!$B$4)</f>
+        <f>MIN(8,D26+Settings!$B$4)</f>
       </c>
       <c r="S26" s="0" t="inlineStr">
         <is>
@@ -7074,22 +7215,22 @@
         </is>
       </c>
       <c r="M27" s="7">
-        <f>E27*(1+G27/Settings!$B$8)</f>
+        <f>E27*(1+G27/Settings!$B$9)</f>
       </c>
       <c r="N27" s="7">
-        <f>F27*(1+H27/Settings!$B$9)</f>
+        <f>F27*(1+H27/Settings!$B$10)</f>
       </c>
       <c r="O27" s="7">
         <f>ROUND(SQRT(M27*N27),1)</f>
       </c>
       <c r="P27" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O27)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O27)</f>
       </c>
       <c r="Q27" s="0">
-        <f>IF(AND(L27="Y",Settings!$B$7="Y"),D27,MAX(1,D27-Settings!$B$4))</f>
+        <f>IF(AND(L27="Y",Settings!$B$8="Y"),D27,MAX(1,D27-Settings!$B$5))</f>
       </c>
       <c r="R27" s="0">
-        <f>MIN(7,D27+Settings!$B$4)</f>
+        <f>MIN(8,D27+Settings!$B$4)</f>
       </c>
       <c r="S27" s="0" t="inlineStr">
         <is>
@@ -7143,22 +7284,22 @@
         </is>
       </c>
       <c r="M28" s="7">
-        <f>E28*(1+G28/Settings!$B$8)</f>
+        <f>E28*(1+G28/Settings!$B$9)</f>
       </c>
       <c r="N28" s="7">
-        <f>F28*(1+H28/Settings!$B$9)</f>
+        <f>F28*(1+H28/Settings!$B$10)</f>
       </c>
       <c r="O28" s="7">
         <f>ROUND(SQRT(M28*N28),1)</f>
       </c>
       <c r="P28" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O28)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O28)</f>
       </c>
       <c r="Q28" s="0">
-        <f>IF(AND(L28="Y",Settings!$B$7="Y"),D28,MAX(1,D28-Settings!$B$4))</f>
+        <f>IF(AND(L28="Y",Settings!$B$8="Y"),D28,MAX(1,D28-Settings!$B$5))</f>
       </c>
       <c r="R28" s="0">
-        <f>MIN(7,D28+Settings!$B$4)</f>
+        <f>MIN(8,D28+Settings!$B$4)</f>
       </c>
       <c r="S28" s="0" t="inlineStr">
         <is>
@@ -7212,22 +7353,22 @@
         </is>
       </c>
       <c r="M29" s="7">
-        <f>E29*(1+G29/Settings!$B$8)</f>
+        <f>E29*(1+G29/Settings!$B$9)</f>
       </c>
       <c r="N29" s="7">
-        <f>F29*(1+H29/Settings!$B$9)</f>
+        <f>F29*(1+H29/Settings!$B$10)</f>
       </c>
       <c r="O29" s="7">
         <f>ROUND(SQRT(M29*N29),1)</f>
       </c>
       <c r="P29" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O29)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O29)</f>
       </c>
       <c r="Q29" s="0">
-        <f>IF(AND(L29="Y",Settings!$B$7="Y"),D29,MAX(1,D29-Settings!$B$4))</f>
+        <f>IF(AND(L29="Y",Settings!$B$8="Y"),D29,MAX(1,D29-Settings!$B$5))</f>
       </c>
       <c r="R29" s="0">
-        <f>MIN(7,D29+Settings!$B$4)</f>
+        <f>MIN(8,D29+Settings!$B$4)</f>
       </c>
       <c r="S29" s="0" t="inlineStr">
         <is>
@@ -7281,22 +7422,22 @@
         </is>
       </c>
       <c r="M30" s="7">
-        <f>E30*(1+G30/Settings!$B$8)</f>
+        <f>E30*(1+G30/Settings!$B$9)</f>
       </c>
       <c r="N30" s="7">
-        <f>F30*(1+H30/Settings!$B$9)</f>
+        <f>F30*(1+H30/Settings!$B$10)</f>
       </c>
       <c r="O30" s="7">
         <f>ROUND(SQRT(M30*N30),1)</f>
       </c>
       <c r="P30" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O30)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O30)</f>
       </c>
       <c r="Q30" s="0">
-        <f>IF(AND(L30="Y",Settings!$B$7="Y"),D30,MAX(1,D30-Settings!$B$4))</f>
+        <f>IF(AND(L30="Y",Settings!$B$8="Y"),D30,MAX(1,D30-Settings!$B$5))</f>
       </c>
       <c r="R30" s="0">
-        <f>MIN(7,D30+Settings!$B$4)</f>
+        <f>MIN(8,D30+Settings!$B$4)</f>
       </c>
       <c r="S30" s="0" t="inlineStr">
         <is>
@@ -7350,22 +7491,22 @@
         </is>
       </c>
       <c r="M31" s="7">
-        <f>E31*(1+G31/Settings!$B$8)</f>
+        <f>E31*(1+G31/Settings!$B$9)</f>
       </c>
       <c r="N31" s="7">
-        <f>F31*(1+H31/Settings!$B$9)</f>
+        <f>F31*(1+H31/Settings!$B$10)</f>
       </c>
       <c r="O31" s="7">
         <f>ROUND(SQRT(M31*N31),1)</f>
       </c>
       <c r="P31" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O31)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O31)</f>
       </c>
       <c r="Q31" s="0">
-        <f>IF(AND(L31="Y",Settings!$B$7="Y"),D31,MAX(1,D31-Settings!$B$4))</f>
+        <f>IF(AND(L31="Y",Settings!$B$8="Y"),D31,MAX(1,D31-Settings!$B$5))</f>
       </c>
       <c r="R31" s="0">
-        <f>MIN(7,D31+Settings!$B$4)</f>
+        <f>MIN(8,D31+Settings!$B$4)</f>
       </c>
       <c r="S31" s="0" t="inlineStr">
         <is>
@@ -7419,22 +7560,22 @@
         </is>
       </c>
       <c r="M32" s="7">
-        <f>E32*(1+G32/Settings!$B$8)</f>
+        <f>E32*(1+G32/Settings!$B$9)</f>
       </c>
       <c r="N32" s="7">
-        <f>F32*(1+H32/Settings!$B$9)</f>
+        <f>F32*(1+H32/Settings!$B$10)</f>
       </c>
       <c r="O32" s="7">
         <f>ROUND(SQRT(M32*N32),1)</f>
       </c>
       <c r="P32" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O32)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O32)</f>
       </c>
       <c r="Q32" s="0">
-        <f>IF(AND(L32="Y",Settings!$B$7="Y"),D32,MAX(1,D32-Settings!$B$4))</f>
+        <f>IF(AND(L32="Y",Settings!$B$8="Y"),D32,MAX(1,D32-Settings!$B$5))</f>
       </c>
       <c r="R32" s="0">
-        <f>MIN(7,D32+Settings!$B$4)</f>
+        <f>MIN(8,D32+Settings!$B$4)</f>
       </c>
       <c r="S32" s="0" t="inlineStr">
         <is>
@@ -7488,22 +7629,22 @@
         </is>
       </c>
       <c r="M33" s="7">
-        <f>E33*(1+G33/Settings!$B$8)</f>
+        <f>E33*(1+G33/Settings!$B$9)</f>
       </c>
       <c r="N33" s="7">
-        <f>F33*(1+H33/Settings!$B$9)</f>
+        <f>F33*(1+H33/Settings!$B$10)</f>
       </c>
       <c r="O33" s="7">
         <f>ROUND(SQRT(M33*N33),1)</f>
       </c>
       <c r="P33" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O33)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O33)</f>
       </c>
       <c r="Q33" s="0">
-        <f>IF(AND(L33="Y",Settings!$B$7="Y"),D33,MAX(1,D33-Settings!$B$4))</f>
+        <f>IF(AND(L33="Y",Settings!$B$8="Y"),D33,MAX(1,D33-Settings!$B$5))</f>
       </c>
       <c r="R33" s="0">
-        <f>MIN(7,D33+Settings!$B$4)</f>
+        <f>MIN(8,D33+Settings!$B$4)</f>
       </c>
       <c r="S33" s="0" t="inlineStr">
         <is>
@@ -7557,22 +7698,22 @@
         </is>
       </c>
       <c r="M34" s="7">
-        <f>E34*(1+G34/Settings!$B$8)</f>
+        <f>E34*(1+G34/Settings!$B$9)</f>
       </c>
       <c r="N34" s="7">
-        <f>F34*(1+H34/Settings!$B$9)</f>
+        <f>F34*(1+H34/Settings!$B$10)</f>
       </c>
       <c r="O34" s="7">
         <f>ROUND(SQRT(M34*N34),1)</f>
       </c>
       <c r="P34" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O34)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O34)</f>
       </c>
       <c r="Q34" s="0">
-        <f>IF(AND(L34="Y",Settings!$B$7="Y"),D34,MAX(1,D34-Settings!$B$4))</f>
+        <f>IF(AND(L34="Y",Settings!$B$8="Y"),D34,MAX(1,D34-Settings!$B$5))</f>
       </c>
       <c r="R34" s="0">
-        <f>MIN(7,D34+Settings!$B$4)</f>
+        <f>MIN(8,D34+Settings!$B$4)</f>
       </c>
       <c r="S34" s="0" t="inlineStr">
         <is>
@@ -7626,22 +7767,22 @@
         </is>
       </c>
       <c r="M35" s="7">
-        <f>E35*(1+G35/Settings!$B$8)</f>
+        <f>E35*(1+G35/Settings!$B$9)</f>
       </c>
       <c r="N35" s="7">
-        <f>F35*(1+H35/Settings!$B$9)</f>
+        <f>F35*(1+H35/Settings!$B$10)</f>
       </c>
       <c r="O35" s="7">
         <f>ROUND(SQRT(M35*N35),1)</f>
       </c>
       <c r="P35" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O35)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O35)</f>
       </c>
       <c r="Q35" s="0">
-        <f>IF(AND(L35="Y",Settings!$B$7="Y"),D35,MAX(1,D35-Settings!$B$4))</f>
+        <f>IF(AND(L35="Y",Settings!$B$8="Y"),D35,MAX(1,D35-Settings!$B$5))</f>
       </c>
       <c r="R35" s="0">
-        <f>MIN(7,D35+Settings!$B$4)</f>
+        <f>MIN(8,D35+Settings!$B$4)</f>
       </c>
       <c r="S35" s="0" t="inlineStr">
         <is>
@@ -7695,22 +7836,22 @@
         </is>
       </c>
       <c r="M36" s="7">
-        <f>E36*(1+G36/Settings!$B$8)</f>
+        <f>E36*(1+G36/Settings!$B$9)</f>
       </c>
       <c r="N36" s="7">
-        <f>F36*(1+H36/Settings!$B$9)</f>
+        <f>F36*(1+H36/Settings!$B$10)</f>
       </c>
       <c r="O36" s="7">
         <f>ROUND(SQRT(M36*N36),1)</f>
       </c>
       <c r="P36" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O36)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O36)</f>
       </c>
       <c r="Q36" s="0">
-        <f>IF(AND(L36="Y",Settings!$B$7="Y"),D36,MAX(1,D36-Settings!$B$4))</f>
+        <f>IF(AND(L36="Y",Settings!$B$8="Y"),D36,MAX(1,D36-Settings!$B$5))</f>
       </c>
       <c r="R36" s="0">
-        <f>MIN(7,D36+Settings!$B$4)</f>
+        <f>MIN(8,D36+Settings!$B$4)</f>
       </c>
       <c r="S36" s="0" t="inlineStr">
         <is>
@@ -7764,22 +7905,22 @@
         </is>
       </c>
       <c r="M37" s="7">
-        <f>E37*(1+G37/Settings!$B$8)</f>
+        <f>E37*(1+G37/Settings!$B$9)</f>
       </c>
       <c r="N37" s="7">
-        <f>F37*(1+H37/Settings!$B$9)</f>
+        <f>F37*(1+H37/Settings!$B$10)</f>
       </c>
       <c r="O37" s="7">
         <f>ROUND(SQRT(M37*N37),1)</f>
       </c>
       <c r="P37" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O37)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O37)</f>
       </c>
       <c r="Q37" s="0">
-        <f>IF(AND(L37="Y",Settings!$B$7="Y"),D37,MAX(1,D37-Settings!$B$4))</f>
+        <f>IF(AND(L37="Y",Settings!$B$8="Y"),D37,MAX(1,D37-Settings!$B$5))</f>
       </c>
       <c r="R37" s="0">
-        <f>MIN(7,D37+Settings!$B$4)</f>
+        <f>MIN(8,D37+Settings!$B$4)</f>
       </c>
       <c r="S37" s="0" t="inlineStr">
         <is>
@@ -7833,22 +7974,22 @@
         </is>
       </c>
       <c r="M38" s="7">
-        <f>E38*(1+G38/Settings!$B$8)</f>
+        <f>E38*(1+G38/Settings!$B$9)</f>
       </c>
       <c r="N38" s="7">
-        <f>F38*(1+H38/Settings!$B$9)</f>
+        <f>F38*(1+H38/Settings!$B$10)</f>
       </c>
       <c r="O38" s="7">
         <f>ROUND(SQRT(M38*N38),1)</f>
       </c>
       <c r="P38" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O38)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O38)</f>
       </c>
       <c r="Q38" s="0">
-        <f>IF(AND(L38="Y",Settings!$B$7="Y"),D38,MAX(1,D38-Settings!$B$4))</f>
+        <f>IF(AND(L38="Y",Settings!$B$8="Y"),D38,MAX(1,D38-Settings!$B$5))</f>
       </c>
       <c r="R38" s="0">
-        <f>MIN(7,D38+Settings!$B$4)</f>
+        <f>MIN(8,D38+Settings!$B$4)</f>
       </c>
       <c r="S38" s="0" t="inlineStr">
         <is>
@@ -7902,22 +8043,22 @@
         </is>
       </c>
       <c r="M39" s="7">
-        <f>E39*(1+G39/Settings!$B$8)</f>
+        <f>E39*(1+G39/Settings!$B$9)</f>
       </c>
       <c r="N39" s="7">
-        <f>F39*(1+H39/Settings!$B$9)</f>
+        <f>F39*(1+H39/Settings!$B$10)</f>
       </c>
       <c r="O39" s="7">
         <f>ROUND(SQRT(M39*N39),1)</f>
       </c>
       <c r="P39" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O39)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O39)</f>
       </c>
       <c r="Q39" s="0">
-        <f>IF(AND(L39="Y",Settings!$B$7="Y"),D39,MAX(1,D39-Settings!$B$4))</f>
+        <f>IF(AND(L39="Y",Settings!$B$8="Y"),D39,MAX(1,D39-Settings!$B$5))</f>
       </c>
       <c r="R39" s="0">
-        <f>MIN(7,D39+Settings!$B$4)</f>
+        <f>MIN(8,D39+Settings!$B$4)</f>
       </c>
       <c r="S39" s="0" t="inlineStr">
         <is>
@@ -7971,22 +8112,22 @@
         </is>
       </c>
       <c r="M40" s="7">
-        <f>E40*(1+G40/Settings!$B$8)</f>
+        <f>E40*(1+G40/Settings!$B$9)</f>
       </c>
       <c r="N40" s="7">
-        <f>F40*(1+H40/Settings!$B$9)</f>
+        <f>F40*(1+H40/Settings!$B$10)</f>
       </c>
       <c r="O40" s="7">
         <f>ROUND(SQRT(M40*N40),1)</f>
       </c>
       <c r="P40" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O40)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O40)</f>
       </c>
       <c r="Q40" s="0">
-        <f>IF(AND(L40="Y",Settings!$B$7="Y"),D40,MAX(1,D40-Settings!$B$4))</f>
+        <f>IF(AND(L40="Y",Settings!$B$8="Y"),D40,MAX(1,D40-Settings!$B$5))</f>
       </c>
       <c r="R40" s="0">
-        <f>MIN(7,D40+Settings!$B$4)</f>
+        <f>MIN(8,D40+Settings!$B$4)</f>
       </c>
       <c r="S40" s="0" t="inlineStr">
         <is>
@@ -8040,22 +8181,22 @@
         </is>
       </c>
       <c r="M41" s="7">
-        <f>E41*(1+G41/Settings!$B$8)</f>
+        <f>E41*(1+G41/Settings!$B$9)</f>
       </c>
       <c r="N41" s="7">
-        <f>F41*(1+H41/Settings!$B$9)</f>
+        <f>F41*(1+H41/Settings!$B$10)</f>
       </c>
       <c r="O41" s="7">
         <f>ROUND(SQRT(M41*N41),1)</f>
       </c>
       <c r="P41" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O41)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O41)</f>
       </c>
       <c r="Q41" s="0">
-        <f>IF(AND(L41="Y",Settings!$B$7="Y"),D41,MAX(1,D41-Settings!$B$4))</f>
+        <f>IF(AND(L41="Y",Settings!$B$8="Y"),D41,MAX(1,D41-Settings!$B$5))</f>
       </c>
       <c r="R41" s="0">
-        <f>MIN(7,D41+Settings!$B$4)</f>
+        <f>MIN(8,D41+Settings!$B$4)</f>
       </c>
       <c r="S41" s="0" t="inlineStr">
         <is>
@@ -8109,22 +8250,22 @@
         </is>
       </c>
       <c r="M42" s="7">
-        <f>E42*(1+G42/Settings!$B$8)</f>
+        <f>E42*(1+G42/Settings!$B$9)</f>
       </c>
       <c r="N42" s="7">
-        <f>F42*(1+H42/Settings!$B$9)</f>
+        <f>F42*(1+H42/Settings!$B$10)</f>
       </c>
       <c r="O42" s="7">
         <f>ROUND(SQRT(M42*N42),1)</f>
       </c>
       <c r="P42" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O42)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O42)</f>
       </c>
       <c r="Q42" s="0">
-        <f>IF(AND(L42="Y",Settings!$B$7="Y"),D42,MAX(1,D42-Settings!$B$4))</f>
+        <f>IF(AND(L42="Y",Settings!$B$8="Y"),D42,MAX(1,D42-Settings!$B$5))</f>
       </c>
       <c r="R42" s="0">
-        <f>MIN(7,D42+Settings!$B$4)</f>
+        <f>MIN(8,D42+Settings!$B$4)</f>
       </c>
       <c r="S42" s="0" t="inlineStr">
         <is>
@@ -8178,22 +8319,22 @@
         </is>
       </c>
       <c r="M43" s="7">
-        <f>E43*(1+G43/Settings!$B$8)</f>
+        <f>E43*(1+G43/Settings!$B$9)</f>
       </c>
       <c r="N43" s="7">
-        <f>F43*(1+H43/Settings!$B$9)</f>
+        <f>F43*(1+H43/Settings!$B$10)</f>
       </c>
       <c r="O43" s="7">
         <f>ROUND(SQRT(M43*N43),1)</f>
       </c>
       <c r="P43" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O43)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O43)</f>
       </c>
       <c r="Q43" s="0">
-        <f>IF(AND(L43="Y",Settings!$B$7="Y"),D43,MAX(1,D43-Settings!$B$4))</f>
+        <f>IF(AND(L43="Y",Settings!$B$8="Y"),D43,MAX(1,D43-Settings!$B$5))</f>
       </c>
       <c r="R43" s="0">
-        <f>MIN(7,D43+Settings!$B$4)</f>
+        <f>MIN(8,D43+Settings!$B$4)</f>
       </c>
       <c r="S43" s="0" t="inlineStr">
         <is>
@@ -8247,22 +8388,22 @@
         </is>
       </c>
       <c r="M44" s="7">
-        <f>E44*(1+G44/Settings!$B$8)</f>
+        <f>E44*(1+G44/Settings!$B$9)</f>
       </c>
       <c r="N44" s="7">
-        <f>F44*(1+H44/Settings!$B$9)</f>
+        <f>F44*(1+H44/Settings!$B$10)</f>
       </c>
       <c r="O44" s="7">
         <f>ROUND(SQRT(M44*N44),1)</f>
       </c>
       <c r="P44" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O44)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O44)</f>
       </c>
       <c r="Q44" s="0">
-        <f>IF(AND(L44="Y",Settings!$B$7="Y"),D44,MAX(1,D44-Settings!$B$4))</f>
+        <f>IF(AND(L44="Y",Settings!$B$8="Y"),D44,MAX(1,D44-Settings!$B$5))</f>
       </c>
       <c r="R44" s="0">
-        <f>MIN(7,D44+Settings!$B$4)</f>
+        <f>MIN(8,D44+Settings!$B$4)</f>
       </c>
       <c r="S44" s="0" t="inlineStr">
         <is>
@@ -8316,22 +8457,22 @@
         </is>
       </c>
       <c r="M45" s="7">
-        <f>E45*(1+G45/Settings!$B$8)</f>
+        <f>E45*(1+G45/Settings!$B$9)</f>
       </c>
       <c r="N45" s="7">
-        <f>F45*(1+H45/Settings!$B$9)</f>
+        <f>F45*(1+H45/Settings!$B$10)</f>
       </c>
       <c r="O45" s="7">
         <f>ROUND(SQRT(M45*N45),1)</f>
       </c>
       <c r="P45" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O45)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O45)</f>
       </c>
       <c r="Q45" s="0">
-        <f>IF(AND(L45="Y",Settings!$B$7="Y"),D45,MAX(1,D45-Settings!$B$4))</f>
+        <f>IF(AND(L45="Y",Settings!$B$8="Y"),D45,MAX(1,D45-Settings!$B$5))</f>
       </c>
       <c r="R45" s="0">
-        <f>MIN(7,D45+Settings!$B$4)</f>
+        <f>MIN(8,D45+Settings!$B$4)</f>
       </c>
       <c r="S45" s="0" t="inlineStr">
         <is>
@@ -8385,22 +8526,22 @@
         </is>
       </c>
       <c r="M46" s="7">
-        <f>E46*(1+G46/Settings!$B$8)</f>
+        <f>E46*(1+G46/Settings!$B$9)</f>
       </c>
       <c r="N46" s="7">
-        <f>F46*(1+H46/Settings!$B$9)</f>
+        <f>F46*(1+H46/Settings!$B$10)</f>
       </c>
       <c r="O46" s="7">
         <f>ROUND(SQRT(M46*N46),1)</f>
       </c>
       <c r="P46" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O46)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O46)</f>
       </c>
       <c r="Q46" s="0">
-        <f>IF(AND(L46="Y",Settings!$B$7="Y"),D46,MAX(1,D46-Settings!$B$4))</f>
+        <f>IF(AND(L46="Y",Settings!$B$8="Y"),D46,MAX(1,D46-Settings!$B$5))</f>
       </c>
       <c r="R46" s="0">
-        <f>MIN(7,D46+Settings!$B$4)</f>
+        <f>MIN(8,D46+Settings!$B$4)</f>
       </c>
       <c r="S46" s="0" t="inlineStr">
         <is>
@@ -8454,22 +8595,22 @@
         </is>
       </c>
       <c r="M47" s="7">
-        <f>E47*(1+G47/Settings!$B$8)</f>
+        <f>E47*(1+G47/Settings!$B$9)</f>
       </c>
       <c r="N47" s="7">
-        <f>F47*(1+H47/Settings!$B$9)</f>
+        <f>F47*(1+H47/Settings!$B$10)</f>
       </c>
       <c r="O47" s="7">
         <f>ROUND(SQRT(M47*N47),1)</f>
       </c>
       <c r="P47" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O47)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O47)</f>
       </c>
       <c r="Q47" s="0">
-        <f>IF(AND(L47="Y",Settings!$B$7="Y"),D47,MAX(1,D47-Settings!$B$4))</f>
+        <f>IF(AND(L47="Y",Settings!$B$8="Y"),D47,MAX(1,D47-Settings!$B$5))</f>
       </c>
       <c r="R47" s="0">
-        <f>MIN(7,D47+Settings!$B$4)</f>
+        <f>MIN(8,D47+Settings!$B$4)</f>
       </c>
       <c r="S47" s="0" t="inlineStr">
         <is>
@@ -8523,22 +8664,22 @@
         </is>
       </c>
       <c r="M48" s="7">
-        <f>E48*(1+G48/Settings!$B$8)</f>
+        <f>E48*(1+G48/Settings!$B$9)</f>
       </c>
       <c r="N48" s="7">
-        <f>F48*(1+H48/Settings!$B$9)</f>
+        <f>F48*(1+H48/Settings!$B$10)</f>
       </c>
       <c r="O48" s="7">
         <f>ROUND(SQRT(M48*N48),1)</f>
       </c>
       <c r="P48" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O48)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O48)</f>
       </c>
       <c r="Q48" s="0">
-        <f>IF(AND(L48="Y",Settings!$B$7="Y"),D48,MAX(1,D48-Settings!$B$4))</f>
+        <f>IF(AND(L48="Y",Settings!$B$8="Y"),D48,MAX(1,D48-Settings!$B$5))</f>
       </c>
       <c r="R48" s="0">
-        <f>MIN(7,D48+Settings!$B$4)</f>
+        <f>MIN(8,D48+Settings!$B$4)</f>
       </c>
       <c r="S48" s="0" t="inlineStr">
         <is>
@@ -8592,22 +8733,22 @@
         </is>
       </c>
       <c r="M49" s="7">
-        <f>E49*(1+G49/Settings!$B$8)</f>
+        <f>E49*(1+G49/Settings!$B$9)</f>
       </c>
       <c r="N49" s="7">
-        <f>F49*(1+H49/Settings!$B$9)</f>
+        <f>F49*(1+H49/Settings!$B$10)</f>
       </c>
       <c r="O49" s="7">
         <f>ROUND(SQRT(M49*N49),1)</f>
       </c>
       <c r="P49" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O49)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O49)</f>
       </c>
       <c r="Q49" s="0">
-        <f>IF(AND(L49="Y",Settings!$B$7="Y"),D49,MAX(1,D49-Settings!$B$4))</f>
+        <f>IF(AND(L49="Y",Settings!$B$8="Y"),D49,MAX(1,D49-Settings!$B$5))</f>
       </c>
       <c r="R49" s="0">
-        <f>MIN(7,D49+Settings!$B$4)</f>
+        <f>MIN(8,D49+Settings!$B$4)</f>
       </c>
       <c r="S49" s="0" t="inlineStr">
         <is>
@@ -8661,22 +8802,22 @@
         </is>
       </c>
       <c r="M50" s="7">
-        <f>E50*(1+G50/Settings!$B$8)</f>
+        <f>E50*(1+G50/Settings!$B$9)</f>
       </c>
       <c r="N50" s="7">
-        <f>F50*(1+H50/Settings!$B$9)</f>
+        <f>F50*(1+H50/Settings!$B$10)</f>
       </c>
       <c r="O50" s="7">
         <f>ROUND(SQRT(M50*N50),1)</f>
       </c>
       <c r="P50" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O50)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O50)</f>
       </c>
       <c r="Q50" s="0">
-        <f>IF(AND(L50="Y",Settings!$B$7="Y"),D50,MAX(1,D50-Settings!$B$4))</f>
+        <f>IF(AND(L50="Y",Settings!$B$8="Y"),D50,MAX(1,D50-Settings!$B$5))</f>
       </c>
       <c r="R50" s="0">
-        <f>MIN(7,D50+Settings!$B$4)</f>
+        <f>MIN(8,D50+Settings!$B$4)</f>
       </c>
       <c r="S50" s="0" t="inlineStr">
         <is>
@@ -8730,22 +8871,22 @@
         </is>
       </c>
       <c r="M51" s="7">
-        <f>E51*(1+G51/Settings!$B$8)</f>
+        <f>E51*(1+G51/Settings!$B$9)</f>
       </c>
       <c r="N51" s="7">
-        <f>F51*(1+H51/Settings!$B$9)</f>
+        <f>F51*(1+H51/Settings!$B$10)</f>
       </c>
       <c r="O51" s="7">
         <f>ROUND(SQRT(M51*N51),1)</f>
       </c>
       <c r="P51" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O51)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O51)</f>
       </c>
       <c r="Q51" s="0">
-        <f>IF(AND(L51="Y",Settings!$B$7="Y"),D51,MAX(1,D51-Settings!$B$4))</f>
+        <f>IF(AND(L51="Y",Settings!$B$8="Y"),D51,MAX(1,D51-Settings!$B$5))</f>
       </c>
       <c r="R51" s="0">
-        <f>MIN(7,D51+Settings!$B$4)</f>
+        <f>MIN(8,D51+Settings!$B$4)</f>
       </c>
       <c r="S51" s="0" t="inlineStr">
         <is>
@@ -8799,22 +8940,22 @@
         </is>
       </c>
       <c r="M52" s="7">
-        <f>E52*(1+G52/Settings!$B$8)</f>
+        <f>E52*(1+G52/Settings!$B$9)</f>
       </c>
       <c r="N52" s="7">
-        <f>F52*(1+H52/Settings!$B$9)</f>
+        <f>F52*(1+H52/Settings!$B$10)</f>
       </c>
       <c r="O52" s="7">
         <f>ROUND(SQRT(M52*N52),1)</f>
       </c>
       <c r="P52" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O52)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O52)</f>
       </c>
       <c r="Q52" s="0">
-        <f>IF(AND(L52="Y",Settings!$B$7="Y"),D52,MAX(1,D52-Settings!$B$4))</f>
+        <f>IF(AND(L52="Y",Settings!$B$8="Y"),D52,MAX(1,D52-Settings!$B$5))</f>
       </c>
       <c r="R52" s="0">
-        <f>MIN(7,D52+Settings!$B$4)</f>
+        <f>MIN(8,D52+Settings!$B$4)</f>
       </c>
       <c r="S52" s="0" t="inlineStr">
         <is>
@@ -8868,22 +9009,22 @@
         </is>
       </c>
       <c r="M53" s="7">
-        <f>E53*(1+G53/Settings!$B$8)</f>
+        <f>E53*(1+G53/Settings!$B$9)</f>
       </c>
       <c r="N53" s="7">
-        <f>F53*(1+H53/Settings!$B$9)</f>
+        <f>F53*(1+H53/Settings!$B$10)</f>
       </c>
       <c r="O53" s="7">
         <f>ROUND(SQRT(M53*N53),1)</f>
       </c>
       <c r="P53" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O53)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O53)</f>
       </c>
       <c r="Q53" s="0">
-        <f>IF(AND(L53="Y",Settings!$B$7="Y"),D53,MAX(1,D53-Settings!$B$4))</f>
+        <f>IF(AND(L53="Y",Settings!$B$8="Y"),D53,MAX(1,D53-Settings!$B$5))</f>
       </c>
       <c r="R53" s="0">
-        <f>MIN(7,D53+Settings!$B$4)</f>
+        <f>MIN(8,D53+Settings!$B$4)</f>
       </c>
       <c r="S53" s="0" t="inlineStr">
         <is>
@@ -8937,22 +9078,22 @@
         </is>
       </c>
       <c r="M54" s="7">
-        <f>E54*(1+G54/Settings!$B$8)</f>
+        <f>E54*(1+G54/Settings!$B$9)</f>
       </c>
       <c r="N54" s="7">
-        <f>F54*(1+H54/Settings!$B$9)</f>
+        <f>F54*(1+H54/Settings!$B$10)</f>
       </c>
       <c r="O54" s="7">
         <f>ROUND(SQRT(M54*N54),1)</f>
       </c>
       <c r="P54" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O54)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O54)</f>
       </c>
       <c r="Q54" s="0">
-        <f>IF(AND(L54="Y",Settings!$B$7="Y"),D54,MAX(1,D54-Settings!$B$4))</f>
+        <f>IF(AND(L54="Y",Settings!$B$8="Y"),D54,MAX(1,D54-Settings!$B$5))</f>
       </c>
       <c r="R54" s="0">
-        <f>MIN(7,D54+Settings!$B$4)</f>
+        <f>MIN(8,D54+Settings!$B$4)</f>
       </c>
       <c r="S54" s="0" t="inlineStr">
         <is>
@@ -9006,22 +9147,22 @@
         </is>
       </c>
       <c r="M55" s="7">
-        <f>E55*(1+G55/Settings!$B$8)</f>
+        <f>E55*(1+G55/Settings!$B$9)</f>
       </c>
       <c r="N55" s="7">
-        <f>F55*(1+H55/Settings!$B$9)</f>
+        <f>F55*(1+H55/Settings!$B$10)</f>
       </c>
       <c r="O55" s="7">
         <f>ROUND(SQRT(M55*N55),1)</f>
       </c>
       <c r="P55" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O55)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O55)</f>
       </c>
       <c r="Q55" s="0">
-        <f>IF(AND(L55="Y",Settings!$B$7="Y"),D55,MAX(1,D55-Settings!$B$4))</f>
+        <f>IF(AND(L55="Y",Settings!$B$8="Y"),D55,MAX(1,D55-Settings!$B$5))</f>
       </c>
       <c r="R55" s="0">
-        <f>MIN(7,D55+Settings!$B$4)</f>
+        <f>MIN(8,D55+Settings!$B$4)</f>
       </c>
       <c r="S55" s="0" t="inlineStr">
         <is>
@@ -9075,22 +9216,22 @@
         </is>
       </c>
       <c r="M56" s="7">
-        <f>E56*(1+G56/Settings!$B$8)</f>
+        <f>E56*(1+G56/Settings!$B$9)</f>
       </c>
       <c r="N56" s="7">
-        <f>F56*(1+H56/Settings!$B$9)</f>
+        <f>F56*(1+H56/Settings!$B$10)</f>
       </c>
       <c r="O56" s="7">
         <f>ROUND(SQRT(M56*N56),1)</f>
       </c>
       <c r="P56" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O56)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O56)</f>
       </c>
       <c r="Q56" s="0">
-        <f>IF(AND(L56="Y",Settings!$B$7="Y"),D56,MAX(1,D56-Settings!$B$4))</f>
+        <f>IF(AND(L56="Y",Settings!$B$8="Y"),D56,MAX(1,D56-Settings!$B$5))</f>
       </c>
       <c r="R56" s="0">
-        <f>MIN(7,D56+Settings!$B$4)</f>
+        <f>MIN(8,D56+Settings!$B$4)</f>
       </c>
       <c r="S56" s="0" t="inlineStr">
         <is>
@@ -9144,22 +9285,22 @@
         </is>
       </c>
       <c r="M57" s="7">
-        <f>E57*(1+G57/Settings!$B$8)</f>
+        <f>E57*(1+G57/Settings!$B$9)</f>
       </c>
       <c r="N57" s="7">
-        <f>F57*(1+H57/Settings!$B$9)</f>
+        <f>F57*(1+H57/Settings!$B$10)</f>
       </c>
       <c r="O57" s="7">
         <f>ROUND(SQRT(M57*N57),1)</f>
       </c>
       <c r="P57" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O57)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O57)</f>
       </c>
       <c r="Q57" s="0">
-        <f>IF(AND(L57="Y",Settings!$B$7="Y"),D57,MAX(1,D57-Settings!$B$4))</f>
+        <f>IF(AND(L57="Y",Settings!$B$8="Y"),D57,MAX(1,D57-Settings!$B$5))</f>
       </c>
       <c r="R57" s="0">
-        <f>MIN(7,D57+Settings!$B$4)</f>
+        <f>MIN(8,D57+Settings!$B$4)</f>
       </c>
       <c r="S57" s="0" t="inlineStr">
         <is>
@@ -9213,22 +9354,22 @@
         </is>
       </c>
       <c r="M58" s="7">
-        <f>E58*(1+G58/Settings!$B$8)</f>
+        <f>E58*(1+G58/Settings!$B$9)</f>
       </c>
       <c r="N58" s="7">
-        <f>F58*(1+H58/Settings!$B$9)</f>
+        <f>F58*(1+H58/Settings!$B$10)</f>
       </c>
       <c r="O58" s="7">
         <f>ROUND(SQRT(M58*N58),1)</f>
       </c>
       <c r="P58" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O58)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O58)</f>
       </c>
       <c r="Q58" s="0">
-        <f>IF(AND(L58="Y",Settings!$B$7="Y"),D58,MAX(1,D58-Settings!$B$4))</f>
+        <f>IF(AND(L58="Y",Settings!$B$8="Y"),D58,MAX(1,D58-Settings!$B$5))</f>
       </c>
       <c r="R58" s="0">
-        <f>MIN(7,D58+Settings!$B$4)</f>
+        <f>MIN(8,D58+Settings!$B$4)</f>
       </c>
       <c r="S58" s="0" t="inlineStr">
         <is>
@@ -9282,22 +9423,22 @@
         </is>
       </c>
       <c r="M59" s="7">
-        <f>E59*(1+G59/Settings!$B$8)</f>
+        <f>E59*(1+G59/Settings!$B$9)</f>
       </c>
       <c r="N59" s="7">
-        <f>F59*(1+H59/Settings!$B$9)</f>
+        <f>F59*(1+H59/Settings!$B$10)</f>
       </c>
       <c r="O59" s="7">
         <f>ROUND(SQRT(M59*N59),1)</f>
       </c>
       <c r="P59" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O59)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O59)</f>
       </c>
       <c r="Q59" s="0">
-        <f>IF(AND(L59="Y",Settings!$B$7="Y"),D59,MAX(1,D59-Settings!$B$4))</f>
+        <f>IF(AND(L59="Y",Settings!$B$8="Y"),D59,MAX(1,D59-Settings!$B$5))</f>
       </c>
       <c r="R59" s="0">
-        <f>MIN(7,D59+Settings!$B$4)</f>
+        <f>MIN(8,D59+Settings!$B$4)</f>
       </c>
       <c r="S59" s="0" t="inlineStr">
         <is>
@@ -9351,22 +9492,22 @@
         </is>
       </c>
       <c r="M60" s="7">
-        <f>E60*(1+G60/Settings!$B$8)</f>
+        <f>E60*(1+G60/Settings!$B$9)</f>
       </c>
       <c r="N60" s="7">
-        <f>F60*(1+H60/Settings!$B$9)</f>
+        <f>F60*(1+H60/Settings!$B$10)</f>
       </c>
       <c r="O60" s="7">
         <f>ROUND(SQRT(M60*N60),1)</f>
       </c>
       <c r="P60" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O60)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O60)</f>
       </c>
       <c r="Q60" s="0">
-        <f>IF(AND(L60="Y",Settings!$B$7="Y"),D60,MAX(1,D60-Settings!$B$4))</f>
+        <f>IF(AND(L60="Y",Settings!$B$8="Y"),D60,MAX(1,D60-Settings!$B$5))</f>
       </c>
       <c r="R60" s="0">
-        <f>MIN(7,D60+Settings!$B$4)</f>
+        <f>MIN(8,D60+Settings!$B$4)</f>
       </c>
       <c r="S60" s="0" t="inlineStr">
         <is>
@@ -9420,22 +9561,22 @@
         </is>
       </c>
       <c r="M61" s="7">
-        <f>E61*(1+G61/Settings!$B$8)</f>
+        <f>E61*(1+G61/Settings!$B$9)</f>
       </c>
       <c r="N61" s="7">
-        <f>F61*(1+H61/Settings!$B$9)</f>
+        <f>F61*(1+H61/Settings!$B$10)</f>
       </c>
       <c r="O61" s="7">
         <f>ROUND(SQRT(M61*N61),1)</f>
       </c>
       <c r="P61" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O61)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O61)</f>
       </c>
       <c r="Q61" s="0">
-        <f>IF(AND(L61="Y",Settings!$B$7="Y"),D61,MAX(1,D61-Settings!$B$4))</f>
+        <f>IF(AND(L61="Y",Settings!$B$8="Y"),D61,MAX(1,D61-Settings!$B$5))</f>
       </c>
       <c r="R61" s="0">
-        <f>MIN(7,D61+Settings!$B$4)</f>
+        <f>MIN(8,D61+Settings!$B$4)</f>
       </c>
       <c r="S61" s="0" t="inlineStr">
         <is>
@@ -9489,22 +9630,22 @@
         </is>
       </c>
       <c r="M62" s="7">
-        <f>E62*(1+G62/Settings!$B$8)</f>
+        <f>E62*(1+G62/Settings!$B$9)</f>
       </c>
       <c r="N62" s="7">
-        <f>F62*(1+H62/Settings!$B$9)</f>
+        <f>F62*(1+H62/Settings!$B$10)</f>
       </c>
       <c r="O62" s="7">
         <f>ROUND(SQRT(M62*N62),1)</f>
       </c>
       <c r="P62" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O62)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O62)</f>
       </c>
       <c r="Q62" s="0">
-        <f>IF(AND(L62="Y",Settings!$B$7="Y"),D62,MAX(1,D62-Settings!$B$4))</f>
+        <f>IF(AND(L62="Y",Settings!$B$8="Y"),D62,MAX(1,D62-Settings!$B$5))</f>
       </c>
       <c r="R62" s="0">
-        <f>MIN(7,D62+Settings!$B$4)</f>
+        <f>MIN(8,D62+Settings!$B$4)</f>
       </c>
       <c r="S62" s="0" t="inlineStr">
         <is>
@@ -9558,22 +9699,22 @@
         </is>
       </c>
       <c r="M63" s="7">
-        <f>E63*(1+G63/Settings!$B$8)</f>
+        <f>E63*(1+G63/Settings!$B$9)</f>
       </c>
       <c r="N63" s="7">
-        <f>F63*(1+H63/Settings!$B$9)</f>
+        <f>F63*(1+H63/Settings!$B$10)</f>
       </c>
       <c r="O63" s="7">
         <f>ROUND(SQRT(M63*N63),1)</f>
       </c>
       <c r="P63" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O63)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O63)</f>
       </c>
       <c r="Q63" s="0">
-        <f>IF(AND(L63="Y",Settings!$B$7="Y"),D63,MAX(1,D63-Settings!$B$4))</f>
+        <f>IF(AND(L63="Y",Settings!$B$8="Y"),D63,MAX(1,D63-Settings!$B$5))</f>
       </c>
       <c r="R63" s="0">
-        <f>MIN(7,D63+Settings!$B$4)</f>
+        <f>MIN(8,D63+Settings!$B$4)</f>
       </c>
       <c r="S63" s="0" t="inlineStr">
         <is>
@@ -9627,22 +9768,22 @@
         </is>
       </c>
       <c r="M64" s="7">
-        <f>E64*(1+G64/Settings!$B$8)</f>
+        <f>E64*(1+G64/Settings!$B$9)</f>
       </c>
       <c r="N64" s="7">
-        <f>F64*(1+H64/Settings!$B$9)</f>
+        <f>F64*(1+H64/Settings!$B$10)</f>
       </c>
       <c r="O64" s="7">
         <f>ROUND(SQRT(M64*N64),1)</f>
       </c>
       <c r="P64" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O64)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O64)</f>
       </c>
       <c r="Q64" s="0">
-        <f>IF(AND(L64="Y",Settings!$B$7="Y"),D64,MAX(1,D64-Settings!$B$4))</f>
+        <f>IF(AND(L64="Y",Settings!$B$8="Y"),D64,MAX(1,D64-Settings!$B$5))</f>
       </c>
       <c r="R64" s="0">
-        <f>MIN(7,D64+Settings!$B$4)</f>
+        <f>MIN(8,D64+Settings!$B$4)</f>
       </c>
       <c r="S64" s="0" t="inlineStr">
         <is>
@@ -9696,22 +9837,22 @@
         </is>
       </c>
       <c r="M65" s="7">
-        <f>E65*(1+G65/Settings!$B$8)</f>
+        <f>E65*(1+G65/Settings!$B$9)</f>
       </c>
       <c r="N65" s="7">
-        <f>F65*(1+H65/Settings!$B$9)</f>
+        <f>F65*(1+H65/Settings!$B$10)</f>
       </c>
       <c r="O65" s="7">
         <f>ROUND(SQRT(M65*N65),1)</f>
       </c>
       <c r="P65" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O65)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O65)</f>
       </c>
       <c r="Q65" s="0">
-        <f>IF(AND(L65="Y",Settings!$B$7="Y"),D65,MAX(1,D65-Settings!$B$4))</f>
+        <f>IF(AND(L65="Y",Settings!$B$8="Y"),D65,MAX(1,D65-Settings!$B$5))</f>
       </c>
       <c r="R65" s="0">
-        <f>MIN(7,D65+Settings!$B$4)</f>
+        <f>MIN(8,D65+Settings!$B$4)</f>
       </c>
       <c r="S65" s="0" t="inlineStr">
         <is>
@@ -9765,22 +9906,22 @@
         </is>
       </c>
       <c r="M66" s="7">
-        <f>E66*(1+G66/Settings!$B$8)</f>
+        <f>E66*(1+G66/Settings!$B$9)</f>
       </c>
       <c r="N66" s="7">
-        <f>F66*(1+H66/Settings!$B$9)</f>
+        <f>F66*(1+H66/Settings!$B$10)</f>
       </c>
       <c r="O66" s="7">
         <f>ROUND(SQRT(M66*N66),1)</f>
       </c>
       <c r="P66" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O66)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O66)</f>
       </c>
       <c r="Q66" s="0">
-        <f>IF(AND(L66="Y",Settings!$B$7="Y"),D66,MAX(1,D66-Settings!$B$4))</f>
+        <f>IF(AND(L66="Y",Settings!$B$8="Y"),D66,MAX(1,D66-Settings!$B$5))</f>
       </c>
       <c r="R66" s="0">
-        <f>MIN(7,D66+Settings!$B$4)</f>
+        <f>MIN(8,D66+Settings!$B$4)</f>
       </c>
       <c r="S66" s="0" t="inlineStr">
         <is>
@@ -9834,22 +9975,22 @@
         </is>
       </c>
       <c r="M67" s="7">
-        <f>E67*(1+G67/Settings!$B$8)</f>
+        <f>E67*(1+G67/Settings!$B$9)</f>
       </c>
       <c r="N67" s="7">
-        <f>F67*(1+H67/Settings!$B$9)</f>
+        <f>F67*(1+H67/Settings!$B$10)</f>
       </c>
       <c r="O67" s="7">
         <f>ROUND(SQRT(M67*N67),1)</f>
       </c>
       <c r="P67" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O67)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O67)</f>
       </c>
       <c r="Q67" s="0">
-        <f>IF(AND(L67="Y",Settings!$B$7="Y"),D67,MAX(1,D67-Settings!$B$4))</f>
+        <f>IF(AND(L67="Y",Settings!$B$8="Y"),D67,MAX(1,D67-Settings!$B$5))</f>
       </c>
       <c r="R67" s="0">
-        <f>MIN(7,D67+Settings!$B$4)</f>
+        <f>MIN(8,D67+Settings!$B$4)</f>
       </c>
       <c r="S67" s="0" t="inlineStr">
         <is>
@@ -9903,22 +10044,22 @@
         </is>
       </c>
       <c r="M68" s="7">
-        <f>E68*(1+G68/Settings!$B$8)</f>
+        <f>E68*(1+G68/Settings!$B$9)</f>
       </c>
       <c r="N68" s="7">
-        <f>F68*(1+H68/Settings!$B$9)</f>
+        <f>F68*(1+H68/Settings!$B$10)</f>
       </c>
       <c r="O68" s="7">
         <f>ROUND(SQRT(M68*N68),1)</f>
       </c>
       <c r="P68" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O68)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O68)</f>
       </c>
       <c r="Q68" s="0">
-        <f>IF(AND(L68="Y",Settings!$B$7="Y"),D68,MAX(1,D68-Settings!$B$4))</f>
+        <f>IF(AND(L68="Y",Settings!$B$8="Y"),D68,MAX(1,D68-Settings!$B$5))</f>
       </c>
       <c r="R68" s="0">
-        <f>MIN(7,D68+Settings!$B$4)</f>
+        <f>MIN(8,D68+Settings!$B$4)</f>
       </c>
       <c r="S68" s="0" t="inlineStr">
         <is>
@@ -9972,22 +10113,22 @@
         </is>
       </c>
       <c r="M69" s="7">
-        <f>E69*(1+G69/Settings!$B$8)</f>
+        <f>E69*(1+G69/Settings!$B$9)</f>
       </c>
       <c r="N69" s="7">
-        <f>F69*(1+H69/Settings!$B$9)</f>
+        <f>F69*(1+H69/Settings!$B$10)</f>
       </c>
       <c r="O69" s="7">
         <f>ROUND(SQRT(M69*N69),1)</f>
       </c>
       <c r="P69" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O69)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O69)</f>
       </c>
       <c r="Q69" s="0">
-        <f>IF(AND(L69="Y",Settings!$B$7="Y"),D69,MAX(1,D69-Settings!$B$4))</f>
+        <f>IF(AND(L69="Y",Settings!$B$8="Y"),D69,MAX(1,D69-Settings!$B$5))</f>
       </c>
       <c r="R69" s="0">
-        <f>MIN(7,D69+Settings!$B$4)</f>
+        <f>MIN(8,D69+Settings!$B$4)</f>
       </c>
       <c r="S69" s="0" t="inlineStr">
         <is>
@@ -10041,22 +10182,22 @@
         </is>
       </c>
       <c r="M70" s="7">
-        <f>E70*(1+G70/Settings!$B$8)</f>
+        <f>E70*(1+G70/Settings!$B$9)</f>
       </c>
       <c r="N70" s="7">
-        <f>F70*(1+H70/Settings!$B$9)</f>
+        <f>F70*(1+H70/Settings!$B$10)</f>
       </c>
       <c r="O70" s="7">
         <f>ROUND(SQRT(M70*N70),1)</f>
       </c>
       <c r="P70" s="0">
-        <f>1+COUNTIF(Settings!$B$12:$B$17,"&lt;="&amp;O70)</f>
+        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O70)</f>
       </c>
       <c r="Q70" s="0">
-        <f>IF(AND(L70="Y",Settings!$B$7="Y"),D70,MAX(1,D70-Settings!$B$4))</f>
+        <f>IF(AND(L70="Y",Settings!$B$8="Y"),D70,MAX(1,D70-Settings!$B$5))</f>
       </c>
       <c r="R70" s="0">
-        <f>MIN(7,D70+Settings!$B$4)</f>
+        <f>MIN(8,D70+Settings!$B$4)</f>
       </c>
       <c r="S70" s="0" t="inlineStr">
         <is>
@@ -10091,7 +10232,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pick a monster and a destination area (yellow). The table shows its home stats, the two areas' vanilla averages, the factor between them, and the rescaled stats under Settings!B5. The grid below previews the same monster in every area.</t>
+          <t xml:space="preserve">Pick a monster and a destination area (yellow). The table shows its home stats, the two areas' vanilla averages, the factor between them, the destination's progression guard, and the rescaled stats under Settings!B6. The grid below previews the same monster in every area.</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10298,16 @@
         <f>IF(AND(D6&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),D6&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no (outside spread)")</f>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Destination guard x</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <f>INDEX(Areas!$N:$N,MATCH($B$4,Areas!$B:$B,0))</f>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -10191,7 +10341,7 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scaled</t>
+          <t xml:space="preserve">Scaled (with guard)</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
@@ -10219,13 +10369,13 @@
         <f>D10/C10</f>
       </c>
       <c r="F10" s="7">
-        <f>Settings!$B$5</f>
+        <f>Settings!$B$6</f>
       </c>
       <c r="G10" s="0">
-        <f>MIN(H10,ROUND(B10*E10^F10,0))</f>
+        <f>MIN(H10,ROUND(B10*E10^F10*$B$8,0))</f>
       </c>
       <c r="H10" s="0">
-        <f>Settings!$B$21</f>
+        <f>Settings!$B$23</f>
       </c>
     </row>
     <row r="11">
@@ -10247,13 +10397,13 @@
         <f>D11/C11</f>
       </c>
       <c r="F11" s="7">
-        <f>Settings!$B$5</f>
+        <f>Settings!$B$6</f>
       </c>
       <c r="G11" s="0">
-        <f>MIN(H11,ROUND(B11*E11^F11,0))</f>
+        <f>MIN(H11,ROUND(B11*E11^F11*$B$8,0))</f>
       </c>
       <c r="H11" s="0">
-        <f>Settings!$B$22</f>
+        <f>Settings!$B$24</f>
       </c>
     </row>
     <row r="12">
@@ -10275,13 +10425,13 @@
         <f>D12/C12</f>
       </c>
       <c r="F12" s="7">
-        <f>Settings!$B$5</f>
+        <f>Settings!$B$6</f>
       </c>
       <c r="G12" s="0">
-        <f>MIN(H12,ROUND(B12*E12^F12,0))</f>
+        <f>MIN(H12,ROUND(B12*E12^F12*$B$8,0))</f>
       </c>
       <c r="H12" s="0">
-        <f>Settings!$B$22</f>
+        <f>Settings!$B$24</f>
       </c>
     </row>
     <row r="13">
@@ -10303,13 +10453,13 @@
         <f>D13/C13</f>
       </c>
       <c r="F13" s="7">
-        <f>Settings!$B$5</f>
+        <f>Settings!$B$6</f>
       </c>
       <c r="G13" s="0">
-        <f>MIN(H13,ROUND(B13*E13^F13,0))</f>
+        <f>MIN(H13,ROUND(B13*E13^F13*$B$8,0))</f>
       </c>
       <c r="H13" s="0">
-        <f>Settings!$B$22</f>
+        <f>Settings!$B$24</f>
       </c>
     </row>
     <row r="14">
@@ -10334,7 +10484,7 @@
         <f>1</f>
       </c>
       <c r="G14" s="0">
-        <f>MIN(H14,ROUND(B14*E14^F14,0))</f>
+        <f>MIN(H14,ROUND(B14*E14^F14*$B$8,0))</f>
       </c>
       <c r="H14" s="0">
         <f>99999</f>
@@ -10344,7 +10494,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preview: the chosen monster in every area</t>
+          <t xml:space="preserve">Preview: the chosen monster in every area (guard included)</t>
         </is>
       </c>
     </row>
@@ -10400,19 +10550,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A18,Areas!$B:$B,0))</f>
       </c>
       <c r="C18" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D18" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E18" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F18" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G18" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H18" s="0">
         <f>IF(AND(B18&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B18&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10428,19 +10578,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A19,Areas!$B:$B,0))</f>
       </c>
       <c r="C19" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D19" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E19" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F19" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G19" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H19" s="0">
         <f>IF(AND(B19&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B19&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10456,19 +10606,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A20,Areas!$B:$B,0))</f>
       </c>
       <c r="C20" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D20" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E20" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F20" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G20" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H20" s="0">
         <f>IF(AND(B20&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B20&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10484,19 +10634,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A21,Areas!$B:$B,0))</f>
       </c>
       <c r="C21" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D21" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E21" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F21" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G21" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H21" s="0">
         <f>IF(AND(B21&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B21&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10512,19 +10662,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A22,Areas!$B:$B,0))</f>
       </c>
       <c r="C22" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D22" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E22" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F22" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G22" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H22" s="0">
         <f>IF(AND(B22&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B22&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10540,19 +10690,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A23,Areas!$B:$B,0))</f>
       </c>
       <c r="C23" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D23" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E23" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F23" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G23" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H23" s="0">
         <f>IF(AND(B23&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B23&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10568,19 +10718,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A24,Areas!$B:$B,0))</f>
       </c>
       <c r="C24" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D24" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E24" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F24" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G24" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H24" s="0">
         <f>IF(AND(B24&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B24&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10596,19 +10746,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A25,Areas!$B:$B,0))</f>
       </c>
       <c r="C25" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D25" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E25" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F25" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G25" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H25" s="0">
         <f>IF(AND(B25&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B25&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10624,19 +10774,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A26,Areas!$B:$B,0))</f>
       </c>
       <c r="C26" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D26" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E26" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F26" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G26" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H26" s="0">
         <f>IF(AND(B26&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B26&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10652,19 +10802,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A27,Areas!$B:$B,0))</f>
       </c>
       <c r="C27" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D27" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E27" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F27" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G27" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H27" s="0">
         <f>IF(AND(B27&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B27&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10680,19 +10830,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A28,Areas!$B:$B,0))</f>
       </c>
       <c r="C28" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D28" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E28" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F28" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G28" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H28" s="0">
         <f>IF(AND(B28&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B28&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10708,19 +10858,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A29,Areas!$B:$B,0))</f>
       </c>
       <c r="C29" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D29" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E29" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F29" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G29" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H29" s="0">
         <f>IF(AND(B29&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B29&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10736,19 +10886,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A30,Areas!$B:$B,0))</f>
       </c>
       <c r="C30" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D30" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E30" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F30" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G30" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H30" s="0">
         <f>IF(AND(B30&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B30&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10764,19 +10914,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A31,Areas!$B:$B,0))</f>
       </c>
       <c r="C31" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D31" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E31" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F31" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G31" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H31" s="0">
         <f>IF(AND(B31&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B31&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10792,19 +10942,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A32,Areas!$B:$B,0))</f>
       </c>
       <c r="C32" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D32" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E32" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F32" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G32" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H32" s="0">
         <f>IF(AND(B32&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B32&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10820,19 +10970,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A33,Areas!$B:$B,0))</f>
       </c>
       <c r="C33" s="0">
-        <f>MIN(Settings!$B$21,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D33" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E33" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F33" s="0">
-        <f>MIN(Settings!$B$22,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$5,0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G33" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1,0))</f>
+        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H33" s="0">
         <f>IF(AND(B33&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B33&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10921,7 +11071,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/game/randomizer/randomizer.cpp shuffle_enemies() already owns the table index / pack writes; add the tier pool selection there and the stat writes next to the existing monster_stats writes. Options: enemy_progression (bool), enemy_tier_spread (int), enemy_scale_strength (0/50/100 %), enemy_max_fliers. UI: three controls under the existing "Enemy shuffling" group on the Randomizer tab. The tier table itself can be a constant array (one tier per area, from the Areas tab).</t>
+          <t xml:space="preserve">src/game/randomizer/randomizer.cpp shuffle_enemies() already owns the table index / pack writes; add the tier pool selection there and the stat writes next to the existing monster_stats writes. Options: enemy_progression (bool), enemy_spread_down and enemy_spread_up (int), enemy_scale_strength (0/50/100 %), enemy_max_fliers. The per-area tiers and the progression budgets are constants derived from the Areas tab. UI: four controls under the existing "Enemy shuffling" group on the Randomizer tab. The tier table itself can be a constant array (one tier per area, from the Areas tab).</t>
         </is>
       </c>
     </row>
@@ -10935,7 +11085,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Should the spread be asymmetric (allow one tier down, two up) so the game gets harder rather than easier? Should exp scale with k or always fully (this sheet says always)? Do the story bosses' areas (Connor, Windward, Blue Cave, Boil Hole, Moor, Brannoch) need the boss's own minions kept vanilla for the fight leading up to them?</t>
+          <t xml:space="preserve">Should exp scale with k or always fully (this sheet says always)? Do the story bosses' areas (Connor, Windward, Blue Cave, Boil Hole, Moor, Brannoch) need the boss's own minions kept vanilla for the fight leading up to them?</t>
         </is>
       </c>
     </row>

--- a/DOCS/enemyrandologic.xlsx
+++ b/DOCS/enemyrandologic.xlsx
@@ -174,7 +174,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Spread (Settings B4 down / B5 up). A tier-T area may take monsters of native tier T-down .. T+up. 0/0 = a reshuffle within difficulty bands, 1/1 = the recommended default, 0/2 = only ever harder monsters (scaled down to fit), 7/7 = anything goes (Merrow's behaviour). Dangerous monsters (Monsters column L: Cockatrice petrifies, Flamed Mane) never go below their native tier whatever the spread.</t>
+          <t xml:space="preserve">3. Spread (Settings B4 down / B5 up). Default 7 / 7: any monster set can appear in any area, the scaling below is what balances it. Narrower spreads (e.g. 1 / 1) keep an area to sets whose monsters are within that many tiers of its own; 0 / 0 is a reshuffle within difficulty bands. Note the game\x27s monsters come in six fixed sets that are placed whole (see Implementation), so the window applies to sets, not single monsters.</t>
         </is>
       </c>
     </row>
@@ -202,7 +202,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7. Flying (Monsters column K, the ROM's flag). The vanilla game limits fliers because some spells cannot reach them; keep at most Settings B7 fliers per area and none in tier 1.</t>
+          <t xml:space="preserve">7. Flying and dangerous flags (Monsters K-L) are informational only: nothing is excluded from any area. Cockatrice keeps its petrify wherever it lands, so it is the one monster whose danger the numbers do not capture; Settings B8 = Y pins it (and Flamed Mane) at their native tier or above if that proves too harsh early.</t>
         </is>
       </c>
     </row>
@@ -285,11 +285,11 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An area may take monsters from this many tiers BELOW its own (easier monsters, scaled up). 0 = none.</t>
+          <t xml:space="preserve">An area may take monsters from this many tiers BELOW its own (easier monsters, scaled up). 7 = any tier (the default: placement is unrestricted, the scaling does the balancing). 0 = none.</t>
         </is>
       </c>
     </row>
@@ -330,11 +330,11 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upper bound on flying monsters in one roster; tier 1 gets none.</t>
+          <t xml:space="preserve">Not enforced (any monster may appear anywhere); kept for reference. The ROM flags only Wyvern, Will-o\x27-Wisp and Pixie as flying.</t>
         </is>
       </c>
     </row>
@@ -346,12 +346,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cockatrice / Flamed Mane never appear earlier than vanilla.</t>
+          <t xml:space="preserve">Off by default: Cockatrice / Flamed Mane may appear anywhere, rescaled like everything else. Y pins them at or above their native tier.</t>
         </is>
       </c>
     </row>

--- a/DOCS/enemyrandologic.xlsx
+++ b/DOCS/enemyrandologic.xlsx
@@ -188,7 +188,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. Stat scaling (Settings B6). For a monster placed in area A: factor = AreaAvg(A, stat) / AreaAvg(home, stat); new = round(own * factor ^ k * guard(A)). k = 1.0 fits the monster fully to the new area, 0.5 meets halfway, 0 leaves stats alone (not recommended). EXP always uses k = 1. HP capped at 999, ATK/DEF/AGI at 255. See ScalingExample for a live worked example.</t>
+          <t xml:space="preserve">5. Stat scaling. For a monster placed in area A: new = AreaAvg(A, stat) * (own / AreaAvg(home, stat)) ^ s * guard(A). The monster is moved to the destination\x27s average and keeps its own deviation from its home average, compressed by the shape exponent s (Settings B26, 0.5): a monster three times its home average lands at 1.7 times the destination\x27s, so home-area bruisers like Ork Jr do not become super-bosses late. s = 1 would preserve the ratio exactly, 0 would make every monster the destination average. Applies to HP, ATK, DEF, AGI, EXP and Stones alike; spell damage follows ATK inside the game. HP capped at 999, ATK/DEF/AGI at 255. See ScalingExample.</t>
         </is>
       </c>
     </row>
@@ -542,6 +542,22 @@
       <c r="C24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Stored as bytes in the game's battle struct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shape exponent s</t>
+        </is>
+      </c>
+      <c r="B26" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rule 5: how much of a monster's deviation from its home average survives the move. 0.5 = square root (a monster at 3x its home average lands at 1.7x the destination's); 1 keeps the exact ratio; 0 makes every monster the destination average. This cell is B26.</t>
         </is>
       </c>
     </row>
@@ -10331,12 +10347,12 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factor</t>
+          <t xml:space="preserve">Own / home avg</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">k used</t>
+          <t xml:space="preserve">Shape ^ s</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
@@ -10366,13 +10382,13 @@
         <f>INDEX(Areas!$G:$G,MATCH($B$4,Areas!$B:$B,0))</f>
       </c>
       <c r="E10" s="7">
-        <f>D10/C10</f>
+        <f>B10/C10</f>
       </c>
       <c r="F10" s="7">
-        <f>Settings!$B$6</f>
+        <f>E10^Settings!$B$26</f>
       </c>
       <c r="G10" s="0">
-        <f>MIN(H10,ROUND(B10*E10^F10*$B$8,0))</f>
+        <f>MIN(H10,ROUND(D10*F10*$B$8,0))</f>
       </c>
       <c r="H10" s="0">
         <f>Settings!$B$23</f>
@@ -10394,13 +10410,13 @@
         <f>INDEX(Areas!$H:$H,MATCH($B$4,Areas!$B:$B,0))</f>
       </c>
       <c r="E11" s="7">
-        <f>D11/C11</f>
+        <f>B11/C11</f>
       </c>
       <c r="F11" s="7">
-        <f>Settings!$B$6</f>
+        <f>E11^Settings!$B$26</f>
       </c>
       <c r="G11" s="0">
-        <f>MIN(H11,ROUND(B11*E11^F11*$B$8,0))</f>
+        <f>MIN(H11,ROUND(D11*F11*$B$8,0))</f>
       </c>
       <c r="H11" s="0">
         <f>Settings!$B$24</f>
@@ -10422,13 +10438,13 @@
         <f>INDEX(Areas!$I:$I,MATCH($B$4,Areas!$B:$B,0))</f>
       </c>
       <c r="E12" s="7">
-        <f>D12/C12</f>
+        <f>B12/C12</f>
       </c>
       <c r="F12" s="7">
-        <f>Settings!$B$6</f>
+        <f>E12^Settings!$B$26</f>
       </c>
       <c r="G12" s="0">
-        <f>MIN(H12,ROUND(B12*E12^F12*$B$8,0))</f>
+        <f>MIN(H12,ROUND(D12*F12*$B$8,0))</f>
       </c>
       <c r="H12" s="0">
         <f>Settings!$B$24</f>
@@ -10450,13 +10466,13 @@
         <f>INDEX(Areas!$J:$J,MATCH($B$4,Areas!$B:$B,0))</f>
       </c>
       <c r="E13" s="7">
-        <f>D13/C13</f>
+        <f>B13/C13</f>
       </c>
       <c r="F13" s="7">
-        <f>Settings!$B$6</f>
+        <f>E13^Settings!$B$26</f>
       </c>
       <c r="G13" s="0">
-        <f>MIN(H13,ROUND(B13*E13^F13*$B$8,0))</f>
+        <f>MIN(H13,ROUND(D13*F13*$B$8,0))</f>
       </c>
       <c r="H13" s="0">
         <f>Settings!$B$24</f>
@@ -10478,13 +10494,13 @@
         <f>INDEX(Areas!$K:$K,MATCH($B$4,Areas!$B:$B,0))</f>
       </c>
       <c r="E14" s="7">
-        <f>D14/C14</f>
+        <f>B14/C14</f>
       </c>
       <c r="F14" s="7">
-        <f>1</f>
+        <f>E14^Settings!$B$26</f>
       </c>
       <c r="G14" s="0">
-        <f>MIN(H14,ROUND(B14*E14^F14*$B$8,0))</f>
+        <f>MIN(H14,ROUND(D14*F14*$B$8,0))</f>
       </c>
       <c r="H14" s="0">
         <f>99999</f>
@@ -10550,19 +10566,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A18,Areas!$B:$B,0))</f>
       </c>
       <c r="C18" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D18" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E18" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F18" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G18" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A18,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H18" s="0">
         <f>IF(AND(B18&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B18&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10578,19 +10594,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A19,Areas!$B:$B,0))</f>
       </c>
       <c r="C19" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D19" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E19" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F19" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G19" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A19,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H19" s="0">
         <f>IF(AND(B19&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B19&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10606,19 +10622,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A20,Areas!$B:$B,0))</f>
       </c>
       <c r="C20" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D20" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E20" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F20" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G20" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A20,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H20" s="0">
         <f>IF(AND(B20&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B20&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10634,19 +10650,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A21,Areas!$B:$B,0))</f>
       </c>
       <c r="C21" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D21" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E21" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F21" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G21" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A21,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H21" s="0">
         <f>IF(AND(B21&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B21&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10662,19 +10678,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A22,Areas!$B:$B,0))</f>
       </c>
       <c r="C22" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D22" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E22" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F22" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G22" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A22,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H22" s="0">
         <f>IF(AND(B22&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B22&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10690,19 +10706,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A23,Areas!$B:$B,0))</f>
       </c>
       <c r="C23" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D23" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E23" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F23" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G23" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A23,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H23" s="0">
         <f>IF(AND(B23&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B23&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10718,19 +10734,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A24,Areas!$B:$B,0))</f>
       </c>
       <c r="C24" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D24" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E24" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F24" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G24" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A24,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H24" s="0">
         <f>IF(AND(B24&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B24&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10746,19 +10762,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A25,Areas!$B:$B,0))</f>
       </c>
       <c r="C25" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D25" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E25" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F25" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G25" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A25,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H25" s="0">
         <f>IF(AND(B25&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B25&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10774,19 +10790,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A26,Areas!$B:$B,0))</f>
       </c>
       <c r="C26" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D26" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E26" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F26" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G26" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A26,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H26" s="0">
         <f>IF(AND(B26&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B26&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10802,19 +10818,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A27,Areas!$B:$B,0))</f>
       </c>
       <c r="C27" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D27" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E27" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F27" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G27" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A27,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H27" s="0">
         <f>IF(AND(B27&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B27&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10830,19 +10846,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A28,Areas!$B:$B,0))</f>
       </c>
       <c r="C28" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D28" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E28" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F28" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G28" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A28,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H28" s="0">
         <f>IF(AND(B28&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B28&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10858,19 +10874,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A29,Areas!$B:$B,0))</f>
       </c>
       <c r="C29" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D29" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E29" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F29" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G29" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A29,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H29" s="0">
         <f>IF(AND(B29&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B29&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10886,19 +10902,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A30,Areas!$B:$B,0))</f>
       </c>
       <c r="C30" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D30" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E30" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F30" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G30" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A30,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H30" s="0">
         <f>IF(AND(B30&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B30&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10914,19 +10930,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A31,Areas!$B:$B,0))</f>
       </c>
       <c r="C31" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D31" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E31" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F31" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G31" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A31,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H31" s="0">
         <f>IF(AND(B31&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B31&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10942,19 +10958,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A32,Areas!$B:$B,0))</f>
       </c>
       <c r="C32" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D32" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E32" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F32" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G32" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A32,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H32" s="0">
         <f>IF(AND(B32&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B32&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10970,19 +10986,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A33,Areas!$B:$B,0))</f>
       </c>
       <c r="C33" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$G:$G,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D33" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$H:$H,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E33" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$I:$I,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F33" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$J:$J,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G33" s="0">
-        <f>MIN(99999,ROUND(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))*(INDEX(Areas!$K:$K,MATCH($A33,Areas!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^1*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
+        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H33" s="0">
         <f>IF(AND(B33&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B33&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>

--- a/DOCS/enemyrandologic.xlsx
+++ b/DOCS/enemyrandologic.xlsx
@@ -108,14 +108,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enemy randomizer: progression-aware placement (design)</t>
+          <t xml:space="preserve">Enemy Randomizer: final logic (as implemented)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quest 64 Recomp, 2026-09-20. Data on the Areas / Roster / Monsters tabs is the US ROM's, read out of the Merrow tables the randomizer already ships. Yellow cells are inputs; change them and the sheet recalculates.</t>
+          <t xml:space="preserve">Quest 64 Recomp, 2026-09-21. This is the shipped behaviour of the "Enemy Randomizer" switch on the Randomizer tab, one option that replaces Merrow\x27s "Shuffle Encounters" and the earlier "Enemy Progression". Data on the Areas / Roster / Monsters tabs is the US ROM\x27s, read out of the Merrow tables the randomizer ships. Yellow cells on Settings mirror the code\x27s constants; change them and the sheet previews the effect.</t>
         </is>
       </c>
     </row>
@@ -123,14 +123,14 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The problem</t>
+          <t xml:space="preserve">The problem it solves</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merrow's two enemy options are blind to difficulty. "Enemy tables" swaps whole monster tables between areas at random, so the Holy Plains can draw the Dindom Dries table (Red Wyvern, 550 HP, against a 50 HP Brian) while Brannoch Castle gets Were Hares. "Enemy composition" only rerolls packs inside an area's own table, so nothing actually changes hands. Neither touches stats, so a moved monster keeps its home numbers.</t>
+          <t xml:space="preserve">Merrow's enemy options are blind to difficulty. Swapping whole monster tables at random lets the Holy Plains draw the Dindom Dries set (Red Wyvern, 550 HP, against a 50 HP Brian) while Brannoch Castle gets Were Hares, and nothing touches stats, so a moved monster keeps its home numbers. The Enemy Randomizer keeps the "anything anywhere" variety but rewrites every placed monster's numbers for where it now lives, and guarantees the game gets progressively harder whatever the seed placed where.</t>
         </is>
       </c>
     </row>
@@ -138,14 +138,14 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The idea, in one line</t>
+          <t xml:space="preserve">In one line</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Give every area a tier (1-8, story order) and every monster a native tier (the tier of the area it comes from). An area of tier T draws its roster only from monsters whose native tier is within a chosen spread of T, and every placed monster has its stats rescaled toward the destination area's budget, so the shape of the monster (glass cannon, tank, fast) survives but its numbers match where it now lives. The budget never goes down from one area to the next, so the game always gets progressively harder regardless of what the seed placed where. Exp and stones follow the destination budget, so levelling pace is unchanged.</t>
+          <t xml:space="preserve">Every area is given one of the game's six monster sets at random (any set in any area) and its encounter packs are rerolled; when the set is loaded for that area, each monster's HP / ATK / DEF / AGI / EXP / Stones are moved to the area's vanilla average, keeping the square root of the monster's own deviation from its home average, times a guard that never lets an area's numbers fall below the previous area's.</t>
         </is>
       </c>
     </row>
@@ -160,35 +160,35 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Tiers (Areas tab, column C): T1 Holy Plains / Connor Forest, T2 Dondoran Flats / Glencoe Forest / West Carmaugh, T3 Cull Hazard / East Limelin, T4 Windward Forest / Blue Cave / Isle of Skye, T5 Baragoon Tunnel, T6 Dindom Dries / Boil Hole, T7 Baragoon Moor / Brannoch Castle, T8 Mammon's World. Editable.</t>
+          <t xml:space="preserve">1. Tiers (Areas tab, column C): T1 Holy Plains / Connor Forest, T2 Dondoran Flats / Glencoe Forest / West Carmaugh, T3 Cull Hazard / East Limelin, T4 Windward Forest / Blue Cave / Isle of Skye, T5 Baragoon Tunnel, T6 Dindom Dries / Boil Hole, T7 Baragoon Moor / Brannoch Castle, T8 Mammon's World. Story order; the Areas rows are in this order and the guard (rule 6) walks it.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Monster native tier = tier of its home area (first area it appears in, by progression). The Monsters tab also computes a Power score from stats and a Power tier from thresholds (Settings), so you can see where a monster really sits versus where the game puts it (e.g. Cockatrice is T2 by area but T3 by numbers).</t>
+          <t xml:space="preserve">2. Monster native tier = tier of its home area (first area it appears in, by progression). The Monsters tab also computes a Power score from stats and a Power tier from the Settings thresholds, so you can see where a monster really sits versus where the game puts it (e.g. Cockatrice is T2 by area but T3 by numbers). The code only uses the home area, for the averages.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Spread (Settings B4 down / B5 up). Default 7 / 7: any monster set can appear in any area, the scaling below is what balances it. Narrower spreads (e.g. 1 / 1) keep an area to sets whose monsters are within that many tiers of its own; 0 / 0 is a reshuffle within difficulty bands. Note the game\x27s monsters come in six fixed sets that are placed whole (see Implementation), so the window applies to sets, not single monsters.</t>
+          <t xml:space="preserve">3. Placement is per monster set, not per monster. The game keeps its monsters in six files (Implementation tab), and every file loads to the same RAM address, so an area can only ever hold one whole set. For each of the 16 areas in progression order the seed picks one of the six sets; with spread 7 / 7 (Settings B4-B5) every set is a candidate for every area. When there is a choice, the set the previous area got is skipped, so consecutive areas look different. Submaps that share pack definitions (Baragoon Moor 1-2, Brannoch 1-6, Mammon 1-6) are one area and get one set.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Roster size stays the same. Each area keeps its vanilla number of distinct monsters (Areas column E), because the pack definitions reference table slots 0..N-1 and the packs' shapes (how many of each, min + extra) are kept as they are. The randomizer fills those slots from the allowed pool, no repeats within an area, and prefers monsters not already used by a neighbouring tier so the game does not become the same eight enemies everywhere.</t>
+          <t xml:space="preserve">4. Packs are rerolled. Each area keeps its vanilla number of packs and each pack its shape (how many members, always-count + extra-count), but every member slot is refilled from the new set with no repeats inside a pack, and every region gets a full seven presets drawn from the area's packs (Merrow's composition logic). So the roster an area shows is the whole placed set, in new combinations.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. Stat scaling. For a monster placed in area A: new = AreaAvg(A, stat) * (own / AreaAvg(home, stat)) ^ s * guard(A). The monster is moved to the destination\x27s average and keeps its own deviation from its home average, compressed by the shape exponent s (Settings B26, 0.5): a monster three times its home average lands at 1.7 times the destination\x27s, so home-area bruisers like Ork Jr do not become super-bosses late. s = 1 would preserve the ratio exactly, 0 would make every monster the destination average. Applies to HP, ATK, DEF, AGI, EXP and Stones alike; spell damage follows ATK inside the game. HP capped at 999, ATK/DEF/AGI at 255. See ScalingExample.</t>
+          <t xml:space="preserve">5. Stat scaling. For a monster of home area H placed in area A: new = AreaAvg(A, stat) * (own / AreaAvg(H, stat)) ^ s * guard(A), with s = Settings B6 (0.5). The monster is moved to the destination's average and keeps its own deviation from its home average, compressed: a monster three times its home average lands at 1.7 times the destination's, so home-area bruisers like Ork Jr do not become super-bosses late. Applies to HP, ATK, DEF, AGI, EXP and Stones alike, then rounds, floors at 1 and caps (HP 999, ATK/DEF/AGI 255, EXP 65535). See ScalingExample.</t>
         </is>
       </c>
     </row>
@@ -202,36 +202,35 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7. Flying and dangerous flags (Monsters K-L) are informational only: nothing is excluded from any area. Cockatrice keeps its petrify wherever it lands, so it is the one monster whose danger the numbers do not capture; Settings B8 = Y pins it (and Flamed Mane) at their native tier or above if that proves too harsh early.</t>
+          <t xml:space="preserve">7. Damage needs nothing extra. The game computes an enemy's spell / attack damage from the ATK in its table entry (the base passed to the damage routine already follows it), so scaling ATK scales damage. An earlier build also multiplied the damage itself and double-counted (a Were Hare hit for 592 in Mammon's World); that hook is gone. Brian's own damage is never touched.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8. Bosses are out of scope. The boss logic that already exists in the randomizer stays as it is; nothing here moves, rescales or reads the boss entries (monster ids 67+).</t>
+          <t xml:space="preserve">8. Flying and dangerous flags (Monsters K-L) are informational only: nothing is excluded from any area. Cockatrice keeps its petrify wherever it lands, so it is the one monster whose danger the numbers do not capture.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9. Same seed, same result: the placement is a pure function of the seed and these settings, so a seed can be shared like any other randomizer seed, and the spoiler log lists each area's new roster with the scaled stats.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
+          <t xml:space="preserve">9. Bosses are out of scope. The boss logic that already exists in the randomizer stays as it is; nothing here moves, rescales or reads the boss entries (monster ids 67+), and the boss files are separate from the six sets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Same seed, same result. Set choice and pack rerolls come from the seed's RNG, and the scaling is a pure function of the data on these tabs, so a seed can be shared like any other. The spoiler log (%LOCALAPPDATA%\Quest64Recompiled\randomizer_spoiler.txt) lists each area's set, guard and every monster's vanilla -&gt; scaled HP/ATK/DEF/AGI/EXP.</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Why this is cheap to build</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Everything it changes is ROM data the randomizer already writes at boot: the area's table index (map header), the pack member ids, and each monster's six stat halfwords (Monsters column S has the ROM address). No native hooks and no recompiled code. The one engine question to verify is whether a table can mix monsters from different world chunks (the Implementation tab explains).</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11. Stacking with other options. The "Stats" randomizer option (Merrow's monster stat shuffle) writes the ROM at boot, and the Enemy Randomizer scales whatever the file holds when it loads, so the two stack: Stats perturbs a monster's own numbers, the Enemy Randomizer then fits them to the area. Hard Mode overrides the whole randomizer, so with Hard Mode on none of this runs.</t>
         </is>
       </c>
     </row>
@@ -250,14 +249,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settings (inputs)</t>
+          <t xml:space="preserve">Settings (the constants the code uses)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yellow cells are the knobs the design refers to. Everything else on the other tabs is calculated from these and the game data.</t>
+          <t xml:space="preserve">Yellow cells are the knobs the design refers to; the other tabs recalculate from them. The game itself uses the same values as constants in enemy_progression.cpp (spread_down, spread_up, shape_exponent, caps[]), so changing a cell here previews a change, it does not apply one.</t>
         </is>
       </c>
     </row>
@@ -289,7 +288,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An area may take monsters from this many tiers BELOW its own (easier monsters, scaled up). 7 = any tier (the default: placement is unrestricted, the scaling does the balancing). 0 = none.</t>
+          <t xml:space="preserve">An area may take a monster set from this many tiers BELOW its own (easier monsters, scaled up). 7 = any tier. The shipped value is 7: placement is unrestricted and the scaling does the balancing.</t>
         </is>
       </c>
     </row>
@@ -300,264 +299,231 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">An area may take monsters from this many tiers ABOVE its own (harder monsters, scaled down). 0 = none. 7 = anything (Merrow's behaviour).</t>
+          <t xml:space="preserve">An area may take a set from this many tiers ABOVE its own (harder monsters, scaled down). 7 = any tier (shipped). 0 would keep an area to sets no harder than its own tier.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scaling strength k</t>
+          <t xml:space="preserve">Shape exponent s</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 = keep home stats, 0.5 = halfway to the destination area's average, 1 = full fit. EXP and the progression guard always use 1.</t>
+          <t xml:space="preserve">Rule 5: how much of a monster's deviation from its home average survives the move. 0.5 = square root (a monster at 3x its home average lands at 1.7x the destination's); 1 keeps the exact ratio; 0 makes every monster the destination average. Shipped: 0.5, chosen after Ork Jr (3x its home HP) hit the 999 cap in Mammon's World at s = 1.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max fliers per area</t>
+          <t xml:space="preserve">Bulk: DEF weight</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not enforced (any monster may appear anywhere); kept for reference. The ROM flags only Wyvern, Will-o\x27-Wisp and Pixie as flying.</t>
+          <t xml:space="preserve">Bulk = HP * (1 + DEF / this). Larger = DEF matters less. Feeds the Power score, which the guard (rule 6) is built on.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dangerous: keep at native tier or above</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
+          <t xml:space="preserve">Threat: AGI weight</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>50</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Off by default: Cockatrice / Flamed Mane may appear anywhere, rescaled like everything else. Y pins them at or above their native tier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bulk: DEF weight</t>
-        </is>
-      </c>
-      <c r="B9" s="2">
-        <v>25</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bulk = HP * (1 + DEF / this). Larger = DEF matters less.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">Threat = ATK * (1 + AGI / this). Larger = AGI matters less.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Threat: AGI weight</t>
-        </is>
-      </c>
-      <c r="B10" s="2">
-        <v>50</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Threat = ATK * (1 + AGI / this). Larger = AGI matters less.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power tier thresholds</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power at least</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T2 from</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <v>30</v>
+      </c>
+      <c r="C11" s="0">
+        <v>2</v>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Power tier thresholds</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Power at least</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tier</t>
-        </is>
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T3 from</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <v>80</v>
+      </c>
+      <c r="C12" s="0">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2 from</t>
+          <t xml:space="preserve">T4 from</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C13" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T3 from</t>
+          <t xml:space="preserve">T5 from</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="C14" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T4 from</t>
+          <t xml:space="preserve">T6 from</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C15" s="0">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T5 from</t>
+          <t xml:space="preserve">T7 from</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="C16" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">T6 from</t>
+          <t xml:space="preserve">T8 from</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="C17" s="0">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T7 from</t>
-        </is>
-      </c>
-      <c r="B18" s="2">
-        <v>360</v>
-      </c>
-      <c r="C18" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T8 from</t>
-        </is>
-      </c>
-      <c r="B19" s="2">
-        <v>450</v>
-      </c>
-      <c r="C19" s="0">
-        <v>8</v>
-      </c>
-    </row>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power = SQRT(Bulk * Threat). Vanilla tier averages under the eight tiers: T1 15, T2 48, T3 119, T4 111, T5 187, T6 329, T7 397, T8 504 (T3 and T4 overlap: East Limelin is tougher by numbers than Windward/Blue Cave). Informational: the code does not use power tiers, only the area averages and the guard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Power = SQRT(Bulk * Threat). Vanilla tier averages under the eight tiers: T1 15, T2 48, T3 119, T4 111, T5 187, T6 329, T7 397, T8 504 (T3 and T4 overlap: East Limelin is tougher by numbers than Windward/Blue Cave). Adjust and watch Monsters column P.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stat caps</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cap</t>
+        </is>
+      </c>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HP cap</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>999</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vanilla monsters stay under 999; Hard Mode raises Brian's caps to 999 too.</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stat caps</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cap</t>
-        </is>
-      </c>
-      <c r="C22" s="1"/>
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATK/DEF/AGI cap</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>255</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stored as bytes in the game's battle struct.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">HP cap</t>
+          <t xml:space="preserve">EXP / Stones cap</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>999</v>
+        <v>65535</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vanilla monsters stay under 999; Hard Mode raises Brian's caps to 999 too.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ATK/DEF/AGI cap</t>
-        </is>
-      </c>
-      <c r="B24" s="2">
-        <v>255</v>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stored as bytes in the game's battle struct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shape exponent s</t>
-        </is>
-      </c>
-      <c r="B26" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rule 5: how much of a monster's deviation from its home average survives the move. 0.5 = square root (a monster at 3x its home average lands at 1.7x the destination's); 1 keeps the exact ratio; 0 makes every monster the destination average. This cell is B26.</t>
+          <t xml:space="preserve">EXP and Stones are words in the table; capped generously. Every scaled value is also floored at 1.</t>
         </is>
       </c>
     </row>
@@ -597,7 +563,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tier (C) is an input. Averages (G-L) are over the area's vanilla roster (Roster tab). Budget (M) = MAX(own average power, previous budget), so it never falls; Guard (N) = budget / own average, the multiplier applied to everything placed here. Allowed tiers (O-P) follow the spread settings. Q counts how many monsters could be placed here under the current settings; E is how many the randomizer must place.</t>
+          <t xml:space="preserve">Tier (C) is an input. Averages (G-L) are over the area's vanilla roster (Roster tab). Budget (M) = MAX(own average power, previous budget), so it never falls; Guard (N) = budget / own average, the multiplier applied to everything placed here. Allowed tiers (O-P) follow the spread settings. Q counts how many monsters could be placed here under the current settings (all 67 with 7 / 7); E is the vanilla roster size, which the placed set replaces whole.</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5463,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stats are the ROM's (HP, ATK, DEF, AGI, EXP; Drop is the item drop slot). Native tier comes from the home area's tier on the Areas tab. Flying is the ROM's own flag (only Wyvern, Will-o'-Wisp and Pixie carry it), not a visual judgement. Power/Power tier use the Settings weights and thresholds. Q-R are the area tiers this monster may be placed in under the current spread (Q uses spread-up: a monster may go to areas up to that many tiers below it; R uses spread-down); dangerous monsters are pinned at or above their native tier. S is where the six stat halfwords live in the ROM. Bosses (ids 67+) are not listed: they are not part of this.</t>
+          <t xml:space="preserve">Stats are the ROM's (HP, ATK, DEF, AGI, EXP; Drop is the item drop slot). Native tier comes from the home area's tier on the Areas tab. Flying is the ROM's own flag (only Wyvern, Will-o'-Wisp and Pixie carry it), not a visual judgement. Power/Power tier use the Settings weights and thresholds. Q-R are the area tiers this monster may be placed in under the current spread (Q uses spread-up: a monster may go to areas up to that many tiers below it; R uses spread-down); with the shipped 7 / 7 that is every tier. Dangerous (L) is informational. S is where the six stat halfwords live in the ROM. Bosses (ids 67+) are not listed: they are not part of this.</t>
         </is>
       </c>
     </row>
@@ -5644,19 +5610,19 @@
         </is>
       </c>
       <c r="M4" s="7">
-        <f>E4*(1+G4/Settings!$B$9)</f>
+        <f>E4*(1+G4/Settings!$B$7)</f>
       </c>
       <c r="N4" s="7">
-        <f>F4*(1+H4/Settings!$B$10)</f>
+        <f>F4*(1+H4/Settings!$B$8)</f>
       </c>
       <c r="O4" s="7">
         <f>ROUND(SQRT(M4*N4),1)</f>
       </c>
       <c r="P4" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O4)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O4)</f>
       </c>
       <c r="Q4" s="0">
-        <f>IF(AND(L4="Y",Settings!$B$8="Y"),D4,MAX(1,D4-Settings!$B$5))</f>
+        <f>MAX(1,D4-Settings!$B$5)</f>
       </c>
       <c r="R4" s="0">
         <f>MIN(8,D4+Settings!$B$4)</f>
@@ -5713,19 +5679,19 @@
         </is>
       </c>
       <c r="M5" s="7">
-        <f>E5*(1+G5/Settings!$B$9)</f>
+        <f>E5*(1+G5/Settings!$B$7)</f>
       </c>
       <c r="N5" s="7">
-        <f>F5*(1+H5/Settings!$B$10)</f>
+        <f>F5*(1+H5/Settings!$B$8)</f>
       </c>
       <c r="O5" s="7">
         <f>ROUND(SQRT(M5*N5),1)</f>
       </c>
       <c r="P5" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O5)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O5)</f>
       </c>
       <c r="Q5" s="0">
-        <f>IF(AND(L5="Y",Settings!$B$8="Y"),D5,MAX(1,D5-Settings!$B$5))</f>
+        <f>MAX(1,D5-Settings!$B$5)</f>
       </c>
       <c r="R5" s="0">
         <f>MIN(8,D5+Settings!$B$4)</f>
@@ -5782,19 +5748,19 @@
         </is>
       </c>
       <c r="M6" s="7">
-        <f>E6*(1+G6/Settings!$B$9)</f>
+        <f>E6*(1+G6/Settings!$B$7)</f>
       </c>
       <c r="N6" s="7">
-        <f>F6*(1+H6/Settings!$B$10)</f>
+        <f>F6*(1+H6/Settings!$B$8)</f>
       </c>
       <c r="O6" s="7">
         <f>ROUND(SQRT(M6*N6),1)</f>
       </c>
       <c r="P6" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O6)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O6)</f>
       </c>
       <c r="Q6" s="0">
-        <f>IF(AND(L6="Y",Settings!$B$8="Y"),D6,MAX(1,D6-Settings!$B$5))</f>
+        <f>MAX(1,D6-Settings!$B$5)</f>
       </c>
       <c r="R6" s="0">
         <f>MIN(8,D6+Settings!$B$4)</f>
@@ -5851,19 +5817,19 @@
         </is>
       </c>
       <c r="M7" s="7">
-        <f>E7*(1+G7/Settings!$B$9)</f>
+        <f>E7*(1+G7/Settings!$B$7)</f>
       </c>
       <c r="N7" s="7">
-        <f>F7*(1+H7/Settings!$B$10)</f>
+        <f>F7*(1+H7/Settings!$B$8)</f>
       </c>
       <c r="O7" s="7">
         <f>ROUND(SQRT(M7*N7),1)</f>
       </c>
       <c r="P7" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O7)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O7)</f>
       </c>
       <c r="Q7" s="0">
-        <f>IF(AND(L7="Y",Settings!$B$8="Y"),D7,MAX(1,D7-Settings!$B$5))</f>
+        <f>MAX(1,D7-Settings!$B$5)</f>
       </c>
       <c r="R7" s="0">
         <f>MIN(8,D7+Settings!$B$4)</f>
@@ -5920,19 +5886,19 @@
         </is>
       </c>
       <c r="M8" s="7">
-        <f>E8*(1+G8/Settings!$B$9)</f>
+        <f>E8*(1+G8/Settings!$B$7)</f>
       </c>
       <c r="N8" s="7">
-        <f>F8*(1+H8/Settings!$B$10)</f>
+        <f>F8*(1+H8/Settings!$B$8)</f>
       </c>
       <c r="O8" s="7">
         <f>ROUND(SQRT(M8*N8),1)</f>
       </c>
       <c r="P8" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O8)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O8)</f>
       </c>
       <c r="Q8" s="0">
-        <f>IF(AND(L8="Y",Settings!$B$8="Y"),D8,MAX(1,D8-Settings!$B$5))</f>
+        <f>MAX(1,D8-Settings!$B$5)</f>
       </c>
       <c r="R8" s="0">
         <f>MIN(8,D8+Settings!$B$4)</f>
@@ -5989,19 +5955,19 @@
         </is>
       </c>
       <c r="M9" s="7">
-        <f>E9*(1+G9/Settings!$B$9)</f>
+        <f>E9*(1+G9/Settings!$B$7)</f>
       </c>
       <c r="N9" s="7">
-        <f>F9*(1+H9/Settings!$B$10)</f>
+        <f>F9*(1+H9/Settings!$B$8)</f>
       </c>
       <c r="O9" s="7">
         <f>ROUND(SQRT(M9*N9),1)</f>
       </c>
       <c r="P9" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O9)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O9)</f>
       </c>
       <c r="Q9" s="0">
-        <f>IF(AND(L9="Y",Settings!$B$8="Y"),D9,MAX(1,D9-Settings!$B$5))</f>
+        <f>MAX(1,D9-Settings!$B$5)</f>
       </c>
       <c r="R9" s="0">
         <f>MIN(8,D9+Settings!$B$4)</f>
@@ -6058,19 +6024,19 @@
         </is>
       </c>
       <c r="M10" s="7">
-        <f>E10*(1+G10/Settings!$B$9)</f>
+        <f>E10*(1+G10/Settings!$B$7)</f>
       </c>
       <c r="N10" s="7">
-        <f>F10*(1+H10/Settings!$B$10)</f>
+        <f>F10*(1+H10/Settings!$B$8)</f>
       </c>
       <c r="O10" s="7">
         <f>ROUND(SQRT(M10*N10),1)</f>
       </c>
       <c r="P10" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O10)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O10)</f>
       </c>
       <c r="Q10" s="0">
-        <f>IF(AND(L10="Y",Settings!$B$8="Y"),D10,MAX(1,D10-Settings!$B$5))</f>
+        <f>MAX(1,D10-Settings!$B$5)</f>
       </c>
       <c r="R10" s="0">
         <f>MIN(8,D10+Settings!$B$4)</f>
@@ -6127,19 +6093,19 @@
         </is>
       </c>
       <c r="M11" s="7">
-        <f>E11*(1+G11/Settings!$B$9)</f>
+        <f>E11*(1+G11/Settings!$B$7)</f>
       </c>
       <c r="N11" s="7">
-        <f>F11*(1+H11/Settings!$B$10)</f>
+        <f>F11*(1+H11/Settings!$B$8)</f>
       </c>
       <c r="O11" s="7">
         <f>ROUND(SQRT(M11*N11),1)</f>
       </c>
       <c r="P11" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O11)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O11)</f>
       </c>
       <c r="Q11" s="0">
-        <f>IF(AND(L11="Y",Settings!$B$8="Y"),D11,MAX(1,D11-Settings!$B$5))</f>
+        <f>MAX(1,D11-Settings!$B$5)</f>
       </c>
       <c r="R11" s="0">
         <f>MIN(8,D11+Settings!$B$4)</f>
@@ -6196,19 +6162,19 @@
         </is>
       </c>
       <c r="M12" s="7">
-        <f>E12*(1+G12/Settings!$B$9)</f>
+        <f>E12*(1+G12/Settings!$B$7)</f>
       </c>
       <c r="N12" s="7">
-        <f>F12*(1+H12/Settings!$B$10)</f>
+        <f>F12*(1+H12/Settings!$B$8)</f>
       </c>
       <c r="O12" s="7">
         <f>ROUND(SQRT(M12*N12),1)</f>
       </c>
       <c r="P12" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O12)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O12)</f>
       </c>
       <c r="Q12" s="0">
-        <f>IF(AND(L12="Y",Settings!$B$8="Y"),D12,MAX(1,D12-Settings!$B$5))</f>
+        <f>MAX(1,D12-Settings!$B$5)</f>
       </c>
       <c r="R12" s="0">
         <f>MIN(8,D12+Settings!$B$4)</f>
@@ -6265,19 +6231,19 @@
         </is>
       </c>
       <c r="M13" s="7">
-        <f>E13*(1+G13/Settings!$B$9)</f>
+        <f>E13*(1+G13/Settings!$B$7)</f>
       </c>
       <c r="N13" s="7">
-        <f>F13*(1+H13/Settings!$B$10)</f>
+        <f>F13*(1+H13/Settings!$B$8)</f>
       </c>
       <c r="O13" s="7">
         <f>ROUND(SQRT(M13*N13),1)</f>
       </c>
       <c r="P13" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O13)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O13)</f>
       </c>
       <c r="Q13" s="0">
-        <f>IF(AND(L13="Y",Settings!$B$8="Y"),D13,MAX(1,D13-Settings!$B$5))</f>
+        <f>MAX(1,D13-Settings!$B$5)</f>
       </c>
       <c r="R13" s="0">
         <f>MIN(8,D13+Settings!$B$4)</f>
@@ -6334,19 +6300,19 @@
         </is>
       </c>
       <c r="M14" s="7">
-        <f>E14*(1+G14/Settings!$B$9)</f>
+        <f>E14*(1+G14/Settings!$B$7)</f>
       </c>
       <c r="N14" s="7">
-        <f>F14*(1+H14/Settings!$B$10)</f>
+        <f>F14*(1+H14/Settings!$B$8)</f>
       </c>
       <c r="O14" s="7">
         <f>ROUND(SQRT(M14*N14),1)</f>
       </c>
       <c r="P14" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O14)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O14)</f>
       </c>
       <c r="Q14" s="0">
-        <f>IF(AND(L14="Y",Settings!$B$8="Y"),D14,MAX(1,D14-Settings!$B$5))</f>
+        <f>MAX(1,D14-Settings!$B$5)</f>
       </c>
       <c r="R14" s="0">
         <f>MIN(8,D14+Settings!$B$4)</f>
@@ -6403,19 +6369,19 @@
         </is>
       </c>
       <c r="M15" s="7">
-        <f>E15*(1+G15/Settings!$B$9)</f>
+        <f>E15*(1+G15/Settings!$B$7)</f>
       </c>
       <c r="N15" s="7">
-        <f>F15*(1+H15/Settings!$B$10)</f>
+        <f>F15*(1+H15/Settings!$B$8)</f>
       </c>
       <c r="O15" s="7">
         <f>ROUND(SQRT(M15*N15),1)</f>
       </c>
       <c r="P15" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O15)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O15)</f>
       </c>
       <c r="Q15" s="0">
-        <f>IF(AND(L15="Y",Settings!$B$8="Y"),D15,MAX(1,D15-Settings!$B$5))</f>
+        <f>MAX(1,D15-Settings!$B$5)</f>
       </c>
       <c r="R15" s="0">
         <f>MIN(8,D15+Settings!$B$4)</f>
@@ -6472,19 +6438,19 @@
         </is>
       </c>
       <c r="M16" s="7">
-        <f>E16*(1+G16/Settings!$B$9)</f>
+        <f>E16*(1+G16/Settings!$B$7)</f>
       </c>
       <c r="N16" s="7">
-        <f>F16*(1+H16/Settings!$B$10)</f>
+        <f>F16*(1+H16/Settings!$B$8)</f>
       </c>
       <c r="O16" s="7">
         <f>ROUND(SQRT(M16*N16),1)</f>
       </c>
       <c r="P16" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O16)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O16)</f>
       </c>
       <c r="Q16" s="0">
-        <f>IF(AND(L16="Y",Settings!$B$8="Y"),D16,MAX(1,D16-Settings!$B$5))</f>
+        <f>MAX(1,D16-Settings!$B$5)</f>
       </c>
       <c r="R16" s="0">
         <f>MIN(8,D16+Settings!$B$4)</f>
@@ -6541,19 +6507,19 @@
         </is>
       </c>
       <c r="M17" s="7">
-        <f>E17*(1+G17/Settings!$B$9)</f>
+        <f>E17*(1+G17/Settings!$B$7)</f>
       </c>
       <c r="N17" s="7">
-        <f>F17*(1+H17/Settings!$B$10)</f>
+        <f>F17*(1+H17/Settings!$B$8)</f>
       </c>
       <c r="O17" s="7">
         <f>ROUND(SQRT(M17*N17),1)</f>
       </c>
       <c r="P17" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O17)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O17)</f>
       </c>
       <c r="Q17" s="0">
-        <f>IF(AND(L17="Y",Settings!$B$8="Y"),D17,MAX(1,D17-Settings!$B$5))</f>
+        <f>MAX(1,D17-Settings!$B$5)</f>
       </c>
       <c r="R17" s="0">
         <f>MIN(8,D17+Settings!$B$4)</f>
@@ -6610,19 +6576,19 @@
         </is>
       </c>
       <c r="M18" s="7">
-        <f>E18*(1+G18/Settings!$B$9)</f>
+        <f>E18*(1+G18/Settings!$B$7)</f>
       </c>
       <c r="N18" s="7">
-        <f>F18*(1+H18/Settings!$B$10)</f>
+        <f>F18*(1+H18/Settings!$B$8)</f>
       </c>
       <c r="O18" s="7">
         <f>ROUND(SQRT(M18*N18),1)</f>
       </c>
       <c r="P18" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O18)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O18)</f>
       </c>
       <c r="Q18" s="0">
-        <f>IF(AND(L18="Y",Settings!$B$8="Y"),D18,MAX(1,D18-Settings!$B$5))</f>
+        <f>MAX(1,D18-Settings!$B$5)</f>
       </c>
       <c r="R18" s="0">
         <f>MIN(8,D18+Settings!$B$4)</f>
@@ -6679,19 +6645,19 @@
         </is>
       </c>
       <c r="M19" s="7">
-        <f>E19*(1+G19/Settings!$B$9)</f>
+        <f>E19*(1+G19/Settings!$B$7)</f>
       </c>
       <c r="N19" s="7">
-        <f>F19*(1+H19/Settings!$B$10)</f>
+        <f>F19*(1+H19/Settings!$B$8)</f>
       </c>
       <c r="O19" s="7">
         <f>ROUND(SQRT(M19*N19),1)</f>
       </c>
       <c r="P19" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O19)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O19)</f>
       </c>
       <c r="Q19" s="0">
-        <f>IF(AND(L19="Y",Settings!$B$8="Y"),D19,MAX(1,D19-Settings!$B$5))</f>
+        <f>MAX(1,D19-Settings!$B$5)</f>
       </c>
       <c r="R19" s="0">
         <f>MIN(8,D19+Settings!$B$4)</f>
@@ -6748,19 +6714,19 @@
         </is>
       </c>
       <c r="M20" s="7">
-        <f>E20*(1+G20/Settings!$B$9)</f>
+        <f>E20*(1+G20/Settings!$B$7)</f>
       </c>
       <c r="N20" s="7">
-        <f>F20*(1+H20/Settings!$B$10)</f>
+        <f>F20*(1+H20/Settings!$B$8)</f>
       </c>
       <c r="O20" s="7">
         <f>ROUND(SQRT(M20*N20),1)</f>
       </c>
       <c r="P20" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O20)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O20)</f>
       </c>
       <c r="Q20" s="0">
-        <f>IF(AND(L20="Y",Settings!$B$8="Y"),D20,MAX(1,D20-Settings!$B$5))</f>
+        <f>MAX(1,D20-Settings!$B$5)</f>
       </c>
       <c r="R20" s="0">
         <f>MIN(8,D20+Settings!$B$4)</f>
@@ -6817,19 +6783,19 @@
         </is>
       </c>
       <c r="M21" s="7">
-        <f>E21*(1+G21/Settings!$B$9)</f>
+        <f>E21*(1+G21/Settings!$B$7)</f>
       </c>
       <c r="N21" s="7">
-        <f>F21*(1+H21/Settings!$B$10)</f>
+        <f>F21*(1+H21/Settings!$B$8)</f>
       </c>
       <c r="O21" s="7">
         <f>ROUND(SQRT(M21*N21),1)</f>
       </c>
       <c r="P21" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O21)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O21)</f>
       </c>
       <c r="Q21" s="0">
-        <f>IF(AND(L21="Y",Settings!$B$8="Y"),D21,MAX(1,D21-Settings!$B$5))</f>
+        <f>MAX(1,D21-Settings!$B$5)</f>
       </c>
       <c r="R21" s="0">
         <f>MIN(8,D21+Settings!$B$4)</f>
@@ -6886,19 +6852,19 @@
         </is>
       </c>
       <c r="M22" s="7">
-        <f>E22*(1+G22/Settings!$B$9)</f>
+        <f>E22*(1+G22/Settings!$B$7)</f>
       </c>
       <c r="N22" s="7">
-        <f>F22*(1+H22/Settings!$B$10)</f>
+        <f>F22*(1+H22/Settings!$B$8)</f>
       </c>
       <c r="O22" s="7">
         <f>ROUND(SQRT(M22*N22),1)</f>
       </c>
       <c r="P22" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O22)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O22)</f>
       </c>
       <c r="Q22" s="0">
-        <f>IF(AND(L22="Y",Settings!$B$8="Y"),D22,MAX(1,D22-Settings!$B$5))</f>
+        <f>MAX(1,D22-Settings!$B$5)</f>
       </c>
       <c r="R22" s="0">
         <f>MIN(8,D22+Settings!$B$4)</f>
@@ -6955,19 +6921,19 @@
         </is>
       </c>
       <c r="M23" s="7">
-        <f>E23*(1+G23/Settings!$B$9)</f>
+        <f>E23*(1+G23/Settings!$B$7)</f>
       </c>
       <c r="N23" s="7">
-        <f>F23*(1+H23/Settings!$B$10)</f>
+        <f>F23*(1+H23/Settings!$B$8)</f>
       </c>
       <c r="O23" s="7">
         <f>ROUND(SQRT(M23*N23),1)</f>
       </c>
       <c r="P23" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O23)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O23)</f>
       </c>
       <c r="Q23" s="0">
-        <f>IF(AND(L23="Y",Settings!$B$8="Y"),D23,MAX(1,D23-Settings!$B$5))</f>
+        <f>MAX(1,D23-Settings!$B$5)</f>
       </c>
       <c r="R23" s="0">
         <f>MIN(8,D23+Settings!$B$4)</f>
@@ -7024,19 +6990,19 @@
         </is>
       </c>
       <c r="M24" s="7">
-        <f>E24*(1+G24/Settings!$B$9)</f>
+        <f>E24*(1+G24/Settings!$B$7)</f>
       </c>
       <c r="N24" s="7">
-        <f>F24*(1+H24/Settings!$B$10)</f>
+        <f>F24*(1+H24/Settings!$B$8)</f>
       </c>
       <c r="O24" s="7">
         <f>ROUND(SQRT(M24*N24),1)</f>
       </c>
       <c r="P24" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O24)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O24)</f>
       </c>
       <c r="Q24" s="0">
-        <f>IF(AND(L24="Y",Settings!$B$8="Y"),D24,MAX(1,D24-Settings!$B$5))</f>
+        <f>MAX(1,D24-Settings!$B$5)</f>
       </c>
       <c r="R24" s="0">
         <f>MIN(8,D24+Settings!$B$4)</f>
@@ -7093,19 +7059,19 @@
         </is>
       </c>
       <c r="M25" s="7">
-        <f>E25*(1+G25/Settings!$B$9)</f>
+        <f>E25*(1+G25/Settings!$B$7)</f>
       </c>
       <c r="N25" s="7">
-        <f>F25*(1+H25/Settings!$B$10)</f>
+        <f>F25*(1+H25/Settings!$B$8)</f>
       </c>
       <c r="O25" s="7">
         <f>ROUND(SQRT(M25*N25),1)</f>
       </c>
       <c r="P25" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O25)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O25)</f>
       </c>
       <c r="Q25" s="0">
-        <f>IF(AND(L25="Y",Settings!$B$8="Y"),D25,MAX(1,D25-Settings!$B$5))</f>
+        <f>MAX(1,D25-Settings!$B$5)</f>
       </c>
       <c r="R25" s="0">
         <f>MIN(8,D25+Settings!$B$4)</f>
@@ -7162,19 +7128,19 @@
         </is>
       </c>
       <c r="M26" s="7">
-        <f>E26*(1+G26/Settings!$B$9)</f>
+        <f>E26*(1+G26/Settings!$B$7)</f>
       </c>
       <c r="N26" s="7">
-        <f>F26*(1+H26/Settings!$B$10)</f>
+        <f>F26*(1+H26/Settings!$B$8)</f>
       </c>
       <c r="O26" s="7">
         <f>ROUND(SQRT(M26*N26),1)</f>
       </c>
       <c r="P26" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O26)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O26)</f>
       </c>
       <c r="Q26" s="0">
-        <f>IF(AND(L26="Y",Settings!$B$8="Y"),D26,MAX(1,D26-Settings!$B$5))</f>
+        <f>MAX(1,D26-Settings!$B$5)</f>
       </c>
       <c r="R26" s="0">
         <f>MIN(8,D26+Settings!$B$4)</f>
@@ -7231,19 +7197,19 @@
         </is>
       </c>
       <c r="M27" s="7">
-        <f>E27*(1+G27/Settings!$B$9)</f>
+        <f>E27*(1+G27/Settings!$B$7)</f>
       </c>
       <c r="N27" s="7">
-        <f>F27*(1+H27/Settings!$B$10)</f>
+        <f>F27*(1+H27/Settings!$B$8)</f>
       </c>
       <c r="O27" s="7">
         <f>ROUND(SQRT(M27*N27),1)</f>
       </c>
       <c r="P27" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O27)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O27)</f>
       </c>
       <c r="Q27" s="0">
-        <f>IF(AND(L27="Y",Settings!$B$8="Y"),D27,MAX(1,D27-Settings!$B$5))</f>
+        <f>MAX(1,D27-Settings!$B$5)</f>
       </c>
       <c r="R27" s="0">
         <f>MIN(8,D27+Settings!$B$4)</f>
@@ -7300,19 +7266,19 @@
         </is>
       </c>
       <c r="M28" s="7">
-        <f>E28*(1+G28/Settings!$B$9)</f>
+        <f>E28*(1+G28/Settings!$B$7)</f>
       </c>
       <c r="N28" s="7">
-        <f>F28*(1+H28/Settings!$B$10)</f>
+        <f>F28*(1+H28/Settings!$B$8)</f>
       </c>
       <c r="O28" s="7">
         <f>ROUND(SQRT(M28*N28),1)</f>
       </c>
       <c r="P28" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O28)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O28)</f>
       </c>
       <c r="Q28" s="0">
-        <f>IF(AND(L28="Y",Settings!$B$8="Y"),D28,MAX(1,D28-Settings!$B$5))</f>
+        <f>MAX(1,D28-Settings!$B$5)</f>
       </c>
       <c r="R28" s="0">
         <f>MIN(8,D28+Settings!$B$4)</f>
@@ -7369,19 +7335,19 @@
         </is>
       </c>
       <c r="M29" s="7">
-        <f>E29*(1+G29/Settings!$B$9)</f>
+        <f>E29*(1+G29/Settings!$B$7)</f>
       </c>
       <c r="N29" s="7">
-        <f>F29*(1+H29/Settings!$B$10)</f>
+        <f>F29*(1+H29/Settings!$B$8)</f>
       </c>
       <c r="O29" s="7">
         <f>ROUND(SQRT(M29*N29),1)</f>
       </c>
       <c r="P29" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O29)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O29)</f>
       </c>
       <c r="Q29" s="0">
-        <f>IF(AND(L29="Y",Settings!$B$8="Y"),D29,MAX(1,D29-Settings!$B$5))</f>
+        <f>MAX(1,D29-Settings!$B$5)</f>
       </c>
       <c r="R29" s="0">
         <f>MIN(8,D29+Settings!$B$4)</f>
@@ -7438,19 +7404,19 @@
         </is>
       </c>
       <c r="M30" s="7">
-        <f>E30*(1+G30/Settings!$B$9)</f>
+        <f>E30*(1+G30/Settings!$B$7)</f>
       </c>
       <c r="N30" s="7">
-        <f>F30*(1+H30/Settings!$B$10)</f>
+        <f>F30*(1+H30/Settings!$B$8)</f>
       </c>
       <c r="O30" s="7">
         <f>ROUND(SQRT(M30*N30),1)</f>
       </c>
       <c r="P30" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O30)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O30)</f>
       </c>
       <c r="Q30" s="0">
-        <f>IF(AND(L30="Y",Settings!$B$8="Y"),D30,MAX(1,D30-Settings!$B$5))</f>
+        <f>MAX(1,D30-Settings!$B$5)</f>
       </c>
       <c r="R30" s="0">
         <f>MIN(8,D30+Settings!$B$4)</f>
@@ -7507,19 +7473,19 @@
         </is>
       </c>
       <c r="M31" s="7">
-        <f>E31*(1+G31/Settings!$B$9)</f>
+        <f>E31*(1+G31/Settings!$B$7)</f>
       </c>
       <c r="N31" s="7">
-        <f>F31*(1+H31/Settings!$B$10)</f>
+        <f>F31*(1+H31/Settings!$B$8)</f>
       </c>
       <c r="O31" s="7">
         <f>ROUND(SQRT(M31*N31),1)</f>
       </c>
       <c r="P31" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O31)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O31)</f>
       </c>
       <c r="Q31" s="0">
-        <f>IF(AND(L31="Y",Settings!$B$8="Y"),D31,MAX(1,D31-Settings!$B$5))</f>
+        <f>MAX(1,D31-Settings!$B$5)</f>
       </c>
       <c r="R31" s="0">
         <f>MIN(8,D31+Settings!$B$4)</f>
@@ -7576,19 +7542,19 @@
         </is>
       </c>
       <c r="M32" s="7">
-        <f>E32*(1+G32/Settings!$B$9)</f>
+        <f>E32*(1+G32/Settings!$B$7)</f>
       </c>
       <c r="N32" s="7">
-        <f>F32*(1+H32/Settings!$B$10)</f>
+        <f>F32*(1+H32/Settings!$B$8)</f>
       </c>
       <c r="O32" s="7">
         <f>ROUND(SQRT(M32*N32),1)</f>
       </c>
       <c r="P32" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O32)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O32)</f>
       </c>
       <c r="Q32" s="0">
-        <f>IF(AND(L32="Y",Settings!$B$8="Y"),D32,MAX(1,D32-Settings!$B$5))</f>
+        <f>MAX(1,D32-Settings!$B$5)</f>
       </c>
       <c r="R32" s="0">
         <f>MIN(8,D32+Settings!$B$4)</f>
@@ -7645,19 +7611,19 @@
         </is>
       </c>
       <c r="M33" s="7">
-        <f>E33*(1+G33/Settings!$B$9)</f>
+        <f>E33*(1+G33/Settings!$B$7)</f>
       </c>
       <c r="N33" s="7">
-        <f>F33*(1+H33/Settings!$B$10)</f>
+        <f>F33*(1+H33/Settings!$B$8)</f>
       </c>
       <c r="O33" s="7">
         <f>ROUND(SQRT(M33*N33),1)</f>
       </c>
       <c r="P33" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O33)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O33)</f>
       </c>
       <c r="Q33" s="0">
-        <f>IF(AND(L33="Y",Settings!$B$8="Y"),D33,MAX(1,D33-Settings!$B$5))</f>
+        <f>MAX(1,D33-Settings!$B$5)</f>
       </c>
       <c r="R33" s="0">
         <f>MIN(8,D33+Settings!$B$4)</f>
@@ -7714,19 +7680,19 @@
         </is>
       </c>
       <c r="M34" s="7">
-        <f>E34*(1+G34/Settings!$B$9)</f>
+        <f>E34*(1+G34/Settings!$B$7)</f>
       </c>
       <c r="N34" s="7">
-        <f>F34*(1+H34/Settings!$B$10)</f>
+        <f>F34*(1+H34/Settings!$B$8)</f>
       </c>
       <c r="O34" s="7">
         <f>ROUND(SQRT(M34*N34),1)</f>
       </c>
       <c r="P34" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O34)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O34)</f>
       </c>
       <c r="Q34" s="0">
-        <f>IF(AND(L34="Y",Settings!$B$8="Y"),D34,MAX(1,D34-Settings!$B$5))</f>
+        <f>MAX(1,D34-Settings!$B$5)</f>
       </c>
       <c r="R34" s="0">
         <f>MIN(8,D34+Settings!$B$4)</f>
@@ -7783,19 +7749,19 @@
         </is>
       </c>
       <c r="M35" s="7">
-        <f>E35*(1+G35/Settings!$B$9)</f>
+        <f>E35*(1+G35/Settings!$B$7)</f>
       </c>
       <c r="N35" s="7">
-        <f>F35*(1+H35/Settings!$B$10)</f>
+        <f>F35*(1+H35/Settings!$B$8)</f>
       </c>
       <c r="O35" s="7">
         <f>ROUND(SQRT(M35*N35),1)</f>
       </c>
       <c r="P35" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O35)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O35)</f>
       </c>
       <c r="Q35" s="0">
-        <f>IF(AND(L35="Y",Settings!$B$8="Y"),D35,MAX(1,D35-Settings!$B$5))</f>
+        <f>MAX(1,D35-Settings!$B$5)</f>
       </c>
       <c r="R35" s="0">
         <f>MIN(8,D35+Settings!$B$4)</f>
@@ -7852,19 +7818,19 @@
         </is>
       </c>
       <c r="M36" s="7">
-        <f>E36*(1+G36/Settings!$B$9)</f>
+        <f>E36*(1+G36/Settings!$B$7)</f>
       </c>
       <c r="N36" s="7">
-        <f>F36*(1+H36/Settings!$B$10)</f>
+        <f>F36*(1+H36/Settings!$B$8)</f>
       </c>
       <c r="O36" s="7">
         <f>ROUND(SQRT(M36*N36),1)</f>
       </c>
       <c r="P36" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O36)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O36)</f>
       </c>
       <c r="Q36" s="0">
-        <f>IF(AND(L36="Y",Settings!$B$8="Y"),D36,MAX(1,D36-Settings!$B$5))</f>
+        <f>MAX(1,D36-Settings!$B$5)</f>
       </c>
       <c r="R36" s="0">
         <f>MIN(8,D36+Settings!$B$4)</f>
@@ -7921,19 +7887,19 @@
         </is>
       </c>
       <c r="M37" s="7">
-        <f>E37*(1+G37/Settings!$B$9)</f>
+        <f>E37*(1+G37/Settings!$B$7)</f>
       </c>
       <c r="N37" s="7">
-        <f>F37*(1+H37/Settings!$B$10)</f>
+        <f>F37*(1+H37/Settings!$B$8)</f>
       </c>
       <c r="O37" s="7">
         <f>ROUND(SQRT(M37*N37),1)</f>
       </c>
       <c r="P37" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O37)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O37)</f>
       </c>
       <c r="Q37" s="0">
-        <f>IF(AND(L37="Y",Settings!$B$8="Y"),D37,MAX(1,D37-Settings!$B$5))</f>
+        <f>MAX(1,D37-Settings!$B$5)</f>
       </c>
       <c r="R37" s="0">
         <f>MIN(8,D37+Settings!$B$4)</f>
@@ -7990,19 +7956,19 @@
         </is>
       </c>
       <c r="M38" s="7">
-        <f>E38*(1+G38/Settings!$B$9)</f>
+        <f>E38*(1+G38/Settings!$B$7)</f>
       </c>
       <c r="N38" s="7">
-        <f>F38*(1+H38/Settings!$B$10)</f>
+        <f>F38*(1+H38/Settings!$B$8)</f>
       </c>
       <c r="O38" s="7">
         <f>ROUND(SQRT(M38*N38),1)</f>
       </c>
       <c r="P38" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O38)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O38)</f>
       </c>
       <c r="Q38" s="0">
-        <f>IF(AND(L38="Y",Settings!$B$8="Y"),D38,MAX(1,D38-Settings!$B$5))</f>
+        <f>MAX(1,D38-Settings!$B$5)</f>
       </c>
       <c r="R38" s="0">
         <f>MIN(8,D38+Settings!$B$4)</f>
@@ -8059,19 +8025,19 @@
         </is>
       </c>
       <c r="M39" s="7">
-        <f>E39*(1+G39/Settings!$B$9)</f>
+        <f>E39*(1+G39/Settings!$B$7)</f>
       </c>
       <c r="N39" s="7">
-        <f>F39*(1+H39/Settings!$B$10)</f>
+        <f>F39*(1+H39/Settings!$B$8)</f>
       </c>
       <c r="O39" s="7">
         <f>ROUND(SQRT(M39*N39),1)</f>
       </c>
       <c r="P39" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O39)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O39)</f>
       </c>
       <c r="Q39" s="0">
-        <f>IF(AND(L39="Y",Settings!$B$8="Y"),D39,MAX(1,D39-Settings!$B$5))</f>
+        <f>MAX(1,D39-Settings!$B$5)</f>
       </c>
       <c r="R39" s="0">
         <f>MIN(8,D39+Settings!$B$4)</f>
@@ -8128,19 +8094,19 @@
         </is>
       </c>
       <c r="M40" s="7">
-        <f>E40*(1+G40/Settings!$B$9)</f>
+        <f>E40*(1+G40/Settings!$B$7)</f>
       </c>
       <c r="N40" s="7">
-        <f>F40*(1+H40/Settings!$B$10)</f>
+        <f>F40*(1+H40/Settings!$B$8)</f>
       </c>
       <c r="O40" s="7">
         <f>ROUND(SQRT(M40*N40),1)</f>
       </c>
       <c r="P40" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O40)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O40)</f>
       </c>
       <c r="Q40" s="0">
-        <f>IF(AND(L40="Y",Settings!$B$8="Y"),D40,MAX(1,D40-Settings!$B$5))</f>
+        <f>MAX(1,D40-Settings!$B$5)</f>
       </c>
       <c r="R40" s="0">
         <f>MIN(8,D40+Settings!$B$4)</f>
@@ -8197,19 +8163,19 @@
         </is>
       </c>
       <c r="M41" s="7">
-        <f>E41*(1+G41/Settings!$B$9)</f>
+        <f>E41*(1+G41/Settings!$B$7)</f>
       </c>
       <c r="N41" s="7">
-        <f>F41*(1+H41/Settings!$B$10)</f>
+        <f>F41*(1+H41/Settings!$B$8)</f>
       </c>
       <c r="O41" s="7">
         <f>ROUND(SQRT(M41*N41),1)</f>
       </c>
       <c r="P41" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O41)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O41)</f>
       </c>
       <c r="Q41" s="0">
-        <f>IF(AND(L41="Y",Settings!$B$8="Y"),D41,MAX(1,D41-Settings!$B$5))</f>
+        <f>MAX(1,D41-Settings!$B$5)</f>
       </c>
       <c r="R41" s="0">
         <f>MIN(8,D41+Settings!$B$4)</f>
@@ -8266,19 +8232,19 @@
         </is>
       </c>
       <c r="M42" s="7">
-        <f>E42*(1+G42/Settings!$B$9)</f>
+        <f>E42*(1+G42/Settings!$B$7)</f>
       </c>
       <c r="N42" s="7">
-        <f>F42*(1+H42/Settings!$B$10)</f>
+        <f>F42*(1+H42/Settings!$B$8)</f>
       </c>
       <c r="O42" s="7">
         <f>ROUND(SQRT(M42*N42),1)</f>
       </c>
       <c r="P42" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O42)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O42)</f>
       </c>
       <c r="Q42" s="0">
-        <f>IF(AND(L42="Y",Settings!$B$8="Y"),D42,MAX(1,D42-Settings!$B$5))</f>
+        <f>MAX(1,D42-Settings!$B$5)</f>
       </c>
       <c r="R42" s="0">
         <f>MIN(8,D42+Settings!$B$4)</f>
@@ -8335,19 +8301,19 @@
         </is>
       </c>
       <c r="M43" s="7">
-        <f>E43*(1+G43/Settings!$B$9)</f>
+        <f>E43*(1+G43/Settings!$B$7)</f>
       </c>
       <c r="N43" s="7">
-        <f>F43*(1+H43/Settings!$B$10)</f>
+        <f>F43*(1+H43/Settings!$B$8)</f>
       </c>
       <c r="O43" s="7">
         <f>ROUND(SQRT(M43*N43),1)</f>
       </c>
       <c r="P43" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O43)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O43)</f>
       </c>
       <c r="Q43" s="0">
-        <f>IF(AND(L43="Y",Settings!$B$8="Y"),D43,MAX(1,D43-Settings!$B$5))</f>
+        <f>MAX(1,D43-Settings!$B$5)</f>
       </c>
       <c r="R43" s="0">
         <f>MIN(8,D43+Settings!$B$4)</f>
@@ -8404,19 +8370,19 @@
         </is>
       </c>
       <c r="M44" s="7">
-        <f>E44*(1+G44/Settings!$B$9)</f>
+        <f>E44*(1+G44/Settings!$B$7)</f>
       </c>
       <c r="N44" s="7">
-        <f>F44*(1+H44/Settings!$B$10)</f>
+        <f>F44*(1+H44/Settings!$B$8)</f>
       </c>
       <c r="O44" s="7">
         <f>ROUND(SQRT(M44*N44),1)</f>
       </c>
       <c r="P44" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O44)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O44)</f>
       </c>
       <c r="Q44" s="0">
-        <f>IF(AND(L44="Y",Settings!$B$8="Y"),D44,MAX(1,D44-Settings!$B$5))</f>
+        <f>MAX(1,D44-Settings!$B$5)</f>
       </c>
       <c r="R44" s="0">
         <f>MIN(8,D44+Settings!$B$4)</f>
@@ -8473,19 +8439,19 @@
         </is>
       </c>
       <c r="M45" s="7">
-        <f>E45*(1+G45/Settings!$B$9)</f>
+        <f>E45*(1+G45/Settings!$B$7)</f>
       </c>
       <c r="N45" s="7">
-        <f>F45*(1+H45/Settings!$B$10)</f>
+        <f>F45*(1+H45/Settings!$B$8)</f>
       </c>
       <c r="O45" s="7">
         <f>ROUND(SQRT(M45*N45),1)</f>
       </c>
       <c r="P45" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O45)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O45)</f>
       </c>
       <c r="Q45" s="0">
-        <f>IF(AND(L45="Y",Settings!$B$8="Y"),D45,MAX(1,D45-Settings!$B$5))</f>
+        <f>MAX(1,D45-Settings!$B$5)</f>
       </c>
       <c r="R45" s="0">
         <f>MIN(8,D45+Settings!$B$4)</f>
@@ -8542,19 +8508,19 @@
         </is>
       </c>
       <c r="M46" s="7">
-        <f>E46*(1+G46/Settings!$B$9)</f>
+        <f>E46*(1+G46/Settings!$B$7)</f>
       </c>
       <c r="N46" s="7">
-        <f>F46*(1+H46/Settings!$B$10)</f>
+        <f>F46*(1+H46/Settings!$B$8)</f>
       </c>
       <c r="O46" s="7">
         <f>ROUND(SQRT(M46*N46),1)</f>
       </c>
       <c r="P46" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O46)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O46)</f>
       </c>
       <c r="Q46" s="0">
-        <f>IF(AND(L46="Y",Settings!$B$8="Y"),D46,MAX(1,D46-Settings!$B$5))</f>
+        <f>MAX(1,D46-Settings!$B$5)</f>
       </c>
       <c r="R46" s="0">
         <f>MIN(8,D46+Settings!$B$4)</f>
@@ -8611,19 +8577,19 @@
         </is>
       </c>
       <c r="M47" s="7">
-        <f>E47*(1+G47/Settings!$B$9)</f>
+        <f>E47*(1+G47/Settings!$B$7)</f>
       </c>
       <c r="N47" s="7">
-        <f>F47*(1+H47/Settings!$B$10)</f>
+        <f>F47*(1+H47/Settings!$B$8)</f>
       </c>
       <c r="O47" s="7">
         <f>ROUND(SQRT(M47*N47),1)</f>
       </c>
       <c r="P47" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O47)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O47)</f>
       </c>
       <c r="Q47" s="0">
-        <f>IF(AND(L47="Y",Settings!$B$8="Y"),D47,MAX(1,D47-Settings!$B$5))</f>
+        <f>MAX(1,D47-Settings!$B$5)</f>
       </c>
       <c r="R47" s="0">
         <f>MIN(8,D47+Settings!$B$4)</f>
@@ -8680,19 +8646,19 @@
         </is>
       </c>
       <c r="M48" s="7">
-        <f>E48*(1+G48/Settings!$B$9)</f>
+        <f>E48*(1+G48/Settings!$B$7)</f>
       </c>
       <c r="N48" s="7">
-        <f>F48*(1+H48/Settings!$B$10)</f>
+        <f>F48*(1+H48/Settings!$B$8)</f>
       </c>
       <c r="O48" s="7">
         <f>ROUND(SQRT(M48*N48),1)</f>
       </c>
       <c r="P48" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O48)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O48)</f>
       </c>
       <c r="Q48" s="0">
-        <f>IF(AND(L48="Y",Settings!$B$8="Y"),D48,MAX(1,D48-Settings!$B$5))</f>
+        <f>MAX(1,D48-Settings!$B$5)</f>
       </c>
       <c r="R48" s="0">
         <f>MIN(8,D48+Settings!$B$4)</f>
@@ -8749,19 +8715,19 @@
         </is>
       </c>
       <c r="M49" s="7">
-        <f>E49*(1+G49/Settings!$B$9)</f>
+        <f>E49*(1+G49/Settings!$B$7)</f>
       </c>
       <c r="N49" s="7">
-        <f>F49*(1+H49/Settings!$B$10)</f>
+        <f>F49*(1+H49/Settings!$B$8)</f>
       </c>
       <c r="O49" s="7">
         <f>ROUND(SQRT(M49*N49),1)</f>
       </c>
       <c r="P49" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O49)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O49)</f>
       </c>
       <c r="Q49" s="0">
-        <f>IF(AND(L49="Y",Settings!$B$8="Y"),D49,MAX(1,D49-Settings!$B$5))</f>
+        <f>MAX(1,D49-Settings!$B$5)</f>
       </c>
       <c r="R49" s="0">
         <f>MIN(8,D49+Settings!$B$4)</f>
@@ -8818,19 +8784,19 @@
         </is>
       </c>
       <c r="M50" s="7">
-        <f>E50*(1+G50/Settings!$B$9)</f>
+        <f>E50*(1+G50/Settings!$B$7)</f>
       </c>
       <c r="N50" s="7">
-        <f>F50*(1+H50/Settings!$B$10)</f>
+        <f>F50*(1+H50/Settings!$B$8)</f>
       </c>
       <c r="O50" s="7">
         <f>ROUND(SQRT(M50*N50),1)</f>
       </c>
       <c r="P50" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O50)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O50)</f>
       </c>
       <c r="Q50" s="0">
-        <f>IF(AND(L50="Y",Settings!$B$8="Y"),D50,MAX(1,D50-Settings!$B$5))</f>
+        <f>MAX(1,D50-Settings!$B$5)</f>
       </c>
       <c r="R50" s="0">
         <f>MIN(8,D50+Settings!$B$4)</f>
@@ -8887,19 +8853,19 @@
         </is>
       </c>
       <c r="M51" s="7">
-        <f>E51*(1+G51/Settings!$B$9)</f>
+        <f>E51*(1+G51/Settings!$B$7)</f>
       </c>
       <c r="N51" s="7">
-        <f>F51*(1+H51/Settings!$B$10)</f>
+        <f>F51*(1+H51/Settings!$B$8)</f>
       </c>
       <c r="O51" s="7">
         <f>ROUND(SQRT(M51*N51),1)</f>
       </c>
       <c r="P51" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O51)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O51)</f>
       </c>
       <c r="Q51" s="0">
-        <f>IF(AND(L51="Y",Settings!$B$8="Y"),D51,MAX(1,D51-Settings!$B$5))</f>
+        <f>MAX(1,D51-Settings!$B$5)</f>
       </c>
       <c r="R51" s="0">
         <f>MIN(8,D51+Settings!$B$4)</f>
@@ -8956,19 +8922,19 @@
         </is>
       </c>
       <c r="M52" s="7">
-        <f>E52*(1+G52/Settings!$B$9)</f>
+        <f>E52*(1+G52/Settings!$B$7)</f>
       </c>
       <c r="N52" s="7">
-        <f>F52*(1+H52/Settings!$B$10)</f>
+        <f>F52*(1+H52/Settings!$B$8)</f>
       </c>
       <c r="O52" s="7">
         <f>ROUND(SQRT(M52*N52),1)</f>
       </c>
       <c r="P52" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O52)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O52)</f>
       </c>
       <c r="Q52" s="0">
-        <f>IF(AND(L52="Y",Settings!$B$8="Y"),D52,MAX(1,D52-Settings!$B$5))</f>
+        <f>MAX(1,D52-Settings!$B$5)</f>
       </c>
       <c r="R52" s="0">
         <f>MIN(8,D52+Settings!$B$4)</f>
@@ -9025,19 +8991,19 @@
         </is>
       </c>
       <c r="M53" s="7">
-        <f>E53*(1+G53/Settings!$B$9)</f>
+        <f>E53*(1+G53/Settings!$B$7)</f>
       </c>
       <c r="N53" s="7">
-        <f>F53*(1+H53/Settings!$B$10)</f>
+        <f>F53*(1+H53/Settings!$B$8)</f>
       </c>
       <c r="O53" s="7">
         <f>ROUND(SQRT(M53*N53),1)</f>
       </c>
       <c r="P53" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O53)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O53)</f>
       </c>
       <c r="Q53" s="0">
-        <f>IF(AND(L53="Y",Settings!$B$8="Y"),D53,MAX(1,D53-Settings!$B$5))</f>
+        <f>MAX(1,D53-Settings!$B$5)</f>
       </c>
       <c r="R53" s="0">
         <f>MIN(8,D53+Settings!$B$4)</f>
@@ -9094,19 +9060,19 @@
         </is>
       </c>
       <c r="M54" s="7">
-        <f>E54*(1+G54/Settings!$B$9)</f>
+        <f>E54*(1+G54/Settings!$B$7)</f>
       </c>
       <c r="N54" s="7">
-        <f>F54*(1+H54/Settings!$B$10)</f>
+        <f>F54*(1+H54/Settings!$B$8)</f>
       </c>
       <c r="O54" s="7">
         <f>ROUND(SQRT(M54*N54),1)</f>
       </c>
       <c r="P54" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O54)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O54)</f>
       </c>
       <c r="Q54" s="0">
-        <f>IF(AND(L54="Y",Settings!$B$8="Y"),D54,MAX(1,D54-Settings!$B$5))</f>
+        <f>MAX(1,D54-Settings!$B$5)</f>
       </c>
       <c r="R54" s="0">
         <f>MIN(8,D54+Settings!$B$4)</f>
@@ -9163,19 +9129,19 @@
         </is>
       </c>
       <c r="M55" s="7">
-        <f>E55*(1+G55/Settings!$B$9)</f>
+        <f>E55*(1+G55/Settings!$B$7)</f>
       </c>
       <c r="N55" s="7">
-        <f>F55*(1+H55/Settings!$B$10)</f>
+        <f>F55*(1+H55/Settings!$B$8)</f>
       </c>
       <c r="O55" s="7">
         <f>ROUND(SQRT(M55*N55),1)</f>
       </c>
       <c r="P55" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O55)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O55)</f>
       </c>
       <c r="Q55" s="0">
-        <f>IF(AND(L55="Y",Settings!$B$8="Y"),D55,MAX(1,D55-Settings!$B$5))</f>
+        <f>MAX(1,D55-Settings!$B$5)</f>
       </c>
       <c r="R55" s="0">
         <f>MIN(8,D55+Settings!$B$4)</f>
@@ -9232,19 +9198,19 @@
         </is>
       </c>
       <c r="M56" s="7">
-        <f>E56*(1+G56/Settings!$B$9)</f>
+        <f>E56*(1+G56/Settings!$B$7)</f>
       </c>
       <c r="N56" s="7">
-        <f>F56*(1+H56/Settings!$B$10)</f>
+        <f>F56*(1+H56/Settings!$B$8)</f>
       </c>
       <c r="O56" s="7">
         <f>ROUND(SQRT(M56*N56),1)</f>
       </c>
       <c r="P56" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O56)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O56)</f>
       </c>
       <c r="Q56" s="0">
-        <f>IF(AND(L56="Y",Settings!$B$8="Y"),D56,MAX(1,D56-Settings!$B$5))</f>
+        <f>MAX(1,D56-Settings!$B$5)</f>
       </c>
       <c r="R56" s="0">
         <f>MIN(8,D56+Settings!$B$4)</f>
@@ -9301,19 +9267,19 @@
         </is>
       </c>
       <c r="M57" s="7">
-        <f>E57*(1+G57/Settings!$B$9)</f>
+        <f>E57*(1+G57/Settings!$B$7)</f>
       </c>
       <c r="N57" s="7">
-        <f>F57*(1+H57/Settings!$B$10)</f>
+        <f>F57*(1+H57/Settings!$B$8)</f>
       </c>
       <c r="O57" s="7">
         <f>ROUND(SQRT(M57*N57),1)</f>
       </c>
       <c r="P57" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O57)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O57)</f>
       </c>
       <c r="Q57" s="0">
-        <f>IF(AND(L57="Y",Settings!$B$8="Y"),D57,MAX(1,D57-Settings!$B$5))</f>
+        <f>MAX(1,D57-Settings!$B$5)</f>
       </c>
       <c r="R57" s="0">
         <f>MIN(8,D57+Settings!$B$4)</f>
@@ -9370,19 +9336,19 @@
         </is>
       </c>
       <c r="M58" s="7">
-        <f>E58*(1+G58/Settings!$B$9)</f>
+        <f>E58*(1+G58/Settings!$B$7)</f>
       </c>
       <c r="N58" s="7">
-        <f>F58*(1+H58/Settings!$B$10)</f>
+        <f>F58*(1+H58/Settings!$B$8)</f>
       </c>
       <c r="O58" s="7">
         <f>ROUND(SQRT(M58*N58),1)</f>
       </c>
       <c r="P58" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O58)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O58)</f>
       </c>
       <c r="Q58" s="0">
-        <f>IF(AND(L58="Y",Settings!$B$8="Y"),D58,MAX(1,D58-Settings!$B$5))</f>
+        <f>MAX(1,D58-Settings!$B$5)</f>
       </c>
       <c r="R58" s="0">
         <f>MIN(8,D58+Settings!$B$4)</f>
@@ -9439,19 +9405,19 @@
         </is>
       </c>
       <c r="M59" s="7">
-        <f>E59*(1+G59/Settings!$B$9)</f>
+        <f>E59*(1+G59/Settings!$B$7)</f>
       </c>
       <c r="N59" s="7">
-        <f>F59*(1+H59/Settings!$B$10)</f>
+        <f>F59*(1+H59/Settings!$B$8)</f>
       </c>
       <c r="O59" s="7">
         <f>ROUND(SQRT(M59*N59),1)</f>
       </c>
       <c r="P59" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O59)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O59)</f>
       </c>
       <c r="Q59" s="0">
-        <f>IF(AND(L59="Y",Settings!$B$8="Y"),D59,MAX(1,D59-Settings!$B$5))</f>
+        <f>MAX(1,D59-Settings!$B$5)</f>
       </c>
       <c r="R59" s="0">
         <f>MIN(8,D59+Settings!$B$4)</f>
@@ -9508,19 +9474,19 @@
         </is>
       </c>
       <c r="M60" s="7">
-        <f>E60*(1+G60/Settings!$B$9)</f>
+        <f>E60*(1+G60/Settings!$B$7)</f>
       </c>
       <c r="N60" s="7">
-        <f>F60*(1+H60/Settings!$B$10)</f>
+        <f>F60*(1+H60/Settings!$B$8)</f>
       </c>
       <c r="O60" s="7">
         <f>ROUND(SQRT(M60*N60),1)</f>
       </c>
       <c r="P60" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O60)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O60)</f>
       </c>
       <c r="Q60" s="0">
-        <f>IF(AND(L60="Y",Settings!$B$8="Y"),D60,MAX(1,D60-Settings!$B$5))</f>
+        <f>MAX(1,D60-Settings!$B$5)</f>
       </c>
       <c r="R60" s="0">
         <f>MIN(8,D60+Settings!$B$4)</f>
@@ -9577,19 +9543,19 @@
         </is>
       </c>
       <c r="M61" s="7">
-        <f>E61*(1+G61/Settings!$B$9)</f>
+        <f>E61*(1+G61/Settings!$B$7)</f>
       </c>
       <c r="N61" s="7">
-        <f>F61*(1+H61/Settings!$B$10)</f>
+        <f>F61*(1+H61/Settings!$B$8)</f>
       </c>
       <c r="O61" s="7">
         <f>ROUND(SQRT(M61*N61),1)</f>
       </c>
       <c r="P61" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O61)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O61)</f>
       </c>
       <c r="Q61" s="0">
-        <f>IF(AND(L61="Y",Settings!$B$8="Y"),D61,MAX(1,D61-Settings!$B$5))</f>
+        <f>MAX(1,D61-Settings!$B$5)</f>
       </c>
       <c r="R61" s="0">
         <f>MIN(8,D61+Settings!$B$4)</f>
@@ -9646,19 +9612,19 @@
         </is>
       </c>
       <c r="M62" s="7">
-        <f>E62*(1+G62/Settings!$B$9)</f>
+        <f>E62*(1+G62/Settings!$B$7)</f>
       </c>
       <c r="N62" s="7">
-        <f>F62*(1+H62/Settings!$B$10)</f>
+        <f>F62*(1+H62/Settings!$B$8)</f>
       </c>
       <c r="O62" s="7">
         <f>ROUND(SQRT(M62*N62),1)</f>
       </c>
       <c r="P62" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O62)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O62)</f>
       </c>
       <c r="Q62" s="0">
-        <f>IF(AND(L62="Y",Settings!$B$8="Y"),D62,MAX(1,D62-Settings!$B$5))</f>
+        <f>MAX(1,D62-Settings!$B$5)</f>
       </c>
       <c r="R62" s="0">
         <f>MIN(8,D62+Settings!$B$4)</f>
@@ -9715,19 +9681,19 @@
         </is>
       </c>
       <c r="M63" s="7">
-        <f>E63*(1+G63/Settings!$B$9)</f>
+        <f>E63*(1+G63/Settings!$B$7)</f>
       </c>
       <c r="N63" s="7">
-        <f>F63*(1+H63/Settings!$B$10)</f>
+        <f>F63*(1+H63/Settings!$B$8)</f>
       </c>
       <c r="O63" s="7">
         <f>ROUND(SQRT(M63*N63),1)</f>
       </c>
       <c r="P63" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O63)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O63)</f>
       </c>
       <c r="Q63" s="0">
-        <f>IF(AND(L63="Y",Settings!$B$8="Y"),D63,MAX(1,D63-Settings!$B$5))</f>
+        <f>MAX(1,D63-Settings!$B$5)</f>
       </c>
       <c r="R63" s="0">
         <f>MIN(8,D63+Settings!$B$4)</f>
@@ -9784,19 +9750,19 @@
         </is>
       </c>
       <c r="M64" s="7">
-        <f>E64*(1+G64/Settings!$B$9)</f>
+        <f>E64*(1+G64/Settings!$B$7)</f>
       </c>
       <c r="N64" s="7">
-        <f>F64*(1+H64/Settings!$B$10)</f>
+        <f>F64*(1+H64/Settings!$B$8)</f>
       </c>
       <c r="O64" s="7">
         <f>ROUND(SQRT(M64*N64),1)</f>
       </c>
       <c r="P64" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O64)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O64)</f>
       </c>
       <c r="Q64" s="0">
-        <f>IF(AND(L64="Y",Settings!$B$8="Y"),D64,MAX(1,D64-Settings!$B$5))</f>
+        <f>MAX(1,D64-Settings!$B$5)</f>
       </c>
       <c r="R64" s="0">
         <f>MIN(8,D64+Settings!$B$4)</f>
@@ -9853,19 +9819,19 @@
         </is>
       </c>
       <c r="M65" s="7">
-        <f>E65*(1+G65/Settings!$B$9)</f>
+        <f>E65*(1+G65/Settings!$B$7)</f>
       </c>
       <c r="N65" s="7">
-        <f>F65*(1+H65/Settings!$B$10)</f>
+        <f>F65*(1+H65/Settings!$B$8)</f>
       </c>
       <c r="O65" s="7">
         <f>ROUND(SQRT(M65*N65),1)</f>
       </c>
       <c r="P65" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O65)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O65)</f>
       </c>
       <c r="Q65" s="0">
-        <f>IF(AND(L65="Y",Settings!$B$8="Y"),D65,MAX(1,D65-Settings!$B$5))</f>
+        <f>MAX(1,D65-Settings!$B$5)</f>
       </c>
       <c r="R65" s="0">
         <f>MIN(8,D65+Settings!$B$4)</f>
@@ -9922,19 +9888,19 @@
         </is>
       </c>
       <c r="M66" s="7">
-        <f>E66*(1+G66/Settings!$B$9)</f>
+        <f>E66*(1+G66/Settings!$B$7)</f>
       </c>
       <c r="N66" s="7">
-        <f>F66*(1+H66/Settings!$B$10)</f>
+        <f>F66*(1+H66/Settings!$B$8)</f>
       </c>
       <c r="O66" s="7">
         <f>ROUND(SQRT(M66*N66),1)</f>
       </c>
       <c r="P66" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O66)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O66)</f>
       </c>
       <c r="Q66" s="0">
-        <f>IF(AND(L66="Y",Settings!$B$8="Y"),D66,MAX(1,D66-Settings!$B$5))</f>
+        <f>MAX(1,D66-Settings!$B$5)</f>
       </c>
       <c r="R66" s="0">
         <f>MIN(8,D66+Settings!$B$4)</f>
@@ -9991,19 +9957,19 @@
         </is>
       </c>
       <c r="M67" s="7">
-        <f>E67*(1+G67/Settings!$B$9)</f>
+        <f>E67*(1+G67/Settings!$B$7)</f>
       </c>
       <c r="N67" s="7">
-        <f>F67*(1+H67/Settings!$B$10)</f>
+        <f>F67*(1+H67/Settings!$B$8)</f>
       </c>
       <c r="O67" s="7">
         <f>ROUND(SQRT(M67*N67),1)</f>
       </c>
       <c r="P67" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O67)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O67)</f>
       </c>
       <c r="Q67" s="0">
-        <f>IF(AND(L67="Y",Settings!$B$8="Y"),D67,MAX(1,D67-Settings!$B$5))</f>
+        <f>MAX(1,D67-Settings!$B$5)</f>
       </c>
       <c r="R67" s="0">
         <f>MIN(8,D67+Settings!$B$4)</f>
@@ -10060,19 +10026,19 @@
         </is>
       </c>
       <c r="M68" s="7">
-        <f>E68*(1+G68/Settings!$B$9)</f>
+        <f>E68*(1+G68/Settings!$B$7)</f>
       </c>
       <c r="N68" s="7">
-        <f>F68*(1+H68/Settings!$B$10)</f>
+        <f>F68*(1+H68/Settings!$B$8)</f>
       </c>
       <c r="O68" s="7">
         <f>ROUND(SQRT(M68*N68),1)</f>
       </c>
       <c r="P68" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O68)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O68)</f>
       </c>
       <c r="Q68" s="0">
-        <f>IF(AND(L68="Y",Settings!$B$8="Y"),D68,MAX(1,D68-Settings!$B$5))</f>
+        <f>MAX(1,D68-Settings!$B$5)</f>
       </c>
       <c r="R68" s="0">
         <f>MIN(8,D68+Settings!$B$4)</f>
@@ -10129,19 +10095,19 @@
         </is>
       </c>
       <c r="M69" s="7">
-        <f>E69*(1+G69/Settings!$B$9)</f>
+        <f>E69*(1+G69/Settings!$B$7)</f>
       </c>
       <c r="N69" s="7">
-        <f>F69*(1+H69/Settings!$B$10)</f>
+        <f>F69*(1+H69/Settings!$B$8)</f>
       </c>
       <c r="O69" s="7">
         <f>ROUND(SQRT(M69*N69),1)</f>
       </c>
       <c r="P69" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O69)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O69)</f>
       </c>
       <c r="Q69" s="0">
-        <f>IF(AND(L69="Y",Settings!$B$8="Y"),D69,MAX(1,D69-Settings!$B$5))</f>
+        <f>MAX(1,D69-Settings!$B$5)</f>
       </c>
       <c r="R69" s="0">
         <f>MIN(8,D69+Settings!$B$4)</f>
@@ -10198,19 +10164,19 @@
         </is>
       </c>
       <c r="M70" s="7">
-        <f>E70*(1+G70/Settings!$B$9)</f>
+        <f>E70*(1+G70/Settings!$B$7)</f>
       </c>
       <c r="N70" s="7">
-        <f>F70*(1+H70/Settings!$B$10)</f>
+        <f>F70*(1+H70/Settings!$B$8)</f>
       </c>
       <c r="O70" s="7">
         <f>ROUND(SQRT(M70*N70),1)</f>
       </c>
       <c r="P70" s="0">
-        <f>1+COUNTIF(Settings!$B$13:$B$19,"&lt;="&amp;O70)</f>
+        <f>1+COUNTIF(Settings!$B$11:$B$17,"&lt;="&amp;O70)</f>
       </c>
       <c r="Q70" s="0">
-        <f>IF(AND(L70="Y",Settings!$B$8="Y"),D70,MAX(1,D70-Settings!$B$5))</f>
+        <f>MAX(1,D70-Settings!$B$5)</f>
       </c>
       <c r="R70" s="0">
         <f>MIN(8,D70+Settings!$B$4)</f>
@@ -10248,7 +10214,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pick a monster and a destination area (yellow). The table shows its home stats, the two areas' vanilla averages, the factor between them, the destination's progression guard, and the rescaled stats under Settings!B6. The grid below previews the same monster in every area.</t>
+          <t xml:space="preserve">Pick a monster and a destination area (yellow). The table shows its home stats, the two areas' vanilla averages, the factor between them, the destination's progression guard, and the rescaled stats under the shape exponent (Settings B6) with the guard applied. The grid below previews the same monster in every area.</t>
         </is>
       </c>
     </row>
@@ -10385,13 +10351,13 @@
         <f>B10/C10</f>
       </c>
       <c r="F10" s="7">
-        <f>E10^Settings!$B$26</f>
+        <f>E10^Settings!$B$6</f>
       </c>
       <c r="G10" s="0">
         <f>MIN(H10,ROUND(D10*F10*$B$8,0))</f>
       </c>
       <c r="H10" s="0">
-        <f>Settings!$B$23</f>
+        <f>Settings!$B$21</f>
       </c>
     </row>
     <row r="11">
@@ -10413,13 +10379,13 @@
         <f>B11/C11</f>
       </c>
       <c r="F11" s="7">
-        <f>E11^Settings!$B$26</f>
+        <f>E11^Settings!$B$6</f>
       </c>
       <c r="G11" s="0">
         <f>MIN(H11,ROUND(D11*F11*$B$8,0))</f>
       </c>
       <c r="H11" s="0">
-        <f>Settings!$B$24</f>
+        <f>Settings!$B$22</f>
       </c>
     </row>
     <row r="12">
@@ -10441,13 +10407,13 @@
         <f>B12/C12</f>
       </c>
       <c r="F12" s="7">
-        <f>E12^Settings!$B$26</f>
+        <f>E12^Settings!$B$6</f>
       </c>
       <c r="G12" s="0">
         <f>MIN(H12,ROUND(D12*F12*$B$8,0))</f>
       </c>
       <c r="H12" s="0">
-        <f>Settings!$B$24</f>
+        <f>Settings!$B$22</f>
       </c>
     </row>
     <row r="13">
@@ -10469,13 +10435,13 @@
         <f>B13/C13</f>
       </c>
       <c r="F13" s="7">
-        <f>E13^Settings!$B$26</f>
+        <f>E13^Settings!$B$6</f>
       </c>
       <c r="G13" s="0">
         <f>MIN(H13,ROUND(D13*F13*$B$8,0))</f>
       </c>
       <c r="H13" s="0">
-        <f>Settings!$B$24</f>
+        <f>Settings!$B$22</f>
       </c>
     </row>
     <row r="14">
@@ -10497,13 +10463,13 @@
         <f>B14/C14</f>
       </c>
       <c r="F14" s="7">
-        <f>E14^Settings!$B$26</f>
+        <f>E14^Settings!$B$6</f>
       </c>
       <c r="G14" s="0">
         <f>MIN(H14,ROUND(D14*F14*$B$8,0))</f>
       </c>
       <c r="H14" s="0">
-        <f>99999</f>
+        <f>Settings!$B$23</f>
       </c>
     </row>
     <row r="15"/>
@@ -10566,19 +10532,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A18,Areas!$B:$B,0))</f>
       </c>
       <c r="C18" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D18" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E18" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F18" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G18" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A18,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A18,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H18" s="0">
         <f>IF(AND(B18&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B18&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10594,19 +10560,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A19,Areas!$B:$B,0))</f>
       </c>
       <c r="C19" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D19" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E19" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F19" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G19" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A19,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A19,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H19" s="0">
         <f>IF(AND(B19&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B19&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10622,19 +10588,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A20,Areas!$B:$B,0))</f>
       </c>
       <c r="C20" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D20" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E20" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F20" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G20" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A20,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A20,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H20" s="0">
         <f>IF(AND(B20&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B20&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10650,19 +10616,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A21,Areas!$B:$B,0))</f>
       </c>
       <c r="C21" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D21" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E21" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F21" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G21" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A21,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A21,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H21" s="0">
         <f>IF(AND(B21&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B21&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10678,19 +10644,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A22,Areas!$B:$B,0))</f>
       </c>
       <c r="C22" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D22" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E22" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F22" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G22" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A22,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A22,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H22" s="0">
         <f>IF(AND(B22&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B22&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10706,19 +10672,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A23,Areas!$B:$B,0))</f>
       </c>
       <c r="C23" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D23" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E23" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F23" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G23" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A23,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A23,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H23" s="0">
         <f>IF(AND(B23&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B23&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10734,19 +10700,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A24,Areas!$B:$B,0))</f>
       </c>
       <c r="C24" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D24" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E24" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F24" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G24" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A24,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A24,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H24" s="0">
         <f>IF(AND(B24&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B24&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10762,19 +10728,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A25,Areas!$B:$B,0))</f>
       </c>
       <c r="C25" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D25" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E25" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F25" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G25" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A25,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A25,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H25" s="0">
         <f>IF(AND(B25&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B25&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10790,19 +10756,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A26,Areas!$B:$B,0))</f>
       </c>
       <c r="C26" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D26" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E26" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F26" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G26" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A26,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A26,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H26" s="0">
         <f>IF(AND(B26&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B26&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10818,19 +10784,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A27,Areas!$B:$B,0))</f>
       </c>
       <c r="C27" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D27" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E27" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F27" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G27" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A27,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A27,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H27" s="0">
         <f>IF(AND(B27&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B27&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10846,19 +10812,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A28,Areas!$B:$B,0))</f>
       </c>
       <c r="C28" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D28" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E28" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F28" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G28" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A28,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A28,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H28" s="0">
         <f>IF(AND(B28&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B28&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10874,19 +10840,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A29,Areas!$B:$B,0))</f>
       </c>
       <c r="C29" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D29" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E29" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F29" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G29" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A29,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A29,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H29" s="0">
         <f>IF(AND(B29&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B29&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10902,19 +10868,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A30,Areas!$B:$B,0))</f>
       </c>
       <c r="C30" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D30" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E30" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F30" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G30" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A30,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A30,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H30" s="0">
         <f>IF(AND(B30&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B30&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10930,19 +10896,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A31,Areas!$B:$B,0))</f>
       </c>
       <c r="C31" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D31" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E31" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F31" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G31" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A31,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A31,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H31" s="0">
         <f>IF(AND(B31&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B31&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10958,19 +10924,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A32,Areas!$B:$B,0))</f>
       </c>
       <c r="C32" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D32" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E32" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F32" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G32" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A32,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A32,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H32" s="0">
         <f>IF(AND(B32&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B32&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -10986,19 +10952,19 @@
         <f>INDEX(Areas!$C:$C,MATCH($A33,Areas!$B:$B,0))</f>
       </c>
       <c r="C33" s="0">
-        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$G:$G,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$21,ROUND(INDEX(Areas!$G:$G,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$E:$E,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$G:$G,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="D33" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$H:$H,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$H:$H,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$F:$F,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$H:$H,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="E33" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$I:$I,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$I:$I,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$G:$G,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$I:$I,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="F33" s="0">
-        <f>MIN(Settings!$B$24,ROUND(INDEX(Areas!$J:$J,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$22,ROUND(INDEX(Areas!$J:$J,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$H:$H,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$J:$J,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="G33" s="0">
-        <f>MIN(99999,ROUND(INDEX(Areas!$K:$K,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$26*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
+        <f>MIN(Settings!$B$23,ROUND(INDEX(Areas!$K:$K,MATCH($A33,Areas!$B:$B,0))*(INDEX(Monsters!$I:$I,MATCH($B$3,Monsters!$B:$B,0))/INDEX(Areas!$K:$K,MATCH($B$5,Areas!$B:$B,0)))^Settings!$B$6*INDEX(Areas!$N:$N,MATCH($A33,Areas!$B:$B,0)),0))</f>
       </c>
       <c r="H33" s="0">
         <f>IF(AND(B33&gt;=INDEX(Monsters!$Q:$Q,MATCH($B$3,Monsters!$B:$B,0)),B33&lt;=INDEX(Monsters!$R:$R,MATCH($B$3,Monsters!$B:$B,0))),"yes","no")</f>
@@ -11017,7 +10983,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implementation notes (for the recomp's randomizer)</t>
+          <t xml:space="preserve">Implementation notes (how the recomp does it)</t>
         </is>
       </c>
     </row>
@@ -11031,77 +10997,98 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Six monster tables, one per world chunk: table 0 (ROM 0xADC090) Holy Plains + West Carmaugh, 1 (0xB63378) Connor / Dondoran Flats / Glencoe, 2 (0xBBDE98) Cull Hazard / Blue Cave / East Limelin, 3 (0xC317E8) Dindom / Boil Hole / Baragoon Moor / Brannoch, 4 (0xC9BE50) Windward / Isle of Skye / Baragoon Tunnel, 5 Mammon's World. Each area's 0x18-byte map header holds the table index it uses (merrow_mapdata.cpp AreaMap.table_index).</t>
+          <t xml:space="preserve">Six monster files, one per world chunk: file 0 (ROM 0xADC090) Holy Plains + West Carmaugh, 1 (0xB63378) Connor / Dondoran Flats / Glencoe, 2 (0xBBDE98) Cull Hazard / Blue Cave / East Limelin, 3 (0xC317E8) Dindom / Boil Hole / Baragoon Moor / Brannoch, 4 (0xC9BE50) Windward / Isle of Skye / Baragoon Tunnel, 5 Mammon's World. Each area's 0x18-byte map header holds the file index it uses (merrow_mapdata.cpp AreaMap.table_index). The file table at 0x80054160 has one 20-byte row per file: ROM start, ROM end, then three RAM pointers into the loaded file (table end at +8, table start at +0xC). Every file is DMA'd to the same RAM base (0x8020E6F0), which is why placement is per set: two sets cannot be in memory at once.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Encounters are packs: up to four (table slot, always-count, extra-count) entries, written as packCount*3 words at the pack's ROM address. Regions pick from up to seven pack presets. Baragoon Moor 1-2, Brannoch 1-6 and Mammon 1-6 share pack definitions, so those submaps must be treated as one area (the sheet already merges them).</t>
+          <t xml:space="preserve">Encounters are packs: up to four (table slot, always-count, extra-count) entries, written as packCount*3 words at the pack's ROM address. Regions pick from up to seven pack presets. Baragoon Moor 1-2, Brannoch 1-6 and Mammon 1-6 share pack definitions, so those submaps are treated as one area (the sheet merges them the same way).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monster stats are six halfwords per monster at the addresses in Monsters!S (HP is stored twice in a row; Merrow's one-hit-KO writes both). The randomizer already writes them (options.monster_stats / monster_scale), so rescaled stats are the same Write records.</t>
+          <t xml:space="preserve">The loaded monster table is 0x38 bytes per entry: +2 index, +4 and +6 HP (stored twice), +0xC AGI, +0xE DEF, +0x10 EXP (word), +0x14 Stones (word), +0x2A ATK. The battle set-up routine (func_80008FE0) copies an entry into the battle struct, and Soul Searcher reads the table directly, so the table is the one place that must hold the scaled numbers.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algorithm (boot time, pure function of seed + settings)</t>
+          <t xml:space="preserve">Boot (randomizer.cpp shuffle_enemies / patch_enemies, seed-driven)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Read tiers, spread, k from the options. 2. For each area in progression order: pool = monsters with Placeable-from &lt;= tier &lt;= Placeable-to, minus monsters already placed in this tier and its neighbours where possible, minus fliers over the cap. 3. Draw roster-size monsters from the pool (seeded RNG). 4. Build the area's table: either (a) point the area at the table that already holds those monsters when they all come from one chunk, or (b) write a new table into free ROM space listing the chosen monsters' entries. 5. Keep the pack shapes, remap each pack member's slot to the new roster. 6. For each placed monster, write scaled stats. 7. Spoiler log: area -&gt; roster with scaled stats.</t>
+          <t xml:space="preserve">1. For each of the 16 merged areas in progression order, candidate_tables() lists the files whose monsters fall inside the spread (all six with 7 / 7); the previous area's file is dropped when there is a choice; one is drawn with the seed's RNG. 2. The file index is written into every raw submap header of the area, and pack member ids are wrapped to the new file's size. 3. Packs are rerolled: every region gets seven presets drawn from the area's packs, and each pack's member slots are refilled from the file's entries with no repeats (Merrow's composition). 4. make_plan() turns the per-area file choice into a Plan: for each game map id, the (home area, destination area) pair of every entry of the file it uses, and writes the spoiler (vanilla -&gt; scaled stats). The Plan is installed with set_active() and the ROM writes go through the randomizer's normal Write records.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The one thing to verify first</t>
+          <t xml:space="preserve">Play time (native_hooks.cpp quest64_randomizer_enemy_scale_table)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether a table can mix monsters from different chunks, i.e. whether a monster's model and animation data is reachable from any area or only from its own chunk's overlay. Merrow's table swap already makes an area use another chunk's whole table, which suggests monsters load from wherever their table entry points; a 10-minute test is to hand-write one table entry (e.g. put a Wyvern into table 0) and walk into the Holy Plains. If cross-chunk placement is not possible, the fallback is spread = 0 within each chunk plus stat scaling, which still fixes the difficulty problem but with smaller pools.</t>
+          <t xml:space="preserve">One hook in func_80008EF4, the routine that DMAs a monster file, placed right after its dma call (before_vram 0x80008F5C). It reads the file-table row the game just loaded (row pointer at 0x8007D0BC), walks the table between the row's start and end pointers, and rewrites each entry in place with scaled_value(map, entry, stat, own) for HP (both halfwords), AGI, DEF, ATK, EXP and Stones. The map is gCurrentMap (0x80084EEC); if the plan has nothing for it (a load that happens during a transition) gNextMap (0x80084EE4) is used instead. Nothing runs unless the randomizer is the active mode, the Enemy Randomizer switch is on and Hard Mode is off.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Where it goes in the code</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scaling in RAM rather than in the ROM is forced by the shared RAM base: the same file serves several areas with different averages, so its stats cannot be fixed at boot. Scaling on load rather than at battle set-up is what makes Soul Searcher and the battle agree.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/game/randomizer/randomizer.cpp shuffle_enemies() already owns the table index / pack writes; add the tier pool selection there and the stat writes next to the existing monster_stats writes. Options: enemy_progression (bool), enemy_spread_down and enemy_spread_up (int), enemy_scale_strength (0/50/100 %), enemy_max_fliers. The per-area tiers and the progression budgets are constants derived from the Areas tab. UI: four controls under the existing "Enemy shuffling" group on the Randomizer tab. The tier table itself can be a constant array (one tier per area, from the Areas tab).</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula (enemy_progression.cpp rescale)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open questions</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new = round(AreaAvg(dest, stat) * (own / AreaAvg(home, stat)) ^ 0.5 * guard(dest)), then clamped to 1 .. cap (HP 999, ATK/DEF/AGI 255, EXP/Stones 65535). guard(dest) = budget / avg_power with budget = MAX(own avg power, previous area's budget), computed once from the Areas data (columns L-N). The area averages, home areas and file rosters are generated into enemy_progression_data.cpp by tools/enemyrandologic.pl from the same Merrow data this sheet is built from, so the sheet and the code cannot drift apart.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Should exp scale with k or always fully (this sheet says always)? Do the story bosses' areas (Connor, Windward, Blue Cave, Boil Hole, Moor, Brannoch) need the boss's own minions kept vanilla for the fight leading up to them?</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What was tried and dropped</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scaling per monster at battle set-up (func_80008FE0): battle numbers were right but Soul Searcher showed the unscaled table. Keying on gNextMap: wrong during the load that happens after a transition completes. A separate damage hook in func_80006BEC multiplying the damage base by the ATK ratio: the base already follows the scaled ATK, so it double-counted (x14.8 in Mammon's World). Shape exponent 1 (keep the exact ratio): Ork Jr, three times its home average, pinned at 999 HP in Mammon's World; 0.5 lands it around 780.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Files</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/game/randomizer/enemy_progression.h/.cpp (plan, rescale, scaled_value), enemy_progression_data.h/.cpp (GENERATED), native_hooks.cpp (the load hook), randomizer.cpp (placement, packs, spoiler, option), us.rev0.toml (the hook entry), include/randomizer.h (Options::enemy_randomizer), src/ui/ui_config.cpp + assets/config_menu/randomizer.rml (the switch), tools/enemyrandologic.pl (this sheet and the data). Setting stored as "enemy_randomizer" in randomizer.json.</t>
         </is>
       </c>
     </row>
